--- a/assets/download/onboarding-kit/labor-notice.xlsx
+++ b/assets/download/onboarding-kit/labor-notice.xlsx
@@ -3,14 +3,9 @@
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
   <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10913"/>
   <workbookPr/>
-  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-    <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/kondouakihiro/Documents/Codex/2026-08-16/new-chat/outputs/roudo_joken_excel_20260816/"/>
-    </mc:Choice>
-  </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D686B3D8-14CF-5443-9800-2AEFA6F89F2C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="600" windowWidth="51200" windowHeight="28200" activeTab="0" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="入力" sheetId="1" r:id="rId1"/>
@@ -21,7 +16,7 @@
     <definedName name="_xlnm.Print_Area" localSheetId="1">一般労働者用!$A$1:$L$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">短時間労働者用!$A$1:$L$25</definedName>
   </definedNames>
-  <calcPr calcId="191029" forceFullCalc="1"/>
+  <calcPr calcId="191029" calcMode="auto" fullCalcOnLoad="1" forceFullCalc="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -622,9 +617,11 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <numFmts count="2">
+  <numFmts count="4">
     <numFmt numFmtId="176" formatCode="#,##0&quot;円&quot;"/>
     <numFmt numFmtId="177" formatCode="0.##"/>
+    <numFmt numFmtId="178" formatCode="yyyy/m/d"/>
+    <numFmt numFmtId="179" formatCode="0.00"/>
   </numFmts>
   <fonts count="18">
     <font>
@@ -771,7 +768,7 @@
       </patternFill>
     </fill>
   </fills>
-  <borders count="38">
+  <borders count="39">
     <border>
       <left/>
       <right/>
@@ -1170,12 +1167,27 @@
       </bottom>
       <diagonal/>
     </border>
+    <border>
+      <left style="thin">
+        <color rgb="FFA6A6A6"/>
+      </left>
+      <right style="thin">
+        <color rgb="FFA6A6A6"/>
+      </right>
+      <top style="thin">
+        <color rgb="FFA6A6A6"/>
+      </top>
+      <bottom style="thin">
+        <color rgb="FFA6A6A6"/>
+      </bottom>
+      <diagonal/>
+    </border>
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="56">
+  <cellXfs count="65">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
@@ -1341,6 +1353,42 @@
     </xf>
     <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="178" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="6" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="1" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="179" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="179" fontId="6" fillId="5" borderId="38" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="176" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="179" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="right" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="31" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="1" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1560,8 +1608,9 @@
   <cols>
     <col min="1" max="1" width="3" customWidth="1"/>
     <col min="2" max="2" width="25" customWidth="1"/>
-    <col min="3" max="6" width="13" customWidth="1"/>
-    <col min="7" max="10" width="14" customWidth="1"/>
+    <col min="3" max="3" width="52" customWidth="1"/>
+    <col min="4" max="6" width="1.5" customWidth="1"/>
+    <col min="7" max="7" width="14" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:10">
@@ -1628,9 +1677,11 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:10" ht="28" customHeight="1">
-      <c r="A3" s="4" t="s">
-        <v>1</v>
+    <row r="3" spans="1:10" ht="52" customHeight="1">
+      <c r="A3" s="4" t="inlineStr">
+        <is>
+          <t xml:space="preserve">黄色のセルに入力します。末尾の「勤務制度」「基本賃金形態」も選択し、一般労働者用又は短時間労働者用を印刷してください。</t>
+        </is>
       </c>
       <c r="B3" s="5" t="s">
         <v>1</v>
@@ -1704,19 +1755,21 @@
         <v>2</v>
       </c>
     </row>
-    <row r="6" spans="1:10" ht="26" customHeight="1">
+    <row r="6" spans="1:10" ht="36" customHeight="1">
       <c r="A6" s="10" t="s">
         <v>3</v>
       </c>
       <c r="B6" s="10" t="s">
         <v>3</v>
       </c>
-      <c r="C6" s="11"/>
-      <c r="D6" s="11"/>
-      <c r="E6" s="11"/>
-      <c r="F6" s="11"/>
-      <c r="G6" s="12" t="s">
-        <v>4</v>
+      <c r="C6" s="56"/>
+      <c r="D6" s="0"/>
+      <c r="E6" s="0"/>
+      <c r="F6" s="0"/>
+      <c r="G6" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西暦で入力（例：2026/10/05）。日付として入力してください。</t>
+        </is>
       </c>
       <c r="H6" s="12" t="s">
         <v>4</v>
@@ -1728,17 +1781,17 @@
         <v>4</v>
       </c>
     </row>
-    <row r="7" spans="1:10" ht="26" customHeight="1">
+    <row r="7" spans="1:10" ht="36" customHeight="1">
       <c r="A7" s="10" t="s">
         <v>5</v>
       </c>
       <c r="B7" s="10" t="s">
         <v>5</v>
       </c>
-      <c r="C7" s="13"/>
-      <c r="D7" s="13"/>
-      <c r="E7" s="13"/>
-      <c r="F7" s="13"/>
+      <c r="C7" s="57"/>
+      <c r="D7" s="0"/>
+      <c r="E7" s="0"/>
+      <c r="F7" s="0"/>
       <c r="G7" s="12" t="s">
         <v>6</v>
       </c>
@@ -1752,17 +1805,17 @@
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:10" ht="32" customHeight="1">
+    <row r="8" spans="1:10" ht="60" customHeight="1">
       <c r="A8" s="10" t="s">
         <v>7</v>
       </c>
       <c r="B8" s="10" t="s">
         <v>7</v>
       </c>
-      <c r="C8" s="13"/>
-      <c r="D8" s="13"/>
-      <c r="E8" s="13"/>
-      <c r="F8" s="13"/>
+      <c r="C8" s="57"/>
+      <c r="D8" s="0"/>
+      <c r="E8" s="0"/>
+      <c r="F8" s="0"/>
       <c r="G8" s="12" t="s">
         <v>8</v>
       </c>
@@ -1776,17 +1829,17 @@
         <v>8</v>
       </c>
     </row>
-    <row r="9" spans="1:10" ht="38" customHeight="1">
+    <row r="9" spans="1:10" ht="72" customHeight="1">
       <c r="A9" s="10" t="s">
         <v>9</v>
       </c>
       <c r="B9" s="10" t="s">
         <v>9</v>
       </c>
-      <c r="C9" s="13"/>
-      <c r="D9" s="13"/>
-      <c r="E9" s="13"/>
-      <c r="F9" s="13"/>
+      <c r="C9" s="57"/>
+      <c r="D9" s="0"/>
+      <c r="E9" s="0"/>
+      <c r="F9" s="0"/>
       <c r="G9" s="12" t="s">
         <v>10</v>
       </c>
@@ -1800,17 +1853,17 @@
         <v>10</v>
       </c>
     </row>
-    <row r="10" spans="1:10" ht="26" customHeight="1">
+    <row r="10" spans="1:10" ht="36" customHeight="1">
       <c r="A10" s="10" t="s">
         <v>11</v>
       </c>
       <c r="B10" s="10" t="s">
         <v>11</v>
       </c>
-      <c r="C10" s="13"/>
-      <c r="D10" s="13"/>
-      <c r="E10" s="13"/>
-      <c r="F10" s="13"/>
+      <c r="C10" s="57"/>
+      <c r="D10" s="0"/>
+      <c r="E10" s="0"/>
+      <c r="F10" s="0"/>
       <c r="G10" s="12" t="s">
         <v>12</v>
       </c>
@@ -1824,17 +1877,17 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:10" ht="26" customHeight="1">
+    <row r="11" spans="1:10" ht="36" customHeight="1">
       <c r="A11" s="10" t="s">
         <v>13</v>
       </c>
       <c r="B11" s="10" t="s">
         <v>13</v>
       </c>
-      <c r="C11" s="13"/>
-      <c r="D11" s="13"/>
-      <c r="E11" s="13"/>
-      <c r="F11" s="13"/>
+      <c r="C11" s="57"/>
+      <c r="D11" s="0"/>
+      <c r="E11" s="0"/>
+      <c r="F11" s="0"/>
       <c r="G11" s="12" t="s">
         <v>14</v>
       </c>
@@ -1880,17 +1933,17 @@
         <v>15</v>
       </c>
     </row>
-    <row r="13" spans="1:10" ht="26" customHeight="1">
+    <row r="13" spans="1:10" ht="36" customHeight="1">
       <c r="A13" s="10" t="s">
         <v>16</v>
       </c>
       <c r="B13" s="10" t="s">
         <v>16</v>
       </c>
-      <c r="C13" s="13"/>
-      <c r="D13" s="13"/>
-      <c r="E13" s="13"/>
-      <c r="F13" s="13"/>
+      <c r="C13" s="57"/>
+      <c r="D13" s="0"/>
+      <c r="E13" s="0"/>
+      <c r="F13" s="0"/>
       <c r="G13" s="12" t="s">
         <v>17</v>
       </c>
@@ -1904,19 +1957,21 @@
         <v>17</v>
       </c>
     </row>
-    <row r="14" spans="1:10" ht="26" customHeight="1">
+    <row r="14" spans="1:10" ht="36" customHeight="1">
       <c r="A14" s="10" t="s">
         <v>18</v>
       </c>
       <c r="B14" s="10" t="s">
         <v>18</v>
       </c>
-      <c r="C14" s="11"/>
-      <c r="D14" s="11"/>
-      <c r="E14" s="11"/>
-      <c r="F14" s="11"/>
-      <c r="G14" s="12" t="s">
-        <v>19</v>
+      <c r="C14" s="56"/>
+      <c r="D14" s="0"/>
+      <c r="E14" s="0"/>
+      <c r="F14" s="0"/>
+      <c r="G14" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西暦で入力（例：2026/10/05）。日付として入力してください。</t>
+        </is>
       </c>
       <c r="H14" s="12" t="s">
         <v>19</v>
@@ -1928,19 +1983,21 @@
         <v>19</v>
       </c>
     </row>
-    <row r="15" spans="1:10" ht="26" customHeight="1">
+    <row r="15" spans="1:10" ht="36" customHeight="1">
       <c r="A15" s="10" t="s">
         <v>20</v>
       </c>
       <c r="B15" s="10" t="s">
         <v>20</v>
       </c>
-      <c r="C15" s="11"/>
-      <c r="D15" s="11"/>
-      <c r="E15" s="11"/>
-      <c r="F15" s="11"/>
-      <c r="G15" s="12" t="s">
-        <v>19</v>
+      <c r="C15" s="56"/>
+      <c r="D15" s="0"/>
+      <c r="E15" s="0"/>
+      <c r="F15" s="0"/>
+      <c r="G15" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西暦で入力（例：2026/10/05）。日付として入力してください。</t>
+        </is>
       </c>
       <c r="H15" s="12" t="s">
         <v>19</v>
@@ -1952,17 +2009,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="16" spans="1:10" ht="26" customHeight="1">
+    <row r="16" spans="1:10" ht="36" customHeight="1">
       <c r="A16" s="10" t="s">
         <v>21</v>
       </c>
       <c r="B16" s="10" t="s">
         <v>21</v>
       </c>
-      <c r="C16" s="13"/>
-      <c r="D16" s="13"/>
-      <c r="E16" s="13"/>
-      <c r="F16" s="13"/>
+      <c r="C16" s="57"/>
+      <c r="D16" s="0"/>
+      <c r="E16" s="0"/>
+      <c r="F16" s="0"/>
       <c r="G16" s="12" t="s">
         <v>19</v>
       </c>
@@ -1976,17 +2033,17 @@
         <v>19</v>
       </c>
     </row>
-    <row r="17" spans="1:10" ht="32" customHeight="1">
+    <row r="17" spans="1:10" ht="60" customHeight="1">
       <c r="A17" s="10" t="s">
         <v>22</v>
       </c>
       <c r="B17" s="10" t="s">
         <v>22</v>
       </c>
-      <c r="C17" s="13"/>
-      <c r="D17" s="13"/>
-      <c r="E17" s="13"/>
-      <c r="F17" s="13"/>
+      <c r="C17" s="57"/>
+      <c r="D17" s="0"/>
+      <c r="E17" s="0"/>
+      <c r="F17" s="0"/>
       <c r="G17" s="12" t="s">
         <v>23</v>
       </c>
@@ -2000,19 +2057,23 @@
         <v>23</v>
       </c>
     </row>
-    <row r="18" spans="1:10" ht="44" customHeight="1">
-      <c r="A18" s="10" t="s">
-        <v>24</v>
+    <row r="18" spans="1:10" ht="60" customHeight="1">
+      <c r="A18" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">契約更新の判断基準</t>
+        </is>
       </c>
       <c r="B18" s="10" t="s">
         <v>24</v>
       </c>
-      <c r="C18" s="13"/>
-      <c r="D18" s="13"/>
-      <c r="E18" s="13"/>
-      <c r="F18" s="13"/>
-      <c r="G18" s="12" t="s">
-        <v>25</v>
+      <c r="C18" s="57"/>
+      <c r="D18" s="0"/>
+      <c r="E18" s="0"/>
+      <c r="F18" s="0"/>
+      <c r="G18" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">適用する基準を記入。例：業務量、勤務成績・態度、能力、経営状況、業務の進捗状況。</t>
+        </is>
       </c>
       <c r="H18" s="12" t="s">
         <v>25</v>
@@ -2024,17 +2085,17 @@
         <v>25</v>
       </c>
     </row>
-    <row r="19" spans="1:10" ht="26" customHeight="1">
+    <row r="19" spans="1:10" ht="36" customHeight="1">
       <c r="A19" s="10" t="s">
         <v>26</v>
       </c>
       <c r="B19" s="10" t="s">
         <v>26</v>
       </c>
-      <c r="C19" s="13"/>
-      <c r="D19" s="13"/>
-      <c r="E19" s="13"/>
-      <c r="F19" s="13"/>
+      <c r="C19" s="57"/>
+      <c r="D19" s="0"/>
+      <c r="E19" s="0"/>
+      <c r="F19" s="0"/>
       <c r="G19" s="12" t="s">
         <v>27</v>
       </c>
@@ -2048,17 +2109,17 @@
         <v>27</v>
       </c>
     </row>
-    <row r="20" spans="1:10" ht="26" customHeight="1">
+    <row r="20" spans="1:10" ht="36" customHeight="1">
       <c r="A20" s="10" t="s">
         <v>28</v>
       </c>
       <c r="B20" s="10" t="s">
         <v>28</v>
       </c>
-      <c r="C20" s="14"/>
-      <c r="D20" s="14"/>
-      <c r="E20" s="14"/>
-      <c r="F20" s="14"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="0"/>
+      <c r="E20" s="0"/>
+      <c r="F20" s="0"/>
       <c r="G20" s="12" t="s">
         <v>29</v>
       </c>
@@ -2072,17 +2133,17 @@
         <v>29</v>
       </c>
     </row>
-    <row r="21" spans="1:10" ht="26" customHeight="1">
+    <row r="21" spans="1:10" ht="36" customHeight="1">
       <c r="A21" s="10" t="s">
         <v>30</v>
       </c>
       <c r="B21" s="10" t="s">
         <v>30</v>
       </c>
-      <c r="C21" s="14"/>
-      <c r="D21" s="14"/>
-      <c r="E21" s="14"/>
-      <c r="F21" s="14"/>
+      <c r="C21" s="59"/>
+      <c r="D21" s="0"/>
+      <c r="E21" s="0"/>
+      <c r="F21" s="0"/>
       <c r="G21" s="12" t="s">
         <v>31</v>
       </c>
@@ -2096,19 +2157,21 @@
         <v>31</v>
       </c>
     </row>
-    <row r="22" spans="1:10" ht="26" customHeight="1">
+    <row r="22" spans="1:10" ht="36" customHeight="1">
       <c r="A22" s="10" t="s">
         <v>32</v>
       </c>
       <c r="B22" s="10" t="s">
         <v>32</v>
       </c>
-      <c r="C22" s="11"/>
-      <c r="D22" s="11"/>
-      <c r="E22" s="11"/>
-      <c r="F22" s="11"/>
-      <c r="G22" s="12" t="s">
-        <v>33</v>
+      <c r="C22" s="56"/>
+      <c r="D22" s="0"/>
+      <c r="E22" s="0"/>
+      <c r="F22" s="0"/>
+      <c r="G22" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西暦で入力（例：2026/10/05）。日付として入力してください。</t>
+        </is>
       </c>
       <c r="H22" s="12" t="s">
         <v>33</v>
@@ -2120,17 +2183,17 @@
         <v>33</v>
       </c>
     </row>
-    <row r="23" spans="1:10" ht="26" customHeight="1">
+    <row r="23" spans="1:10" ht="36" customHeight="1">
       <c r="A23" s="10" t="s">
         <v>34</v>
       </c>
       <c r="B23" s="10" t="s">
         <v>34</v>
       </c>
-      <c r="C23" s="13"/>
-      <c r="D23" s="13"/>
-      <c r="E23" s="13"/>
-      <c r="F23" s="13"/>
+      <c r="C23" s="57"/>
+      <c r="D23" s="0"/>
+      <c r="E23" s="0"/>
+      <c r="F23" s="0"/>
       <c r="G23" s="12" t="s">
         <v>35</v>
       </c>
@@ -2144,17 +2207,17 @@
         <v>35</v>
       </c>
     </row>
-    <row r="24" spans="1:10" ht="26" customHeight="1">
+    <row r="24" spans="1:10" ht="36" customHeight="1">
       <c r="A24" s="10" t="s">
         <v>36</v>
       </c>
       <c r="B24" s="10" t="s">
         <v>36</v>
       </c>
-      <c r="C24" s="13"/>
-      <c r="D24" s="13"/>
-      <c r="E24" s="13"/>
-      <c r="F24" s="13"/>
+      <c r="C24" s="57"/>
+      <c r="D24" s="0"/>
+      <c r="E24" s="0"/>
+      <c r="F24" s="0"/>
       <c r="G24" s="12" t="s">
         <v>37</v>
       </c>
@@ -2168,17 +2231,17 @@
         <v>37</v>
       </c>
     </row>
-    <row r="25" spans="1:10" ht="26" customHeight="1">
+    <row r="25" spans="1:10" ht="36" customHeight="1">
       <c r="A25" s="10" t="s">
         <v>38</v>
       </c>
       <c r="B25" s="10" t="s">
         <v>38</v>
       </c>
-      <c r="C25" s="14"/>
-      <c r="D25" s="14"/>
-      <c r="E25" s="14"/>
-      <c r="F25" s="14"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="0"/>
+      <c r="E25" s="0"/>
+      <c r="F25" s="0"/>
       <c r="G25" s="12" t="s">
         <v>39</v>
       </c>
@@ -2224,17 +2287,17 @@
         <v>40</v>
       </c>
     </row>
-    <row r="27" spans="1:10" ht="42" customHeight="1">
+    <row r="27" spans="1:10" ht="72" customHeight="1">
       <c r="A27" s="10" t="s">
         <v>41</v>
       </c>
       <c r="B27" s="10" t="s">
         <v>41</v>
       </c>
-      <c r="C27" s="13"/>
-      <c r="D27" s="13"/>
-      <c r="E27" s="13"/>
-      <c r="F27" s="13"/>
+      <c r="C27" s="57"/>
+      <c r="D27" s="0"/>
+      <c r="E27" s="0"/>
+      <c r="F27" s="0"/>
       <c r="G27" s="12" t="s">
         <v>42</v>
       </c>
@@ -2248,17 +2311,17 @@
         <v>42</v>
       </c>
     </row>
-    <row r="28" spans="1:10" ht="42" customHeight="1">
+    <row r="28" spans="1:10" ht="72" customHeight="1">
       <c r="A28" s="10" t="s">
         <v>43</v>
       </c>
       <c r="B28" s="10" t="s">
         <v>43</v>
       </c>
-      <c r="C28" s="13"/>
-      <c r="D28" s="13"/>
-      <c r="E28" s="13"/>
-      <c r="F28" s="13"/>
+      <c r="C28" s="57"/>
+      <c r="D28" s="0"/>
+      <c r="E28" s="0"/>
+      <c r="F28" s="0"/>
       <c r="G28" s="12" t="s">
         <v>44</v>
       </c>
@@ -2272,17 +2335,17 @@
         <v>44</v>
       </c>
     </row>
-    <row r="29" spans="1:10" ht="50" customHeight="1">
+    <row r="29" spans="1:10" ht="72" customHeight="1">
       <c r="A29" s="10" t="s">
         <v>45</v>
       </c>
       <c r="B29" s="10" t="s">
         <v>45</v>
       </c>
-      <c r="C29" s="13"/>
-      <c r="D29" s="13"/>
-      <c r="E29" s="13"/>
-      <c r="F29" s="13"/>
+      <c r="C29" s="57"/>
+      <c r="D29" s="0"/>
+      <c r="E29" s="0"/>
+      <c r="F29" s="0"/>
       <c r="G29" s="12" t="s">
         <v>46</v>
       </c>
@@ -2296,17 +2359,17 @@
         <v>46</v>
       </c>
     </row>
-    <row r="30" spans="1:10" ht="46" customHeight="1">
+    <row r="30" spans="1:10" ht="72" customHeight="1">
       <c r="A30" s="10" t="s">
         <v>47</v>
       </c>
       <c r="B30" s="10" t="s">
         <v>47</v>
       </c>
-      <c r="C30" s="13"/>
-      <c r="D30" s="13"/>
-      <c r="E30" s="13"/>
-      <c r="F30" s="13"/>
+      <c r="C30" s="57"/>
+      <c r="D30" s="0"/>
+      <c r="E30" s="0"/>
+      <c r="F30" s="0"/>
       <c r="G30" s="12" t="s">
         <v>44</v>
       </c>
@@ -2320,17 +2383,17 @@
         <v>44</v>
       </c>
     </row>
-    <row r="31" spans="1:10" ht="38" customHeight="1">
+    <row r="31" spans="1:10" ht="60" customHeight="1">
       <c r="A31" s="10" t="s">
         <v>48</v>
       </c>
       <c r="B31" s="10" t="s">
         <v>48</v>
       </c>
-      <c r="C31" s="13"/>
-      <c r="D31" s="13"/>
-      <c r="E31" s="13"/>
-      <c r="F31" s="13"/>
+      <c r="C31" s="57"/>
+      <c r="D31" s="0"/>
+      <c r="E31" s="0"/>
+      <c r="F31" s="0"/>
       <c r="G31" s="12" t="s">
         <v>49</v>
       </c>
@@ -2344,19 +2407,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="32" spans="1:10" ht="26" customHeight="1">
+    <row r="32" spans="1:10" ht="36" customHeight="1">
       <c r="A32" s="10" t="s">
         <v>50</v>
       </c>
       <c r="B32" s="10" t="s">
         <v>50</v>
       </c>
-      <c r="C32" s="11"/>
-      <c r="D32" s="11"/>
-      <c r="E32" s="11"/>
-      <c r="F32" s="11"/>
-      <c r="G32" s="12" t="s">
-        <v>49</v>
+      <c r="C32" s="56"/>
+      <c r="D32" s="0"/>
+      <c r="E32" s="0"/>
+      <c r="F32" s="0"/>
+      <c r="G32" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西暦で入力（例：2026/10/05）。日付として入力してください。</t>
+        </is>
       </c>
       <c r="H32" s="12" t="s">
         <v>49</v>
@@ -2368,19 +2433,21 @@
         <v>49</v>
       </c>
     </row>
-    <row r="33" spans="1:10" ht="26" customHeight="1">
+    <row r="33" spans="1:10" ht="36" customHeight="1">
       <c r="A33" s="10" t="s">
         <v>51</v>
       </c>
       <c r="B33" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="C33" s="11"/>
-      <c r="D33" s="11"/>
-      <c r="E33" s="11"/>
-      <c r="F33" s="11"/>
-      <c r="G33" s="12" t="s">
-        <v>49</v>
+      <c r="C33" s="56"/>
+      <c r="D33" s="0"/>
+      <c r="E33" s="0"/>
+      <c r="F33" s="0"/>
+      <c r="G33" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">西暦で入力（例：2026/10/05）。日付として入力してください。</t>
+        </is>
       </c>
       <c r="H33" s="12" t="s">
         <v>49</v>
@@ -2424,17 +2491,17 @@
         <v>52</v>
       </c>
     </row>
-    <row r="35" spans="1:10" ht="26" customHeight="1">
+    <row r="35" spans="1:10" ht="36" customHeight="1">
       <c r="A35" s="10" t="s">
         <v>53</v>
       </c>
       <c r="B35" s="10" t="s">
         <v>53</v>
       </c>
-      <c r="C35" s="13"/>
-      <c r="D35" s="13"/>
-      <c r="E35" s="13"/>
-      <c r="F35" s="13"/>
+      <c r="C35" s="57"/>
+      <c r="D35" s="0"/>
+      <c r="E35" s="0"/>
+      <c r="F35" s="0"/>
       <c r="G35" s="12" t="s">
         <v>54</v>
       </c>
@@ -2448,17 +2515,17 @@
         <v>54</v>
       </c>
     </row>
-    <row r="36" spans="1:10" ht="26" customHeight="1">
+    <row r="36" spans="1:10" ht="36" customHeight="1">
       <c r="A36" s="10" t="s">
         <v>55</v>
       </c>
       <c r="B36" s="10" t="s">
         <v>55</v>
       </c>
-      <c r="C36" s="13"/>
-      <c r="D36" s="13"/>
-      <c r="E36" s="13"/>
-      <c r="F36" s="13"/>
+      <c r="C36" s="57"/>
+      <c r="D36" s="0"/>
+      <c r="E36" s="0"/>
+      <c r="F36" s="0"/>
       <c r="G36" s="12" t="s">
         <v>56</v>
       </c>
@@ -2472,19 +2539,23 @@
         <v>56</v>
       </c>
     </row>
-    <row r="37" spans="1:10" ht="26" customHeight="1">
-      <c r="A37" s="10" t="s">
-        <v>57</v>
+    <row r="37" spans="1:10" ht="36" customHeight="1">
+      <c r="A37" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">適用する制度の名称</t>
+        </is>
       </c>
       <c r="B37" s="10" t="s">
         <v>57</v>
       </c>
-      <c r="C37" s="13"/>
-      <c r="D37" s="13"/>
-      <c r="E37" s="13"/>
-      <c r="F37" s="13"/>
-      <c r="G37" s="12" t="s">
-        <v>58</v>
+      <c r="C37" s="57"/>
+      <c r="D37" s="0"/>
+      <c r="E37" s="0"/>
+      <c r="F37" s="0"/>
+      <c r="G37" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">例：1か月単位の変形労働時間制、交替制。実際に適用する制度名を記入。</t>
+        </is>
       </c>
       <c r="H37" s="12" t="s">
         <v>58</v>
@@ -2496,17 +2567,17 @@
         <v>58</v>
       </c>
     </row>
-    <row r="38" spans="1:10" ht="40" customHeight="1">
+    <row r="38" spans="1:10" ht="60" customHeight="1">
       <c r="A38" s="10" t="s">
         <v>59</v>
       </c>
       <c r="B38" s="10" t="s">
         <v>59</v>
       </c>
-      <c r="C38" s="13"/>
-      <c r="D38" s="13"/>
-      <c r="E38" s="13"/>
-      <c r="F38" s="13"/>
+      <c r="C38" s="57"/>
+      <c r="D38" s="0"/>
+      <c r="E38" s="0"/>
+      <c r="F38" s="0"/>
       <c r="G38" s="12" t="s">
         <v>60</v>
       </c>
@@ -2520,17 +2591,17 @@
         <v>60</v>
       </c>
     </row>
-    <row r="39" spans="1:10" ht="40" customHeight="1">
+    <row r="39" spans="1:10" ht="60" customHeight="1">
       <c r="A39" s="10" t="s">
         <v>61</v>
       </c>
       <c r="B39" s="10" t="s">
         <v>61</v>
       </c>
-      <c r="C39" s="13"/>
-      <c r="D39" s="13"/>
-      <c r="E39" s="13"/>
-      <c r="F39" s="13"/>
+      <c r="C39" s="57"/>
+      <c r="D39" s="0"/>
+      <c r="E39" s="0"/>
+      <c r="F39" s="0"/>
       <c r="G39" s="12" t="s">
         <v>62</v>
       </c>
@@ -2544,17 +2615,17 @@
         <v>62</v>
       </c>
     </row>
-    <row r="40" spans="1:10" ht="40" customHeight="1">
+    <row r="40" spans="1:10" ht="60" customHeight="1">
       <c r="A40" s="10" t="s">
         <v>63</v>
       </c>
       <c r="B40" s="10" t="s">
         <v>63</v>
       </c>
-      <c r="C40" s="13"/>
-      <c r="D40" s="13"/>
-      <c r="E40" s="13"/>
-      <c r="F40" s="13"/>
+      <c r="C40" s="57"/>
+      <c r="D40" s="0"/>
+      <c r="E40" s="0"/>
+      <c r="F40" s="0"/>
       <c r="G40" s="12" t="s">
         <v>62</v>
       </c>
@@ -2568,17 +2639,17 @@
         <v>62</v>
       </c>
     </row>
-    <row r="41" spans="1:10" ht="46" customHeight="1">
+    <row r="41" spans="1:10" ht="60" customHeight="1">
       <c r="A41" s="10" t="s">
         <v>64</v>
       </c>
       <c r="B41" s="10" t="s">
         <v>64</v>
       </c>
-      <c r="C41" s="13"/>
-      <c r="D41" s="13"/>
-      <c r="E41" s="13"/>
-      <c r="F41" s="13"/>
+      <c r="C41" s="57"/>
+      <c r="D41" s="0"/>
+      <c r="E41" s="0"/>
+      <c r="F41" s="0"/>
       <c r="G41" s="12" t="s">
         <v>65</v>
       </c>
@@ -2592,17 +2663,17 @@
         <v>65</v>
       </c>
     </row>
-    <row r="42" spans="1:10" ht="32" customHeight="1">
+    <row r="42" spans="1:10" ht="36" customHeight="1">
       <c r="A42" s="10" t="s">
         <v>66</v>
       </c>
       <c r="B42" s="10" t="s">
         <v>66</v>
       </c>
-      <c r="C42" s="13"/>
-      <c r="D42" s="13"/>
-      <c r="E42" s="13"/>
-      <c r="F42" s="13"/>
+      <c r="C42" s="57"/>
+      <c r="D42" s="0"/>
+      <c r="E42" s="0"/>
+      <c r="F42" s="0"/>
       <c r="G42" s="12" t="s">
         <v>67</v>
       </c>
@@ -2616,17 +2687,17 @@
         <v>67</v>
       </c>
     </row>
-    <row r="43" spans="1:10" ht="40" customHeight="1">
+    <row r="43" spans="1:10" ht="60" customHeight="1">
       <c r="A43" s="10" t="s">
         <v>68</v>
       </c>
       <c r="B43" s="10" t="s">
         <v>68</v>
       </c>
-      <c r="C43" s="13"/>
-      <c r="D43" s="13"/>
-      <c r="E43" s="13"/>
-      <c r="F43" s="13"/>
+      <c r="C43" s="57"/>
+      <c r="D43" s="0"/>
+      <c r="E43" s="0"/>
+      <c r="F43" s="0"/>
       <c r="G43" s="12" t="s">
         <v>69</v>
       </c>
@@ -2640,17 +2711,17 @@
         <v>69</v>
       </c>
     </row>
-    <row r="44" spans="1:10" ht="40" customHeight="1">
+    <row r="44" spans="1:10" ht="60" customHeight="1">
       <c r="A44" s="10" t="s">
         <v>70</v>
       </c>
       <c r="B44" s="10" t="s">
         <v>70</v>
       </c>
-      <c r="C44" s="13"/>
-      <c r="D44" s="13"/>
-      <c r="E44" s="13"/>
-      <c r="F44" s="13"/>
+      <c r="C44" s="57"/>
+      <c r="D44" s="0"/>
+      <c r="E44" s="0"/>
+      <c r="F44" s="0"/>
       <c r="G44" s="12" t="s">
         <v>69</v>
       </c>
@@ -2664,17 +2735,17 @@
         <v>69</v>
       </c>
     </row>
-    <row r="45" spans="1:10" ht="38" customHeight="1">
+    <row r="45" spans="1:10" ht="36" customHeight="1">
       <c r="A45" s="10" t="s">
         <v>71</v>
       </c>
       <c r="B45" s="10" t="s">
         <v>71</v>
       </c>
-      <c r="C45" s="13"/>
-      <c r="D45" s="13"/>
-      <c r="E45" s="13"/>
-      <c r="F45" s="13"/>
+      <c r="C45" s="57"/>
+      <c r="D45" s="0"/>
+      <c r="E45" s="0"/>
+      <c r="F45" s="0"/>
       <c r="G45" s="12" t="s">
         <v>72</v>
       </c>
@@ -2688,17 +2759,17 @@
         <v>72</v>
       </c>
     </row>
-    <row r="46" spans="1:10" ht="26" customHeight="1">
+    <row r="46" spans="1:10" ht="36" customHeight="1">
       <c r="A46" s="10" t="s">
         <v>73</v>
       </c>
       <c r="B46" s="10" t="s">
         <v>73</v>
       </c>
-      <c r="C46" s="14"/>
-      <c r="D46" s="14"/>
-      <c r="E46" s="14"/>
-      <c r="F46" s="14"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="0"/>
+      <c r="E46" s="0"/>
+      <c r="F46" s="0"/>
       <c r="G46" s="12" t="s">
         <v>74</v>
       </c>
@@ -2712,17 +2783,17 @@
         <v>74</v>
       </c>
     </row>
-    <row r="47" spans="1:10" ht="26" customHeight="1">
+    <row r="47" spans="1:10" ht="36" customHeight="1">
       <c r="A47" s="10" t="s">
         <v>75</v>
       </c>
       <c r="B47" s="10" t="s">
         <v>75</v>
       </c>
-      <c r="C47" s="13"/>
-      <c r="D47" s="13"/>
-      <c r="E47" s="13"/>
-      <c r="F47" s="13"/>
+      <c r="C47" s="57"/>
+      <c r="D47" s="0"/>
+      <c r="E47" s="0"/>
+      <c r="F47" s="0"/>
       <c r="G47" s="12" t="s">
         <v>76</v>
       </c>
@@ -2736,17 +2807,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="48" spans="1:10" ht="26" customHeight="1">
+    <row r="48" spans="1:10" ht="36" customHeight="1">
       <c r="A48" s="10" t="s">
         <v>77</v>
       </c>
       <c r="B48" s="10" t="s">
         <v>77</v>
       </c>
-      <c r="C48" s="13"/>
-      <c r="D48" s="13"/>
-      <c r="E48" s="13"/>
-      <c r="F48" s="13"/>
+      <c r="C48" s="57"/>
+      <c r="D48" s="0"/>
+      <c r="E48" s="0"/>
+      <c r="F48" s="0"/>
       <c r="G48" s="12" t="s">
         <v>78</v>
       </c>
@@ -2760,19 +2831,23 @@
         <v>78</v>
       </c>
     </row>
-    <row r="49" spans="1:10" ht="26" customHeight="1">
-      <c r="A49" s="10" t="s">
-        <v>79</v>
+    <row r="49" spans="1:10" ht="36" customHeight="1">
+      <c r="A49" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所定時間外労働・1週の時間数</t>
+        </is>
       </c>
       <c r="B49" s="10" t="s">
         <v>79</v>
       </c>
-      <c r="C49" s="13"/>
-      <c r="D49" s="13"/>
-      <c r="E49" s="13"/>
-      <c r="F49" s="13"/>
-      <c r="G49" s="12" t="s">
-        <v>80</v>
+      <c r="C49" s="60"/>
+      <c r="D49" s="0"/>
+      <c r="E49" s="0"/>
+      <c r="F49" s="0"/>
+      <c r="G49" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">短時間用。所定時間外労働が有の場合。時間数を数値で入力。</t>
+        </is>
       </c>
       <c r="H49" s="12" t="s">
         <v>80</v>
@@ -2784,19 +2859,23 @@
         <v>80</v>
       </c>
     </row>
-    <row r="50" spans="1:10" ht="26" customHeight="1">
-      <c r="A50" s="10" t="s">
-        <v>81</v>
+    <row r="50" spans="1:10" ht="36" customHeight="1">
+      <c r="A50" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所定時間外労働・1か月の時間数</t>
+        </is>
       </c>
       <c r="B50" s="10" t="s">
         <v>81</v>
       </c>
-      <c r="C50" s="13"/>
-      <c r="D50" s="13"/>
-      <c r="E50" s="13"/>
-      <c r="F50" s="13"/>
-      <c r="G50" s="12" t="s">
-        <v>82</v>
+      <c r="C50" s="60"/>
+      <c r="D50" s="0"/>
+      <c r="E50" s="0"/>
+      <c r="F50" s="0"/>
+      <c r="G50" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">短時間用。所定時間外労働が有の場合。時間数を数値で入力。</t>
+        </is>
       </c>
       <c r="H50" s="12" t="s">
         <v>82</v>
@@ -2808,19 +2887,23 @@
         <v>82</v>
       </c>
     </row>
-    <row r="51" spans="1:10" ht="26" customHeight="1">
-      <c r="A51" s="10" t="s">
-        <v>83</v>
+    <row r="51" spans="1:10" ht="36" customHeight="1">
+      <c r="A51" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">所定時間外労働・1年の時間数</t>
+        </is>
       </c>
       <c r="B51" s="10" t="s">
         <v>83</v>
       </c>
-      <c r="C51" s="13"/>
-      <c r="D51" s="13"/>
-      <c r="E51" s="13"/>
-      <c r="F51" s="13"/>
-      <c r="G51" s="12" t="s">
-        <v>84</v>
+      <c r="C51" s="60"/>
+      <c r="D51" s="0"/>
+      <c r="E51" s="0"/>
+      <c r="F51" s="0"/>
+      <c r="G51" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">短時間用。所定時間外労働が有の場合。時間数を数値で入力。</t>
+        </is>
       </c>
       <c r="H51" s="12" t="s">
         <v>84</v>
@@ -2864,19 +2947,23 @@
         <v>85</v>
       </c>
     </row>
-    <row r="53" spans="1:10" ht="26" customHeight="1">
-      <c r="A53" s="10" t="s">
-        <v>86</v>
+    <row r="53" spans="1:10" ht="36" customHeight="1">
+      <c r="A53" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定例休日（曜日・祝日等）</t>
+        </is>
       </c>
       <c r="B53" s="10" t="s">
         <v>86</v>
       </c>
-      <c r="C53" s="13"/>
-      <c r="D53" s="13"/>
-      <c r="E53" s="13"/>
-      <c r="F53" s="13"/>
-      <c r="G53" s="12" t="s">
-        <v>87</v>
+      <c r="C53" s="57"/>
+      <c r="D53" s="0"/>
+      <c r="E53" s="0"/>
+      <c r="F53" s="0"/>
+      <c r="G53" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">毎週土・日、国民の祝日など、実際に休日とする日を記入。</t>
+        </is>
       </c>
       <c r="H53" s="12" t="s">
         <v>87</v>
@@ -2888,19 +2975,23 @@
         <v>87</v>
       </c>
     </row>
-    <row r="54" spans="1:10" ht="40" customHeight="1">
-      <c r="A54" s="10" t="s">
-        <v>88</v>
+    <row r="54" spans="1:10" ht="60" customHeight="1">
+      <c r="A54" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定例休日・その他</t>
+        </is>
       </c>
       <c r="B54" s="10" t="s">
         <v>88</v>
       </c>
-      <c r="C54" s="13"/>
-      <c r="D54" s="13"/>
-      <c r="E54" s="13"/>
-      <c r="F54" s="13"/>
-      <c r="G54" s="12" t="s">
-        <v>89</v>
+      <c r="C54" s="57"/>
+      <c r="D54" s="0"/>
+      <c r="E54" s="0"/>
+      <c r="F54" s="0"/>
+      <c r="G54" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">定例休日の補足（例：年末年始）</t>
+        </is>
       </c>
       <c r="H54" s="12" t="s">
         <v>89</v>
@@ -2912,17 +3003,17 @@
         <v>89</v>
       </c>
     </row>
-    <row r="55" spans="1:10" ht="40" customHeight="1">
+    <row r="55" spans="1:10" ht="60" customHeight="1">
       <c r="A55" s="10" t="s">
         <v>90</v>
       </c>
       <c r="B55" s="10" t="s">
         <v>90</v>
       </c>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="13"/>
-      <c r="F55" s="13"/>
+      <c r="C55" s="57"/>
+      <c r="D55" s="0"/>
+      <c r="E55" s="0"/>
+      <c r="F55" s="0"/>
       <c r="G55" s="12" t="s">
         <v>91</v>
       </c>
@@ -2936,17 +3027,17 @@
         <v>91</v>
       </c>
     </row>
-    <row r="56" spans="1:10" ht="26" customHeight="1">
+    <row r="56" spans="1:10" ht="36" customHeight="1">
       <c r="A56" s="10" t="s">
         <v>92</v>
       </c>
       <c r="B56" s="10" t="s">
         <v>92</v>
       </c>
-      <c r="C56" s="14"/>
-      <c r="D56" s="14"/>
-      <c r="E56" s="14"/>
-      <c r="F56" s="14"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="0"/>
+      <c r="E56" s="0"/>
+      <c r="F56" s="0"/>
       <c r="G56" s="12" t="s">
         <v>93</v>
       </c>
@@ -2967,10 +3058,10 @@
       <c r="B57" s="10" t="s">
         <v>94</v>
       </c>
-      <c r="C57" s="13"/>
-      <c r="D57" s="13"/>
-      <c r="E57" s="13"/>
-      <c r="F57" s="13"/>
+      <c r="C57" s="57"/>
+      <c r="D57" s="0"/>
+      <c r="E57" s="0"/>
+      <c r="F57" s="0"/>
       <c r="G57" s="12" t="s">
         <v>95</v>
       </c>
@@ -2984,17 +3075,17 @@
         <v>95</v>
       </c>
     </row>
-    <row r="58" spans="1:10" ht="36" customHeight="1">
+    <row r="58" spans="1:10" ht="60" customHeight="1">
       <c r="A58" s="10" t="s">
         <v>96</v>
       </c>
       <c r="B58" s="10" t="s">
         <v>96</v>
       </c>
-      <c r="C58" s="13"/>
-      <c r="D58" s="13"/>
-      <c r="E58" s="13"/>
-      <c r="F58" s="13"/>
+      <c r="C58" s="57"/>
+      <c r="D58" s="0"/>
+      <c r="E58" s="0"/>
+      <c r="F58" s="0"/>
       <c r="G58" s="12" t="s">
         <v>97</v>
       </c>
@@ -3008,17 +3099,17 @@
         <v>97</v>
       </c>
     </row>
-    <row r="59" spans="1:10" ht="38" customHeight="1">
+    <row r="59" spans="1:10" ht="36" customHeight="1">
       <c r="A59" s="10" t="s">
         <v>98</v>
       </c>
       <c r="B59" s="10" t="s">
         <v>98</v>
       </c>
-      <c r="C59" s="13"/>
-      <c r="D59" s="13"/>
-      <c r="E59" s="13"/>
-      <c r="F59" s="13"/>
+      <c r="C59" s="57"/>
+      <c r="D59" s="0"/>
+      <c r="E59" s="0"/>
+      <c r="F59" s="0"/>
       <c r="G59" s="12" t="s">
         <v>72</v>
       </c>
@@ -3032,17 +3123,17 @@
         <v>72</v>
       </c>
     </row>
-    <row r="60" spans="1:10" ht="26" customHeight="1">
+    <row r="60" spans="1:10" ht="36" customHeight="1">
       <c r="A60" s="10" t="s">
         <v>99</v>
       </c>
       <c r="B60" s="10" t="s">
         <v>99</v>
       </c>
-      <c r="C60" s="14"/>
-      <c r="D60" s="14"/>
-      <c r="E60" s="14"/>
-      <c r="F60" s="14"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="0"/>
+      <c r="E60" s="0"/>
+      <c r="F60" s="0"/>
       <c r="G60" s="12" t="s">
         <v>100</v>
       </c>
@@ -3056,17 +3147,17 @@
         <v>100</v>
       </c>
     </row>
-    <row r="61" spans="1:10" ht="26" customHeight="1">
+    <row r="61" spans="1:10" ht="36" customHeight="1">
       <c r="A61" s="10" t="s">
         <v>101</v>
       </c>
       <c r="B61" s="10" t="s">
         <v>101</v>
       </c>
-      <c r="C61" s="13"/>
-      <c r="D61" s="13"/>
-      <c r="E61" s="13"/>
-      <c r="F61" s="13"/>
+      <c r="C61" s="57"/>
+      <c r="D61" s="0"/>
+      <c r="E61" s="0"/>
+      <c r="F61" s="0"/>
       <c r="G61" s="12" t="s">
         <v>76</v>
       </c>
@@ -3080,17 +3171,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="62" spans="1:10" ht="26" customHeight="1">
+    <row r="62" spans="1:10" ht="36" customHeight="1">
       <c r="A62" s="10" t="s">
         <v>102</v>
       </c>
       <c r="B62" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="C62" s="14"/>
-      <c r="D62" s="14"/>
-      <c r="E62" s="14"/>
-      <c r="F62" s="14"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="0"/>
+      <c r="E62" s="0"/>
+      <c r="F62" s="0"/>
       <c r="G62" s="12" t="s">
         <v>103</v>
       </c>
@@ -3104,17 +3195,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="63" spans="1:10" ht="26" customHeight="1">
+    <row r="63" spans="1:10" ht="36" customHeight="1">
       <c r="A63" s="10" t="s">
         <v>104</v>
       </c>
       <c r="B63" s="10" t="s">
         <v>104</v>
       </c>
-      <c r="C63" s="14"/>
-      <c r="D63" s="14"/>
-      <c r="E63" s="14"/>
-      <c r="F63" s="14"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="0"/>
+      <c r="E63" s="0"/>
+      <c r="F63" s="0"/>
       <c r="G63" s="12" t="s">
         <v>103</v>
       </c>
@@ -3128,17 +3219,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="64" spans="1:10" ht="26" customHeight="1">
+    <row r="64" spans="1:10" ht="36" customHeight="1">
       <c r="A64" s="10" t="s">
         <v>105</v>
       </c>
       <c r="B64" s="10" t="s">
         <v>105</v>
       </c>
-      <c r="C64" s="13"/>
-      <c r="D64" s="13"/>
-      <c r="E64" s="13"/>
-      <c r="F64" s="13"/>
+      <c r="C64" s="57"/>
+      <c r="D64" s="0"/>
+      <c r="E64" s="0"/>
+      <c r="F64" s="0"/>
       <c r="G64" s="12" t="s">
         <v>76</v>
       </c>
@@ -3152,17 +3243,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="65" spans="1:10" ht="26" customHeight="1">
+    <row r="65" spans="1:10" ht="36" customHeight="1">
       <c r="A65" s="10" t="s">
         <v>106</v>
       </c>
       <c r="B65" s="10" t="s">
         <v>106</v>
       </c>
-      <c r="C65" s="13"/>
-      <c r="D65" s="13"/>
-      <c r="E65" s="13"/>
-      <c r="F65" s="13"/>
+      <c r="C65" s="57"/>
+      <c r="D65" s="0"/>
+      <c r="E65" s="0"/>
+      <c r="F65" s="0"/>
       <c r="G65" s="12" t="s">
         <v>76</v>
       </c>
@@ -3176,17 +3267,17 @@
         <v>76</v>
       </c>
     </row>
-    <row r="66" spans="1:10" ht="44" customHeight="1">
+    <row r="66" spans="1:10" ht="60" customHeight="1">
       <c r="A66" s="10" t="s">
         <v>107</v>
       </c>
       <c r="B66" s="10" t="s">
         <v>107</v>
       </c>
-      <c r="C66" s="13"/>
-      <c r="D66" s="13"/>
-      <c r="E66" s="13"/>
-      <c r="F66" s="13"/>
+      <c r="C66" s="57"/>
+      <c r="D66" s="0"/>
+      <c r="E66" s="0"/>
+      <c r="F66" s="0"/>
       <c r="G66" s="12" t="s">
         <v>108</v>
       </c>
@@ -3200,17 +3291,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="67" spans="1:10" ht="44" customHeight="1">
+    <row r="67" spans="1:10" ht="60" customHeight="1">
       <c r="A67" s="10" t="s">
         <v>109</v>
       </c>
       <c r="B67" s="10" t="s">
         <v>109</v>
       </c>
-      <c r="C67" s="13"/>
-      <c r="D67" s="13"/>
-      <c r="E67" s="13"/>
-      <c r="F67" s="13"/>
+      <c r="C67" s="57"/>
+      <c r="D67" s="0"/>
+      <c r="E67" s="0"/>
+      <c r="F67" s="0"/>
       <c r="G67" s="12" t="s">
         <v>108</v>
       </c>
@@ -3224,17 +3315,17 @@
         <v>108</v>
       </c>
     </row>
-    <row r="68" spans="1:10" ht="40" customHeight="1">
+    <row r="68" spans="1:10" ht="36" customHeight="1">
       <c r="A68" s="10" t="s">
         <v>110</v>
       </c>
       <c r="B68" s="10" t="s">
         <v>110</v>
       </c>
-      <c r="C68" s="13"/>
-      <c r="D68" s="13"/>
-      <c r="E68" s="13"/>
-      <c r="F68" s="13"/>
+      <c r="C68" s="57"/>
+      <c r="D68" s="0"/>
+      <c r="E68" s="0"/>
+      <c r="F68" s="0"/>
       <c r="G68" s="12" t="s">
         <v>72</v>
       </c>
@@ -3280,17 +3371,17 @@
         <v>111</v>
       </c>
     </row>
-    <row r="70" spans="1:10" ht="26" customHeight="1">
+    <row r="70" spans="1:10" ht="36" customHeight="1">
       <c r="A70" s="10" t="s">
         <v>112</v>
       </c>
       <c r="B70" s="10" t="s">
         <v>112</v>
       </c>
-      <c r="C70" s="15"/>
-      <c r="D70" s="15"/>
-      <c r="E70" s="15"/>
-      <c r="F70" s="15"/>
+      <c r="C70" s="61"/>
+      <c r="D70" s="0"/>
+      <c r="E70" s="0"/>
+      <c r="F70" s="0"/>
       <c r="G70" s="12" t="s">
         <v>103</v>
       </c>
@@ -3304,17 +3395,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="71" spans="1:10" ht="26" customHeight="1">
+    <row r="71" spans="1:10" ht="36" customHeight="1">
       <c r="A71" s="10" t="s">
         <v>113</v>
       </c>
       <c r="B71" s="10" t="s">
         <v>113</v>
       </c>
-      <c r="C71" s="15"/>
-      <c r="D71" s="15"/>
-      <c r="E71" s="15"/>
-      <c r="F71" s="15"/>
+      <c r="C71" s="61"/>
+      <c r="D71" s="0"/>
+      <c r="E71" s="0"/>
+      <c r="F71" s="0"/>
       <c r="G71" s="12" t="s">
         <v>103</v>
       </c>
@@ -3328,17 +3419,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="72" spans="1:10" ht="26" customHeight="1">
+    <row r="72" spans="1:10" ht="36" customHeight="1">
       <c r="A72" s="10" t="s">
         <v>114</v>
       </c>
       <c r="B72" s="10" t="s">
         <v>114</v>
       </c>
-      <c r="C72" s="15"/>
-      <c r="D72" s="15"/>
-      <c r="E72" s="15"/>
-      <c r="F72" s="15"/>
+      <c r="C72" s="61"/>
+      <c r="D72" s="0"/>
+      <c r="E72" s="0"/>
+      <c r="F72" s="0"/>
       <c r="G72" s="12" t="s">
         <v>103</v>
       </c>
@@ -3352,17 +3443,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="73" spans="1:10" ht="26" customHeight="1">
+    <row r="73" spans="1:10" ht="36" customHeight="1">
       <c r="A73" s="10" t="s">
         <v>115</v>
       </c>
       <c r="B73" s="10" t="s">
         <v>115</v>
       </c>
-      <c r="C73" s="15"/>
-      <c r="D73" s="15"/>
-      <c r="E73" s="15"/>
-      <c r="F73" s="15"/>
+      <c r="C73" s="61"/>
+      <c r="D73" s="0"/>
+      <c r="E73" s="0"/>
+      <c r="F73" s="0"/>
       <c r="G73" s="12" t="s">
         <v>103</v>
       </c>
@@ -3376,17 +3467,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="74" spans="1:10" ht="26" customHeight="1">
+    <row r="74" spans="1:10" ht="36" customHeight="1">
       <c r="A74" s="10" t="s">
         <v>116</v>
       </c>
       <c r="B74" s="10" t="s">
         <v>116</v>
       </c>
-      <c r="C74" s="15"/>
-      <c r="D74" s="15"/>
-      <c r="E74" s="15"/>
-      <c r="F74" s="15"/>
+      <c r="C74" s="61"/>
+      <c r="D74" s="0"/>
+      <c r="E74" s="0"/>
+      <c r="F74" s="0"/>
       <c r="G74" s="12" t="s">
         <v>103</v>
       </c>
@@ -3400,17 +3491,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="75" spans="1:10" ht="26" customHeight="1">
+    <row r="75" spans="1:10" ht="36" customHeight="1">
       <c r="A75" s="10" t="s">
         <v>117</v>
       </c>
       <c r="B75" s="10" t="s">
         <v>117</v>
       </c>
-      <c r="C75" s="15"/>
-      <c r="D75" s="15"/>
-      <c r="E75" s="15"/>
-      <c r="F75" s="15"/>
+      <c r="C75" s="61"/>
+      <c r="D75" s="0"/>
+      <c r="E75" s="0"/>
+      <c r="F75" s="0"/>
       <c r="G75" s="12" t="s">
         <v>103</v>
       </c>
@@ -3424,17 +3515,17 @@
         <v>103</v>
       </c>
     </row>
-    <row r="76" spans="1:10" ht="32" customHeight="1">
+    <row r="76" spans="1:10" ht="60" customHeight="1">
       <c r="A76" s="10" t="s">
         <v>118</v>
       </c>
       <c r="B76" s="10" t="s">
         <v>118</v>
       </c>
-      <c r="C76" s="13"/>
-      <c r="D76" s="13"/>
-      <c r="E76" s="13"/>
-      <c r="F76" s="13"/>
+      <c r="C76" s="57"/>
+      <c r="D76" s="0"/>
+      <c r="E76" s="0"/>
+      <c r="F76" s="0"/>
       <c r="G76" s="12" t="s">
         <v>119</v>
       </c>
@@ -3448,17 +3539,17 @@
         <v>119</v>
       </c>
     </row>
-    <row r="77" spans="1:10" ht="42" customHeight="1">
+    <row r="77" spans="1:10" ht="60" customHeight="1">
       <c r="A77" s="10" t="s">
         <v>120</v>
       </c>
       <c r="B77" s="10" t="s">
         <v>120</v>
       </c>
-      <c r="C77" s="13"/>
-      <c r="D77" s="13"/>
-      <c r="E77" s="13"/>
-      <c r="F77" s="13"/>
+      <c r="C77" s="57"/>
+      <c r="D77" s="0"/>
+      <c r="E77" s="0"/>
+      <c r="F77" s="0"/>
       <c r="G77" s="12" t="s">
         <v>121</v>
       </c>
@@ -3472,17 +3563,17 @@
         <v>121</v>
       </c>
     </row>
-    <row r="78" spans="1:10" ht="42" customHeight="1">
+    <row r="78" spans="1:10" ht="60" customHeight="1">
       <c r="A78" s="10" t="s">
         <v>122</v>
       </c>
       <c r="B78" s="10" t="s">
         <v>122</v>
       </c>
-      <c r="C78" s="13"/>
-      <c r="D78" s="13"/>
-      <c r="E78" s="13"/>
-      <c r="F78" s="13"/>
+      <c r="C78" s="57"/>
+      <c r="D78" s="0"/>
+      <c r="E78" s="0"/>
+      <c r="F78" s="0"/>
       <c r="G78" s="12" t="s">
         <v>121</v>
       </c>
@@ -3496,17 +3587,17 @@
         <v>121</v>
       </c>
     </row>
-    <row r="79" spans="1:10" ht="42" customHeight="1">
+    <row r="79" spans="1:10" ht="60" customHeight="1">
       <c r="A79" s="10" t="s">
         <v>123</v>
       </c>
       <c r="B79" s="10" t="s">
         <v>123</v>
       </c>
-      <c r="C79" s="13"/>
-      <c r="D79" s="13"/>
-      <c r="E79" s="13"/>
-      <c r="F79" s="13"/>
+      <c r="C79" s="57"/>
+      <c r="D79" s="0"/>
+      <c r="E79" s="0"/>
+      <c r="F79" s="0"/>
       <c r="G79" s="12" t="s">
         <v>121</v>
       </c>
@@ -3520,17 +3611,17 @@
         <v>121</v>
       </c>
     </row>
-    <row r="80" spans="1:10" ht="42" customHeight="1">
+    <row r="80" spans="1:10" ht="60" customHeight="1">
       <c r="A80" s="10" t="s">
         <v>124</v>
       </c>
       <c r="B80" s="10" t="s">
         <v>124</v>
       </c>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="13"/>
-      <c r="F80" s="13"/>
+      <c r="C80" s="57"/>
+      <c r="D80" s="0"/>
+      <c r="E80" s="0"/>
+      <c r="F80" s="0"/>
       <c r="G80" s="12" t="s">
         <v>121</v>
       </c>
@@ -3544,17 +3635,17 @@
         <v>121</v>
       </c>
     </row>
-    <row r="81" spans="1:10" ht="26" customHeight="1">
+    <row r="81" spans="1:10" ht="36" customHeight="1">
       <c r="A81" s="10" t="s">
         <v>125</v>
       </c>
       <c r="B81" s="10" t="s">
         <v>125</v>
       </c>
-      <c r="C81" s="16"/>
-      <c r="D81" s="16"/>
-      <c r="E81" s="16"/>
-      <c r="F81" s="16"/>
+      <c r="C81" s="62"/>
+      <c r="D81" s="0"/>
+      <c r="E81" s="0"/>
+      <c r="F81" s="0"/>
       <c r="G81" s="12" t="s">
         <v>126</v>
       </c>
@@ -3568,17 +3659,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="82" spans="1:10" ht="26" customHeight="1">
+    <row r="82" spans="1:10" ht="36" customHeight="1">
       <c r="A82" s="10" t="s">
         <v>127</v>
       </c>
       <c r="B82" s="10" t="s">
         <v>127</v>
       </c>
-      <c r="C82" s="16"/>
-      <c r="D82" s="16"/>
-      <c r="E82" s="16"/>
-      <c r="F82" s="16"/>
+      <c r="C82" s="62"/>
+      <c r="D82" s="0"/>
+      <c r="E82" s="0"/>
+      <c r="F82" s="0"/>
       <c r="G82" s="12" t="s">
         <v>126</v>
       </c>
@@ -3592,17 +3683,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="83" spans="1:10" ht="26" customHeight="1">
+    <row r="83" spans="1:10" ht="36" customHeight="1">
       <c r="A83" s="10" t="s">
         <v>128</v>
       </c>
       <c r="B83" s="10" t="s">
         <v>128</v>
       </c>
-      <c r="C83" s="16"/>
-      <c r="D83" s="16"/>
-      <c r="E83" s="16"/>
-      <c r="F83" s="16"/>
+      <c r="C83" s="62"/>
+      <c r="D83" s="0"/>
+      <c r="E83" s="0"/>
+      <c r="F83" s="0"/>
       <c r="G83" s="12" t="s">
         <v>126</v>
       </c>
@@ -3616,17 +3707,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="84" spans="1:10" ht="26" customHeight="1">
+    <row r="84" spans="1:10" ht="36" customHeight="1">
       <c r="A84" s="10" t="s">
         <v>129</v>
       </c>
       <c r="B84" s="10" t="s">
         <v>129</v>
       </c>
-      <c r="C84" s="16"/>
-      <c r="D84" s="16"/>
-      <c r="E84" s="16"/>
-      <c r="F84" s="16"/>
+      <c r="C84" s="62"/>
+      <c r="D84" s="0"/>
+      <c r="E84" s="0"/>
+      <c r="F84" s="0"/>
       <c r="G84" s="12" t="s">
         <v>126</v>
       </c>
@@ -3640,17 +3731,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="85" spans="1:10" ht="26" customHeight="1">
+    <row r="85" spans="1:10" ht="36" customHeight="1">
       <c r="A85" s="10" t="s">
         <v>130</v>
       </c>
       <c r="B85" s="10" t="s">
         <v>130</v>
       </c>
-      <c r="C85" s="16"/>
-      <c r="D85" s="16"/>
-      <c r="E85" s="16"/>
-      <c r="F85" s="16"/>
+      <c r="C85" s="62"/>
+      <c r="D85" s="0"/>
+      <c r="E85" s="0"/>
+      <c r="F85" s="0"/>
       <c r="G85" s="12" t="s">
         <v>126</v>
       </c>
@@ -3664,17 +3755,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="86" spans="1:10" ht="26" customHeight="1">
+    <row r="86" spans="1:10" ht="36" customHeight="1">
       <c r="A86" s="10" t="s">
         <v>131</v>
       </c>
       <c r="B86" s="10" t="s">
         <v>131</v>
       </c>
-      <c r="C86" s="16"/>
-      <c r="D86" s="16"/>
-      <c r="E86" s="16"/>
-      <c r="F86" s="16"/>
+      <c r="C86" s="62"/>
+      <c r="D86" s="0"/>
+      <c r="E86" s="0"/>
+      <c r="F86" s="0"/>
       <c r="G86" s="12" t="s">
         <v>126</v>
       </c>
@@ -3688,17 +3779,17 @@
         <v>126</v>
       </c>
     </row>
-    <row r="87" spans="1:10" ht="26" customHeight="1">
+    <row r="87" spans="1:10" ht="36" customHeight="1">
       <c r="A87" s="10" t="s">
         <v>132</v>
       </c>
       <c r="B87" s="10" t="s">
         <v>132</v>
       </c>
-      <c r="C87" s="13"/>
-      <c r="D87" s="13"/>
-      <c r="E87" s="13"/>
-      <c r="F87" s="13"/>
+      <c r="C87" s="57"/>
+      <c r="D87" s="0"/>
+      <c r="E87" s="0"/>
+      <c r="F87" s="0"/>
       <c r="G87" s="12" t="s">
         <v>133</v>
       </c>
@@ -3712,17 +3803,17 @@
         <v>133</v>
       </c>
     </row>
-    <row r="88" spans="1:10" ht="26" customHeight="1">
+    <row r="88" spans="1:10" ht="60" customHeight="1">
       <c r="A88" s="10" t="s">
         <v>134</v>
       </c>
       <c r="B88" s="10" t="s">
         <v>134</v>
       </c>
-      <c r="C88" s="13"/>
-      <c r="D88" s="13"/>
-      <c r="E88" s="13"/>
-      <c r="F88" s="13"/>
+      <c r="C88" s="57"/>
+      <c r="D88" s="0"/>
+      <c r="E88" s="0"/>
+      <c r="F88" s="0"/>
       <c r="G88" s="12" t="s">
         <v>135</v>
       </c>
@@ -3736,17 +3827,17 @@
         <v>135</v>
       </c>
     </row>
-    <row r="89" spans="1:10" ht="42" customHeight="1">
+    <row r="89" spans="1:10" ht="60" customHeight="1">
       <c r="A89" s="10" t="s">
         <v>136</v>
       </c>
       <c r="B89" s="10" t="s">
         <v>136</v>
       </c>
-      <c r="C89" s="13"/>
-      <c r="D89" s="13"/>
-      <c r="E89" s="13"/>
-      <c r="F89" s="13"/>
+      <c r="C89" s="57"/>
+      <c r="D89" s="0"/>
+      <c r="E89" s="0"/>
+      <c r="F89" s="0"/>
       <c r="G89" s="12" t="s">
         <v>137</v>
       </c>
@@ -3760,17 +3851,17 @@
         <v>137</v>
       </c>
     </row>
-    <row r="90" spans="1:10" ht="44" customHeight="1">
+    <row r="90" spans="1:10" ht="36" customHeight="1">
       <c r="A90" s="10" t="s">
         <v>138</v>
       </c>
       <c r="B90" s="10" t="s">
         <v>138</v>
       </c>
-      <c r="C90" s="13"/>
-      <c r="D90" s="13"/>
-      <c r="E90" s="13"/>
-      <c r="F90" s="13"/>
+      <c r="C90" s="57"/>
+      <c r="D90" s="0"/>
+      <c r="E90" s="0"/>
+      <c r="F90" s="0"/>
       <c r="G90" s="12" t="s">
         <v>139</v>
       </c>
@@ -3784,17 +3875,17 @@
         <v>139</v>
       </c>
     </row>
-    <row r="91" spans="1:10" ht="36" customHeight="1">
+    <row r="91" spans="1:10" ht="60" customHeight="1">
       <c r="A91" s="10" t="s">
         <v>140</v>
       </c>
       <c r="B91" s="10" t="s">
         <v>140</v>
       </c>
-      <c r="C91" s="13"/>
-      <c r="D91" s="13"/>
-      <c r="E91" s="13"/>
-      <c r="F91" s="13"/>
+      <c r="C91" s="57"/>
+      <c r="D91" s="0"/>
+      <c r="E91" s="0"/>
+      <c r="F91" s="0"/>
       <c r="G91" s="12" t="s">
         <v>141</v>
       </c>
@@ -3808,17 +3899,17 @@
         <v>141</v>
       </c>
     </row>
-    <row r="92" spans="1:10" ht="36" customHeight="1">
+    <row r="92" spans="1:10" ht="60" customHeight="1">
       <c r="A92" s="10" t="s">
         <v>142</v>
       </c>
       <c r="B92" s="10" t="s">
         <v>142</v>
       </c>
-      <c r="C92" s="13"/>
-      <c r="D92" s="13"/>
-      <c r="E92" s="13"/>
-      <c r="F92" s="13"/>
+      <c r="C92" s="57"/>
+      <c r="D92" s="0"/>
+      <c r="E92" s="0"/>
+      <c r="F92" s="0"/>
       <c r="G92" s="12" t="s">
         <v>141</v>
       </c>
@@ -3832,17 +3923,17 @@
         <v>141</v>
       </c>
     </row>
-    <row r="93" spans="1:10" ht="36" customHeight="1">
+    <row r="93" spans="1:10" ht="60" customHeight="1">
       <c r="A93" s="10" t="s">
         <v>143</v>
       </c>
       <c r="B93" s="10" t="s">
         <v>143</v>
       </c>
-      <c r="C93" s="13"/>
-      <c r="D93" s="13"/>
-      <c r="E93" s="13"/>
-      <c r="F93" s="13"/>
+      <c r="C93" s="57"/>
+      <c r="D93" s="0"/>
+      <c r="E93" s="0"/>
+      <c r="F93" s="0"/>
       <c r="G93" s="12" t="s">
         <v>141</v>
       </c>
@@ -3888,17 +3979,17 @@
         <v>144</v>
       </c>
     </row>
-    <row r="95" spans="1:10" ht="26" customHeight="1">
+    <row r="95" spans="1:10" ht="36" customHeight="1">
       <c r="A95" s="10" t="s">
         <v>145</v>
       </c>
       <c r="B95" s="10" t="s">
         <v>145</v>
       </c>
-      <c r="C95" s="13"/>
-      <c r="D95" s="13"/>
-      <c r="E95" s="13"/>
-      <c r="F95" s="13"/>
+      <c r="C95" s="57"/>
+      <c r="D95" s="0"/>
+      <c r="E95" s="0"/>
+      <c r="F95" s="0"/>
       <c r="G95" s="12" t="s">
         <v>146</v>
       </c>
@@ -3912,17 +4003,17 @@
         <v>146</v>
       </c>
     </row>
-    <row r="96" spans="1:10" ht="26" customHeight="1">
+    <row r="96" spans="1:10" ht="36" customHeight="1">
       <c r="A96" s="10" t="s">
         <v>147</v>
       </c>
       <c r="B96" s="10" t="s">
         <v>147</v>
       </c>
-      <c r="C96" s="13"/>
-      <c r="D96" s="13"/>
-      <c r="E96" s="13"/>
-      <c r="F96" s="13"/>
+      <c r="C96" s="57"/>
+      <c r="D96" s="0"/>
+      <c r="E96" s="0"/>
+      <c r="F96" s="0"/>
       <c r="G96" s="12" t="s">
         <v>146</v>
       </c>
@@ -3936,17 +4027,17 @@
         <v>146</v>
       </c>
     </row>
-    <row r="97" spans="1:10" ht="26" customHeight="1">
+    <row r="97" spans="1:10" ht="60" customHeight="1">
       <c r="A97" s="10" t="s">
         <v>148</v>
       </c>
       <c r="B97" s="10" t="s">
         <v>148</v>
       </c>
-      <c r="C97" s="13"/>
-      <c r="D97" s="13"/>
-      <c r="E97" s="13"/>
-      <c r="F97" s="13"/>
+      <c r="C97" s="57"/>
+      <c r="D97" s="0"/>
+      <c r="E97" s="0"/>
+      <c r="F97" s="0"/>
       <c r="G97" s="12" t="s">
         <v>149</v>
       </c>
@@ -3960,17 +4051,17 @@
         <v>149</v>
       </c>
     </row>
-    <row r="98" spans="1:10" ht="26" customHeight="1">
+    <row r="98" spans="1:10" ht="36" customHeight="1">
       <c r="A98" s="10" t="s">
         <v>150</v>
       </c>
       <c r="B98" s="10" t="s">
         <v>150</v>
       </c>
-      <c r="C98" s="14"/>
-      <c r="D98" s="14"/>
-      <c r="E98" s="14"/>
-      <c r="F98" s="14"/>
+      <c r="C98" s="58"/>
+      <c r="D98" s="0"/>
+      <c r="E98" s="0"/>
+      <c r="F98" s="0"/>
       <c r="G98" s="12" t="s">
         <v>151</v>
       </c>
@@ -3984,17 +4075,17 @@
         <v>151</v>
       </c>
     </row>
-    <row r="99" spans="1:10" ht="54" customHeight="1">
+    <row r="99" spans="1:10" ht="72" customHeight="1">
       <c r="A99" s="10" t="s">
         <v>152</v>
       </c>
       <c r="B99" s="10" t="s">
         <v>152</v>
       </c>
-      <c r="C99" s="13"/>
-      <c r="D99" s="13"/>
-      <c r="E99" s="13"/>
-      <c r="F99" s="13"/>
+      <c r="C99" s="57"/>
+      <c r="D99" s="0"/>
+      <c r="E99" s="0"/>
+      <c r="F99" s="0"/>
       <c r="G99" s="12" t="s">
         <v>153</v>
       </c>
@@ -4008,17 +4099,17 @@
         <v>153</v>
       </c>
     </row>
-    <row r="100" spans="1:10" ht="40" customHeight="1">
+    <row r="100" spans="1:10" ht="36" customHeight="1">
       <c r="A100" s="10" t="s">
         <v>154</v>
       </c>
       <c r="B100" s="10" t="s">
         <v>154</v>
       </c>
-      <c r="C100" s="13"/>
-      <c r="D100" s="13"/>
-      <c r="E100" s="13"/>
-      <c r="F100" s="13"/>
+      <c r="C100" s="57"/>
+      <c r="D100" s="0"/>
+      <c r="E100" s="0"/>
+      <c r="F100" s="0"/>
       <c r="G100" s="12" t="s">
         <v>72</v>
       </c>
@@ -4032,17 +4123,17 @@
         <v>72</v>
       </c>
     </row>
-    <row r="101" spans="1:10" ht="38" customHeight="1">
+    <row r="101" spans="1:10" ht="60" customHeight="1">
       <c r="A101" s="10" t="s">
         <v>155</v>
       </c>
       <c r="B101" s="10" t="s">
         <v>155</v>
       </c>
-      <c r="C101" s="13"/>
-      <c r="D101" s="13"/>
-      <c r="E101" s="13"/>
-      <c r="F101" s="13"/>
+      <c r="C101" s="57"/>
+      <c r="D101" s="0"/>
+      <c r="E101" s="0"/>
+      <c r="F101" s="0"/>
       <c r="G101" s="12" t="s">
         <v>156</v>
       </c>
@@ -4056,17 +4147,17 @@
         <v>156</v>
       </c>
     </row>
-    <row r="102" spans="1:10" ht="26" customHeight="1">
+    <row r="102" spans="1:10" ht="36" customHeight="1">
       <c r="A102" s="10" t="s">
         <v>157</v>
       </c>
       <c r="B102" s="10" t="s">
         <v>157</v>
       </c>
-      <c r="C102" s="13"/>
-      <c r="D102" s="13"/>
-      <c r="E102" s="13"/>
-      <c r="F102" s="13"/>
+      <c r="C102" s="57"/>
+      <c r="D102" s="0"/>
+      <c r="E102" s="0"/>
+      <c r="F102" s="0"/>
       <c r="G102" s="12" t="s">
         <v>76</v>
       </c>
@@ -4087,10 +4178,10 @@
       <c r="B103" s="10" t="s">
         <v>158</v>
       </c>
-      <c r="C103" s="13"/>
-      <c r="D103" s="13"/>
-      <c r="E103" s="13"/>
-      <c r="F103" s="13"/>
+      <c r="C103" s="57"/>
+      <c r="D103" s="0"/>
+      <c r="E103" s="0"/>
+      <c r="F103" s="0"/>
       <c r="G103" s="12" t="s">
         <v>159</v>
       </c>
@@ -4104,17 +4195,17 @@
         <v>159</v>
       </c>
     </row>
-    <row r="104" spans="1:10" ht="36" customHeight="1">
+    <row r="104" spans="1:10" ht="60" customHeight="1">
       <c r="A104" s="10" t="s">
         <v>160</v>
       </c>
       <c r="B104" s="10" t="s">
         <v>160</v>
       </c>
-      <c r="C104" s="13"/>
-      <c r="D104" s="13"/>
-      <c r="E104" s="13"/>
-      <c r="F104" s="13"/>
+      <c r="C104" s="57"/>
+      <c r="D104" s="0"/>
+      <c r="E104" s="0"/>
+      <c r="F104" s="0"/>
       <c r="G104" s="12" t="s">
         <v>161</v>
       </c>
@@ -4128,17 +4219,17 @@
         <v>161</v>
       </c>
     </row>
-    <row r="105" spans="1:10" ht="46" customHeight="1">
+    <row r="105" spans="1:10" ht="72" customHeight="1">
       <c r="A105" s="10" t="s">
         <v>162</v>
       </c>
       <c r="B105" s="10" t="s">
         <v>162</v>
       </c>
-      <c r="C105" s="13"/>
-      <c r="D105" s="13"/>
-      <c r="E105" s="13"/>
-      <c r="F105" s="13"/>
+      <c r="C105" s="57"/>
+      <c r="D105" s="0"/>
+      <c r="E105" s="0"/>
+      <c r="F105" s="0"/>
       <c r="G105" s="12" t="s">
         <v>163</v>
       </c>
@@ -4152,17 +4243,17 @@
         <v>163</v>
       </c>
     </row>
-    <row r="106" spans="1:10" ht="46" customHeight="1">
+    <row r="106" spans="1:10" ht="72" customHeight="1">
       <c r="A106" s="10" t="s">
         <v>164</v>
       </c>
       <c r="B106" s="10" t="s">
         <v>164</v>
       </c>
-      <c r="C106" s="13"/>
-      <c r="D106" s="13"/>
-      <c r="E106" s="13"/>
-      <c r="F106" s="13"/>
+      <c r="C106" s="57"/>
+      <c r="D106" s="0"/>
+      <c r="E106" s="0"/>
+      <c r="F106" s="0"/>
       <c r="G106" s="12" t="s">
         <v>163</v>
       </c>
@@ -4176,17 +4267,17 @@
         <v>163</v>
       </c>
     </row>
-    <row r="107" spans="1:10" ht="54" customHeight="1">
+    <row r="107" spans="1:10" ht="60" customHeight="1">
       <c r="A107" s="10" t="s">
         <v>165</v>
       </c>
       <c r="B107" s="10" t="s">
         <v>165</v>
       </c>
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="13"/>
-      <c r="F107" s="13"/>
+      <c r="C107" s="57"/>
+      <c r="D107" s="0"/>
+      <c r="E107" s="0"/>
+      <c r="F107" s="0"/>
       <c r="G107" s="12" t="s">
         <v>166</v>
       </c>
@@ -4200,17 +4291,17 @@
         <v>166</v>
       </c>
     </row>
-    <row r="108" spans="1:10" ht="46" customHeight="1">
+    <row r="108" spans="1:10" ht="60" customHeight="1">
       <c r="A108" s="10" t="s">
         <v>167</v>
       </c>
       <c r="B108" s="10" t="s">
         <v>167</v>
       </c>
-      <c r="C108" s="13"/>
-      <c r="D108" s="13"/>
-      <c r="E108" s="13"/>
-      <c r="F108" s="13"/>
+      <c r="C108" s="57"/>
+      <c r="D108" s="0"/>
+      <c r="E108" s="0"/>
+      <c r="F108" s="0"/>
       <c r="G108" s="12" t="s">
         <v>168</v>
       </c>
@@ -4224,17 +4315,17 @@
         <v>168</v>
       </c>
     </row>
-    <row r="109" spans="1:10" ht="46" customHeight="1">
+    <row r="109" spans="1:10" ht="60" customHeight="1">
       <c r="A109" s="10" t="s">
         <v>169</v>
       </c>
       <c r="B109" s="10" t="s">
         <v>169</v>
       </c>
-      <c r="C109" s="13"/>
-      <c r="D109" s="13"/>
-      <c r="E109" s="13"/>
-      <c r="F109" s="13"/>
+      <c r="C109" s="57"/>
+      <c r="D109" s="0"/>
+      <c r="E109" s="0"/>
+      <c r="F109" s="0"/>
       <c r="G109" s="12" t="s">
         <v>170</v>
       </c>
@@ -4248,9 +4339,11 @@
         <v>170</v>
       </c>
     </row>
-    <row r="110" spans="1:10">
-      <c r="A110" s="17" t="s">
-        <v>171</v>
+    <row r="110" spans="1:10" ht="52" customHeight="1">
+      <c r="A110" s="17" t="inlineStr">
+        <is>
+          <t xml:space="preserve">入力後は印刷プレビューで全文を確認してください。欄に収まらない長い説明は「別紙参照」と記載し、説明を省略せず別紙を添付してください。</t>
+        </is>
       </c>
       <c r="B110" s="18" t="s">
         <v>171</v>
@@ -4356,50 +4449,82 @@
       <c r="I113" s="1"/>
       <c r="J113" s="1"/>
     </row>
-    <row r="114" spans="1:10">
-      <c r="A114" s="1"/>
+    <row r="114" spans="1:10" ht="36" customHeight="1">
+      <c r="A114" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">勤務制度</t>
+        </is>
+      </c>
       <c r="B114" s="1"/>
-      <c r="C114" s="1"/>
-      <c r="D114" s="1"/>
-      <c r="E114" s="1"/>
-      <c r="F114" s="1"/>
-      <c r="G114" s="1"/>
+      <c r="C114" s="63"/>
+      <c r="D114" s="0"/>
+      <c r="E114" s="0"/>
+      <c r="F114" s="0"/>
+      <c r="G114" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">該当する制度を1つ選択。印刷面に○と内容を表示します。</t>
+        </is>
+      </c>
       <c r="H114" s="1"/>
       <c r="I114" s="1"/>
       <c r="J114" s="1"/>
     </row>
-    <row r="115" spans="1:10">
-      <c r="A115" s="1"/>
+    <row r="115" spans="1:10" ht="36" customHeight="1">
+      <c r="A115" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基本賃金形態</t>
+        </is>
+      </c>
       <c r="B115" s="1"/>
-      <c r="C115" s="1"/>
-      <c r="D115" s="1"/>
-      <c r="E115" s="1"/>
-      <c r="F115" s="1"/>
-      <c r="G115" s="1"/>
+      <c r="C115" s="63"/>
+      <c r="D115" s="0"/>
+      <c r="E115" s="0"/>
+      <c r="F115" s="0"/>
+      <c r="G115" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">基本賃金の形態を1つ選択。該当する金額を70～75行に入力。</t>
+        </is>
+      </c>
       <c r="H115" s="1"/>
       <c r="I115" s="1"/>
       <c r="J115" s="1"/>
     </row>
-    <row r="116" spans="1:10">
-      <c r="A116" s="1"/>
+    <row r="116" spans="1:10" ht="36" customHeight="1">
+      <c r="A116" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">休日労働・1か月の日数</t>
+        </is>
+      </c>
       <c r="B116" s="1"/>
-      <c r="C116" s="1"/>
-      <c r="D116" s="1"/>
-      <c r="E116" s="1"/>
-      <c r="F116" s="1"/>
-      <c r="G116" s="1"/>
+      <c r="C116" s="64"/>
+      <c r="D116" s="0"/>
+      <c r="E116" s="0"/>
+      <c r="F116" s="0"/>
+      <c r="G116" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">短時間用。休日労働が有の場合、1か月の日数を数値で入力。</t>
+        </is>
+      </c>
       <c r="H116" s="1"/>
       <c r="I116" s="1"/>
       <c r="J116" s="1"/>
     </row>
-    <row r="117" spans="1:10">
-      <c r="A117" s="1"/>
+    <row r="117" spans="1:10" ht="36" customHeight="1">
+      <c r="A117" s="10" t="inlineStr">
+        <is>
+          <t xml:space="preserve">休日労働・1年の日数</t>
+        </is>
+      </c>
       <c r="B117" s="1"/>
-      <c r="C117" s="1"/>
-      <c r="D117" s="1"/>
-      <c r="E117" s="1"/>
-      <c r="F117" s="1"/>
-      <c r="G117" s="1"/>
+      <c r="C117" s="64"/>
+      <c r="D117" s="0"/>
+      <c r="E117" s="0"/>
+      <c r="F117" s="0"/>
+      <c r="G117" s="12" t="inlineStr">
+        <is>
+          <t xml:space="preserve">短時間用。休日労働が有の場合、1年の日数を数値で入力。</t>
+        </is>
+      </c>
       <c r="H117" s="1"/>
       <c r="I117" s="1"/>
       <c r="J117" s="1"/>
@@ -4501,331 +4626,257 @@
       <c r="J125" s="1"/>
     </row>
   </sheetData>
-  <mergeCells count="304">
+  <mergeCells count="214">
     <mergeCell ref="A109:B109"/>
-    <mergeCell ref="C109:F109"/>
     <mergeCell ref="G109:J109"/>
     <mergeCell ref="A110:J112"/>
     <mergeCell ref="A107:B107"/>
-    <mergeCell ref="C107:F107"/>
     <mergeCell ref="G107:J107"/>
     <mergeCell ref="A108:B108"/>
-    <mergeCell ref="C108:F108"/>
     <mergeCell ref="G108:J108"/>
     <mergeCell ref="A105:B105"/>
-    <mergeCell ref="C105:F105"/>
     <mergeCell ref="G105:J105"/>
     <mergeCell ref="A106:B106"/>
-    <mergeCell ref="C106:F106"/>
     <mergeCell ref="G106:J106"/>
     <mergeCell ref="A103:B103"/>
-    <mergeCell ref="C103:F103"/>
     <mergeCell ref="G103:J103"/>
     <mergeCell ref="A104:B104"/>
-    <mergeCell ref="C104:F104"/>
     <mergeCell ref="G104:J104"/>
     <mergeCell ref="A101:B101"/>
-    <mergeCell ref="C101:F101"/>
     <mergeCell ref="G101:J101"/>
     <mergeCell ref="A102:B102"/>
-    <mergeCell ref="C102:F102"/>
     <mergeCell ref="G102:J102"/>
     <mergeCell ref="A99:B99"/>
-    <mergeCell ref="C99:F99"/>
     <mergeCell ref="G99:J99"/>
     <mergeCell ref="A100:B100"/>
-    <mergeCell ref="C100:F100"/>
     <mergeCell ref="G100:J100"/>
     <mergeCell ref="A97:B97"/>
-    <mergeCell ref="C97:F97"/>
     <mergeCell ref="G97:J97"/>
     <mergeCell ref="A98:B98"/>
-    <mergeCell ref="C98:F98"/>
     <mergeCell ref="G98:J98"/>
     <mergeCell ref="A94:J94"/>
     <mergeCell ref="A95:B95"/>
-    <mergeCell ref="C95:F95"/>
     <mergeCell ref="G95:J95"/>
     <mergeCell ref="A96:B96"/>
-    <mergeCell ref="C96:F96"/>
     <mergeCell ref="G96:J96"/>
     <mergeCell ref="A92:B92"/>
-    <mergeCell ref="C92:F92"/>
     <mergeCell ref="G92:J92"/>
     <mergeCell ref="A93:B93"/>
-    <mergeCell ref="C93:F93"/>
     <mergeCell ref="G93:J93"/>
     <mergeCell ref="A90:B90"/>
-    <mergeCell ref="C90:F90"/>
     <mergeCell ref="G90:J90"/>
     <mergeCell ref="A91:B91"/>
-    <mergeCell ref="C91:F91"/>
     <mergeCell ref="G91:J91"/>
     <mergeCell ref="A88:B88"/>
-    <mergeCell ref="C88:F88"/>
     <mergeCell ref="G88:J88"/>
     <mergeCell ref="A89:B89"/>
-    <mergeCell ref="C89:F89"/>
     <mergeCell ref="G89:J89"/>
     <mergeCell ref="A86:B86"/>
-    <mergeCell ref="C86:F86"/>
     <mergeCell ref="G86:J86"/>
     <mergeCell ref="A87:B87"/>
-    <mergeCell ref="C87:F87"/>
     <mergeCell ref="G87:J87"/>
     <mergeCell ref="A84:B84"/>
-    <mergeCell ref="C84:F84"/>
     <mergeCell ref="G84:J84"/>
     <mergeCell ref="A85:B85"/>
-    <mergeCell ref="C85:F85"/>
     <mergeCell ref="G85:J85"/>
     <mergeCell ref="A82:B82"/>
-    <mergeCell ref="C82:F82"/>
     <mergeCell ref="G82:J82"/>
     <mergeCell ref="A83:B83"/>
-    <mergeCell ref="C83:F83"/>
     <mergeCell ref="G83:J83"/>
     <mergeCell ref="A80:B80"/>
-    <mergeCell ref="C80:F80"/>
     <mergeCell ref="G80:J80"/>
     <mergeCell ref="A81:B81"/>
-    <mergeCell ref="C81:F81"/>
     <mergeCell ref="G81:J81"/>
     <mergeCell ref="A78:B78"/>
-    <mergeCell ref="C78:F78"/>
     <mergeCell ref="G78:J78"/>
     <mergeCell ref="A79:B79"/>
-    <mergeCell ref="C79:F79"/>
     <mergeCell ref="G79:J79"/>
     <mergeCell ref="A76:B76"/>
-    <mergeCell ref="C76:F76"/>
     <mergeCell ref="G76:J76"/>
     <mergeCell ref="A77:B77"/>
-    <mergeCell ref="C77:F77"/>
     <mergeCell ref="G77:J77"/>
     <mergeCell ref="A74:B74"/>
-    <mergeCell ref="C74:F74"/>
     <mergeCell ref="G74:J74"/>
     <mergeCell ref="A75:B75"/>
-    <mergeCell ref="C75:F75"/>
     <mergeCell ref="G75:J75"/>
     <mergeCell ref="A72:B72"/>
-    <mergeCell ref="C72:F72"/>
     <mergeCell ref="G72:J72"/>
     <mergeCell ref="A73:B73"/>
-    <mergeCell ref="C73:F73"/>
     <mergeCell ref="G73:J73"/>
     <mergeCell ref="A69:J69"/>
     <mergeCell ref="A70:B70"/>
-    <mergeCell ref="C70:F70"/>
     <mergeCell ref="G70:J70"/>
     <mergeCell ref="A71:B71"/>
-    <mergeCell ref="C71:F71"/>
     <mergeCell ref="G71:J71"/>
     <mergeCell ref="A67:B67"/>
-    <mergeCell ref="C67:F67"/>
     <mergeCell ref="G67:J67"/>
     <mergeCell ref="A68:B68"/>
-    <mergeCell ref="C68:F68"/>
     <mergeCell ref="G68:J68"/>
     <mergeCell ref="A65:B65"/>
-    <mergeCell ref="C65:F65"/>
     <mergeCell ref="G65:J65"/>
     <mergeCell ref="A66:B66"/>
-    <mergeCell ref="C66:F66"/>
     <mergeCell ref="G66:J66"/>
     <mergeCell ref="A63:B63"/>
-    <mergeCell ref="C63:F63"/>
     <mergeCell ref="G63:J63"/>
     <mergeCell ref="A64:B64"/>
-    <mergeCell ref="C64:F64"/>
     <mergeCell ref="G64:J64"/>
     <mergeCell ref="A61:B61"/>
-    <mergeCell ref="C61:F61"/>
     <mergeCell ref="G61:J61"/>
     <mergeCell ref="A62:B62"/>
-    <mergeCell ref="C62:F62"/>
     <mergeCell ref="G62:J62"/>
     <mergeCell ref="A59:B59"/>
-    <mergeCell ref="C59:F59"/>
     <mergeCell ref="G59:J59"/>
     <mergeCell ref="A60:B60"/>
-    <mergeCell ref="C60:F60"/>
     <mergeCell ref="G60:J60"/>
     <mergeCell ref="A57:B57"/>
-    <mergeCell ref="C57:F57"/>
     <mergeCell ref="G57:J57"/>
     <mergeCell ref="A58:B58"/>
-    <mergeCell ref="C58:F58"/>
     <mergeCell ref="G58:J58"/>
     <mergeCell ref="A55:B55"/>
-    <mergeCell ref="C55:F55"/>
     <mergeCell ref="G55:J55"/>
     <mergeCell ref="A56:B56"/>
-    <mergeCell ref="C56:F56"/>
     <mergeCell ref="G56:J56"/>
     <mergeCell ref="A52:J52"/>
     <mergeCell ref="A53:B53"/>
-    <mergeCell ref="C53:F53"/>
     <mergeCell ref="G53:J53"/>
     <mergeCell ref="A54:B54"/>
-    <mergeCell ref="C54:F54"/>
     <mergeCell ref="G54:J54"/>
     <mergeCell ref="A50:B50"/>
-    <mergeCell ref="C50:F50"/>
     <mergeCell ref="G50:J50"/>
     <mergeCell ref="A51:B51"/>
-    <mergeCell ref="C51:F51"/>
     <mergeCell ref="G51:J51"/>
     <mergeCell ref="A48:B48"/>
-    <mergeCell ref="C48:F48"/>
     <mergeCell ref="G48:J48"/>
     <mergeCell ref="A49:B49"/>
-    <mergeCell ref="C49:F49"/>
     <mergeCell ref="G49:J49"/>
     <mergeCell ref="A46:B46"/>
-    <mergeCell ref="C46:F46"/>
     <mergeCell ref="G46:J46"/>
     <mergeCell ref="A47:B47"/>
-    <mergeCell ref="C47:F47"/>
     <mergeCell ref="G47:J47"/>
     <mergeCell ref="A44:B44"/>
-    <mergeCell ref="C44:F44"/>
     <mergeCell ref="G44:J44"/>
     <mergeCell ref="A45:B45"/>
-    <mergeCell ref="C45:F45"/>
     <mergeCell ref="G45:J45"/>
     <mergeCell ref="A42:B42"/>
-    <mergeCell ref="C42:F42"/>
     <mergeCell ref="G42:J42"/>
     <mergeCell ref="A43:B43"/>
-    <mergeCell ref="C43:F43"/>
     <mergeCell ref="G43:J43"/>
     <mergeCell ref="A40:B40"/>
-    <mergeCell ref="C40:F40"/>
     <mergeCell ref="G40:J40"/>
     <mergeCell ref="A41:B41"/>
-    <mergeCell ref="C41:F41"/>
     <mergeCell ref="G41:J41"/>
     <mergeCell ref="A38:B38"/>
-    <mergeCell ref="C38:F38"/>
     <mergeCell ref="G38:J38"/>
     <mergeCell ref="A39:B39"/>
-    <mergeCell ref="C39:F39"/>
     <mergeCell ref="G39:J39"/>
     <mergeCell ref="A36:B36"/>
-    <mergeCell ref="C36:F36"/>
     <mergeCell ref="G36:J36"/>
     <mergeCell ref="A37:B37"/>
-    <mergeCell ref="C37:F37"/>
     <mergeCell ref="G37:J37"/>
     <mergeCell ref="A33:B33"/>
-    <mergeCell ref="C33:F33"/>
     <mergeCell ref="G33:J33"/>
     <mergeCell ref="A34:J34"/>
     <mergeCell ref="A35:B35"/>
-    <mergeCell ref="C35:F35"/>
     <mergeCell ref="G35:J35"/>
     <mergeCell ref="A31:B31"/>
-    <mergeCell ref="C31:F31"/>
     <mergeCell ref="G31:J31"/>
     <mergeCell ref="A32:B32"/>
-    <mergeCell ref="C32:F32"/>
     <mergeCell ref="G32:J32"/>
     <mergeCell ref="A29:B29"/>
-    <mergeCell ref="C29:F29"/>
     <mergeCell ref="G29:J29"/>
     <mergeCell ref="A30:B30"/>
-    <mergeCell ref="C30:F30"/>
     <mergeCell ref="G30:J30"/>
     <mergeCell ref="A26:J26"/>
     <mergeCell ref="A27:B27"/>
-    <mergeCell ref="C27:F27"/>
     <mergeCell ref="G27:J27"/>
     <mergeCell ref="A28:B28"/>
-    <mergeCell ref="C28:F28"/>
     <mergeCell ref="G28:J28"/>
     <mergeCell ref="A24:B24"/>
-    <mergeCell ref="C24:F24"/>
     <mergeCell ref="G24:J24"/>
     <mergeCell ref="A25:B25"/>
-    <mergeCell ref="C25:F25"/>
     <mergeCell ref="G25:J25"/>
     <mergeCell ref="A22:B22"/>
-    <mergeCell ref="C22:F22"/>
     <mergeCell ref="G22:J22"/>
     <mergeCell ref="A23:B23"/>
-    <mergeCell ref="C23:F23"/>
     <mergeCell ref="G23:J23"/>
     <mergeCell ref="A20:B20"/>
-    <mergeCell ref="C20:F20"/>
     <mergeCell ref="G20:J20"/>
     <mergeCell ref="A21:B21"/>
-    <mergeCell ref="C21:F21"/>
     <mergeCell ref="G21:J21"/>
     <mergeCell ref="A18:B18"/>
-    <mergeCell ref="C18:F18"/>
     <mergeCell ref="G18:J18"/>
     <mergeCell ref="A19:B19"/>
-    <mergeCell ref="C19:F19"/>
     <mergeCell ref="G19:J19"/>
     <mergeCell ref="A16:B16"/>
-    <mergeCell ref="C16:F16"/>
     <mergeCell ref="G16:J16"/>
     <mergeCell ref="A17:B17"/>
-    <mergeCell ref="C17:F17"/>
     <mergeCell ref="G17:J17"/>
     <mergeCell ref="A14:B14"/>
-    <mergeCell ref="C14:F14"/>
     <mergeCell ref="G14:J14"/>
     <mergeCell ref="A15:B15"/>
-    <mergeCell ref="C15:F15"/>
     <mergeCell ref="G15:J15"/>
     <mergeCell ref="A11:B11"/>
-    <mergeCell ref="C11:F11"/>
     <mergeCell ref="G11:J11"/>
     <mergeCell ref="A12:J12"/>
     <mergeCell ref="A13:B13"/>
-    <mergeCell ref="C13:F13"/>
     <mergeCell ref="G13:J13"/>
     <mergeCell ref="A9:B9"/>
-    <mergeCell ref="C9:F9"/>
     <mergeCell ref="G9:J9"/>
     <mergeCell ref="A10:B10"/>
-    <mergeCell ref="C10:F10"/>
     <mergeCell ref="G10:J10"/>
     <mergeCell ref="A7:B7"/>
-    <mergeCell ref="C7:F7"/>
     <mergeCell ref="G7:J7"/>
     <mergeCell ref="A8:B8"/>
-    <mergeCell ref="C8:F8"/>
     <mergeCell ref="G8:J8"/>
     <mergeCell ref="A1:J2"/>
     <mergeCell ref="A3:J3"/>
     <mergeCell ref="A5:J5"/>
     <mergeCell ref="A6:B6"/>
-    <mergeCell ref="C6:F6"/>
     <mergeCell ref="G6:J6"/>
+    <mergeCell ref="A114:B114"/>
+    <mergeCell ref="G114:J114"/>
+    <mergeCell ref="A115:B115"/>
+    <mergeCell ref="G115:J115"/>
+    <mergeCell ref="A116:B116"/>
+    <mergeCell ref="G116:J116"/>
+    <mergeCell ref="A117:B117"/>
+    <mergeCell ref="G117:J117"/>
   </mergeCells>
   <phoneticPr fontId="17"/>
-  <dataValidations count="6">
-    <dataValidation type="list" sqref="C13" xr:uid="{00000000-0002-0000-0000-000000000000}">
+  <dataValidations count="11">
+    <dataValidation type="list" sqref="C13" xr:uid="{00000000-0002-0000-0000-000000000000}" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。">
       <formula1>"期間の定めなし,期間の定めあり"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}">
+    <dataValidation type="list" sqref="C16" xr:uid="{00000000-0002-0000-0000-000001000000}" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。">
       <formula1>"自動的に更新する,更新する場合があり得る,契約の更新はしない,その他"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C19" xr:uid="{00000000-0002-0000-0000-000002000000}">
+    <dataValidation type="list" sqref="C19" xr:uid="{00000000-0002-0000-0000-000002000000}" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。">
       <formula1>"無,有"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C23" xr:uid="{00000000-0002-0000-0000-000003000000}">
+    <dataValidation type="list" sqref="C23" xr:uid="{00000000-0002-0000-0000-000003000000}" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。">
       <formula1>"無,有（別紙のとおり）"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}">
+    <dataValidation type="list" sqref="C24" xr:uid="{00000000-0002-0000-0000-000004000000}" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。">
       <formula1>"該当なし,高度専門,定年後の高齢者"</formula1>
     </dataValidation>
-    <dataValidation type="list" sqref="C102 C64:C65 C61 C47:C48" xr:uid="{00000000-0002-0000-0000-000005000000}">
+    <dataValidation type="list" sqref="C102 C64:C65 C61 C47:C48" xr:uid="{00000000-0002-0000-0000-000005000000}" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。">
       <formula1>"有,無"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。" sqref="C114">
+      <formula1>"通常勤務,変形労働時間制等,フレックスタイム制,事業場外みなし労働時間制,裁量労働制"</formula1>
+    </dataValidation>
+    <dataValidation type="list" allowBlank="1" showDropDown="0" showErrorMessage="1" errorStyle="stop" errorTitle="入力値を確認してください" error="一覧の選択肢を選んでください。" sqref="C115">
+      <formula1>"月給,日給,時間給,出来高給,その他"</formula1>
+    </dataValidation>
+    <dataValidation type="date" operator="between" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="日付を入力してください" error="例：2026/10/05 のように日付を入力してください。" sqref="C6 C14 C15 C22 C32 C33">
+      <formula1>1</formula1>
+      <formula2>2958465</formula2>
+    </dataValidation>
+    <dataValidation type="whole" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="整数を入力してください" error="0以上の整数を入力してください。" sqref="C20 C25 C46 C56 C60 C62 C63 C98 C116 C117 C70 C71 C72 C73 C74 C75">
+      <formula1>0</formula1>
+    </dataValidation>
+    <dataValidation type="decimal" operator="greaterThanOrEqual" allowBlank="1" showErrorMessage="1" errorStyle="stop" errorTitle="数値を入力してください" error="0以上の数値を入力してください。率は25%の場合25と入力します。" sqref="C21 C49 C50 C51 C81 C82 C83 C84 C85 C86">
+      <formula1>0</formula1>
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -4844,7 +4895,7 @@
     <col min="3" max="12" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16" customHeight="1">
+    <row r="1" spans="1:12" ht="12" customHeight="1">
       <c r="A1" s="26" t="s">
         <v>172</v>
       </c>
@@ -4942,27 +4993,23 @@
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
-      <c r="H4" s="31" t="str">
-        <f>IF(入力!$C$6="","　　年　月　日",TEXT(入力!$C$6,"yyyy年m月d日"))</f>
-        <v>　　年　月　日</v>
+      <c r="H4" s="31">
+        <f>IF(LEN('入力'!$C$6)=0,"　　年　月　日",TEXT('入力'!$C$6,"yyyy年m月d日"))</f>
       </c>
       <c r="I4" s="32"/>
       <c r="J4" s="32"/>
       <c r="K4" s="32"/>
       <c r="L4" s="33"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="34" t="str">
-        <f>IF(入力!$C$7="","　　　　　　　　　",入力!$C$7)&amp;"　殿"</f>
-        <v>　　　　　　　　　　殿</v>
+    <row r="5" spans="1:12" ht="60" customHeight="1">
+      <c r="A5" s="34">
+        <f>IF(LEN('入力'!$C$7)=0,"　　　　　　　　　",'入力'!$C$7)&amp;"　殿"</f>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
       <c r="D5" s="36"/>
-      <c r="E5" s="40" t="str">
-        <f>"事業場名称・所在地　"&amp;IF(入力!$C$8="","　　　　　　　　　",入力!$C$8)&amp;CHAR(10)&amp;"　　　　　　　　　"&amp;IF(入力!$C$9="","　　　　　　　　　",入力!$C$9)</f>
-        <v>事業場名称・所在地　　　　　　　　　　
-　　　　　　　　　　　　　　　　　　</v>
+      <c r="E5" s="40">
+        <f>"事業場名称・所在地　"&amp;IF(LEN('入力'!$C$8)=0,"　　　　　　　　　",'入力'!$C$8)&amp;CHAR(10)&amp;"　　　　　　　　　"&amp;IF(LEN('入力'!$C$9)=0,"　　　　　　　　　",'入力'!$C$9)</f>
       </c>
       <c r="F5" s="41"/>
       <c r="G5" s="41"/>
@@ -4972,14 +5019,13 @@
       <c r="K5" s="41"/>
       <c r="L5" s="42"/>
     </row>
-    <row r="6" spans="1:12" ht="24" customHeight="1">
+    <row r="6" spans="1:12" ht="36" customHeight="1">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="39"/>
-      <c r="E6" s="43" t="str">
-        <f>"使　用　者　職　氏　名　"&amp;IF(入力!$C$10="","　　　　　",入力!$C$10)&amp;"　"&amp;IF(入力!$C$11="","　　　　　",入力!$C$11)</f>
-        <v>使　用　者　職　氏　名　　　　　　　　　　　　</v>
+      <c r="E6" s="43">
+        <f>"使　用　者　職　氏　名　"&amp;IF(LEN('入力'!$C$10)=0,"　　　　　",'入力'!$C$10)&amp;"　"&amp;IF(LEN('入力'!$C$11)=0,"　　　　　",'入力'!$C$11)</f>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -4989,24 +5035,15 @@
       <c r="K6" s="44"/>
       <c r="L6" s="45"/>
     </row>
-    <row r="7" spans="1:12" ht="121" customHeight="1">
+    <row r="7" spans="1:12" ht="100" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="47" t="str">
-        <f>IF(入力!$C$13="期間の定めなし","○期間の定めなし","期間の定めなし")&amp;"、"&amp;IF(入力!$C$13="期間の定めあり","○期間の定めあり","期間の定めあり")&amp;"（"&amp;IF(入力!$C$14="","　年　月　日",TEXT(入力!$C$14,"yyyy年m月d日"))&amp;"～"&amp;IF(入力!$C$15="","　年　月　日",TEXT(入力!$C$15,"yyyy年m月d日"))&amp;"）"&amp;CHAR(10)&amp;"※以下は、「契約期間」について「期間の定めあり」とした場合に記入"&amp;CHAR(10)&amp;"１　契約の更新の有無"&amp;CHAR(10)&amp;"　［"&amp;IF(入力!$C$16="自動的に更新する","○自動的に更新する","自動的に更新する")&amp;"・"&amp;IF(入力!$C$16="更新する場合があり得る","○更新する場合があり得る","更新する場合があり得る")&amp;"・"&amp;IF(入力!$C$16="契約の更新はしない","○契約の更新はしない","契約の更新はしない")&amp;"・"&amp;IF(入力!$C$16="その他","○その他","その他")&amp;"（"&amp;IF(入力!$C$17="","　　　",入力!$C$17)&amp;"）］"&amp;CHAR(10)&amp;"２　契約の更新は次により判断する。"&amp;CHAR(10)&amp;"　・契約期間満了時の業務量　　・勤務成績、態度　　　　・能力"&amp;CHAR(10)&amp;"　・会社の経営状況　　・従事している業務の進捗状況"&amp;CHAR(10)&amp;"　・その他（"&amp;IF(入力!$C$18="","　　　　　　　　　　　　　",入力!$C$18)&amp;"）"&amp;CHAR(10)&amp;"３　更新上限の有無（"&amp;IF(入力!$C$19="無","○無","無")&amp;"・"&amp;IF(入力!$C$19="有","○有","有")&amp;"（更新　"&amp;IF(入力!$C$20="","　",TEXT(入力!$C$20,IF(入力!$C$20=INT(N(入力!$C$20)),"0","0.##")))&amp;"回まで／通算契約期間　"&amp;IF(入力!$C$21="","　",TEXT(入力!$C$21,IF(入力!$C$21=INT(N(入力!$C$21)),"0","0.##")))&amp;"年まで））"</f>
-        <v>期間の定めなし、期間の定めあり（　年　月　日～　年　月　日）
-※以下は、「契約期間」について「期間の定めあり」とした場合に記入
-１　契約の更新の有無
-　［自動的に更新する・更新する場合があり得る・契約の更新はしない・その他（　　　）］
-２　契約の更新は次により判断する。
-　・契約期間満了時の業務量　　・勤務成績、態度　　　　・能力
-　・会社の経営状況　　・従事している業務の進捗状況
-　・その他（　　　　　　　　　　　　　）
-３　更新上限の有無（無・有（更新　　回まで／通算契約期間　　年まで））</v>
+      <c r="C7" s="47">
+        <f>IF('入力'!$C$13="期間の定めなし","○期間の定めなし","期間の定めなし")&amp;"、"&amp;IF('入力'!$C$13="期間の定めあり","○期間の定めあり","期間の定めあり")&amp;IF('入力'!$C$13="期間の定めあり","（"&amp;IF(LEN('入力'!$C$14)=0,"　年　月　日",TEXT('入力'!$C$14,"yyyy年m月d日"))&amp;"～"&amp;IF(LEN('入力'!$C$15)=0,"　年　月　日",TEXT('入力'!$C$15,"yyyy年m月d日"))&amp;"）"&amp;CHAR(10)&amp;"１ 契約更新："&amp;IF('入力'!$C$16="自動的に更新する","○自動的に更新する","自動的に更新する")&amp;"・"&amp;IF('入力'!$C$16="更新する場合があり得る","○更新する場合があり得る","更新する場合があり得る")&amp;"・"&amp;IF('入力'!$C$16="契約の更新はしない","○契約の更新はしない","契約の更新はしない")&amp;"・"&amp;IF('入力'!$C$16="その他","○その他","その他")&amp;IF(LEN('入力'!$C$17)=0,"","（"&amp;'入力'!$C$17&amp;"）")&amp;CHAR(10)&amp;"２ 契約更新の判断基準："&amp;IF(LEN('入力'!$C$18)=0,"適用する判断基準を記入",'入力'!$C$18)&amp;CHAR(10)&amp;"３ 更新上限："&amp;IF('入力'!$C$19="無","○無","無")&amp;"・"&amp;IF('入力'!$C$19="有","○有","有")&amp;IF('入力'!$C$19="有","（更新 "&amp;IF(LEN('入力'!$C$20)=0,"　",TEXT('入力'!$C$20,IF('入力'!$C$20=INT(N('入力'!$C$20)),"0","0.##")))&amp;"回まで／通算契約期間 "&amp;IF(LEN('入力'!$C$21)=0,"　",TEXT('入力'!$C$21,IF('入力'!$C$21=INT(N('入力'!$C$21)),"0","0.##")))&amp;"年まで）",""),"")</f>
       </c>
       <c r="D7" s="47"/>
       <c r="E7" s="47"/>
@@ -5019,10 +5056,8 @@
       <c r="L7" s="47"/>
     </row>
     <row r="8" spans="1:12" ht="45" customHeight="1">
-      <c r="A8" s="47" t="str">
-        <f>"【労働契約法に定める同一の企業との間での通算契約期間が５年を超える有期労働契約の締結の場合】"&amp;CHAR(10)&amp;"　本契約期間中に会社に対して期間の定めのない労働契約（無期労働契約）の締結の申込みをすることにより、本契約期間の末日の翌日（"&amp;IF(入力!$C$22="","　年　月　日",TEXT(入力!$C$22,"yyyy年m月d日"))&amp;"）から、無期労働契約での雇用に転換することができる。この場合の本契約からの労働条件の変更の有無（"&amp;IF(入力!$C$23="無","○無","無")&amp;"・"&amp;IF(入力!$C$23="有（別紙のとおり）","○有（別紙のとおり）","有（別紙のとおり）")&amp;"）"</f>
-        <v>【労働契約法に定める同一の企業との間での通算契約期間が５年を超える有期労働契約の締結の場合】
-　本契約期間中に会社に対して期間の定めのない労働契約（無期労働契約）の締結の申込みをすることにより、本契約期間の末日の翌日（　年　月　日）から、無期労働契約での雇用に転換することができる。この場合の本契約からの労働条件の変更の有無（無・有（別紙のとおり））</v>
+      <c r="A8" s="47">
+        <f>"【労働契約法に定める同一の企業との間での通算契約期間が５年を超える有期労働契約の締結の場合】"&amp;CHAR(10)&amp;"　本契約期間中に会社に対して期間の定めのない労働契約（無期労働契約）の締結の申込みをすることにより、本契約期間の末日の翌日（"&amp;IF(LEN('入力'!$C$22)=0,"　年　月　日",TEXT('入力'!$C$22,"yyyy年m月d日"))&amp;"）から、無期労働契約での雇用に転換することができる。この場合の本契約からの労働条件の変更の有無（"&amp;IF('入力'!$C$23="無","○無","無")&amp;"・"&amp;IF('入力'!$C$23="有（別紙のとおり）","○有（別紙のとおり）","有（別紙のとおり）")&amp;"）"</f>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="47"/>
@@ -5036,13 +5071,9 @@
       <c r="K8" s="47"/>
       <c r="L8" s="47"/>
     </row>
-    <row r="9" spans="1:12" ht="56" customHeight="1">
-      <c r="A9" s="47" t="str">
-        <f>"【有期雇用特別措置法による特例の対象者の場合】"&amp;CHAR(10)&amp;"　無期転換申込権が発生しない期間：　Ⅰ（高度専門）・Ⅱ（定年後の高齢者）　　対象："&amp;IF(入力!$C$24="","　　　　　　",入力!$C$24)&amp;CHAR(10)&amp;"　Ⅰ　特定有期業務の開始から完了までの期間（　"&amp;IF(入力!$C$25="","　",TEXT(入力!$C$25,IF(入力!$C$25=INT(N(入力!$C$25)),"0","0.##")))&amp;"か月（上限10年））"&amp;CHAR(10)&amp;"　Ⅱ　定年後引き続いて雇用されている期間"</f>
-        <v>【有期雇用特別措置法による特例の対象者の場合】
-　無期転換申込権が発生しない期間：　Ⅰ（高度専門）・Ⅱ（定年後の高齢者）　　対象：　　　　　　
-　Ⅰ　特定有期業務の開始から完了までの期間（　　か月（上限10年））
-　Ⅱ　定年後引き続いて雇用されている期間</v>
+    <row r="9" spans="1:12" ht="38" customHeight="1">
+      <c r="A9" s="47">
+        <f>"【有期雇用特別措置法による特例の対象者の場合】"&amp;CHAR(10)&amp;"無期転換申込権が発生しない期間／対象："&amp;IF(LEN('入力'!$C$24)=0,"　",'入力'!$C$24)&amp;IF('入力'!$C$24="高度専門",CHAR(10)&amp;"Ⅰ 特定有期業務の開始から完了まで（"&amp;IF(LEN('入力'!$C$25)=0,"　",TEXT('入力'!$C$25,IF('入力'!$C$25=INT(N('入力'!$C$25)),"0","0.##")))&amp;"か月、上限10年）",IF('入力'!$C$24="定年後の高齢者",CHAR(10)&amp;"Ⅱ 定年後引き続いて雇用されている期間",""))</f>
       </c>
       <c r="B9" s="47"/>
       <c r="C9" s="47"/>
@@ -5056,17 +5087,15 @@
       <c r="K9" s="47"/>
       <c r="L9" s="47"/>
     </row>
-    <row r="10" spans="1:12" ht="30" customHeight="1">
+    <row r="10" spans="1:12" ht="60" customHeight="1">
       <c r="A10" s="48" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="55" t="str">
-        <f>"（雇入れ直後）"&amp;IF(入力!$C$27="","　　　　　　　　　　　",入力!$C$27)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(入力!$C$28="","　　　　　　　　　　　",入力!$C$28)</f>
-        <v>（雇入れ直後）　　　　　　　　　　　
-（変更の範囲）　　　　　　　　　　　</v>
+      <c r="C10" s="55">
+        <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$27)=0,"　　　　　　　　　　　",'入力'!$C$27)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$28)=0,"　　　　　　　　　　　",'入力'!$C$28)</f>
       </c>
       <c r="D10" s="55"/>
       <c r="E10" s="55"/>
@@ -5078,19 +5107,15 @@
       <c r="K10" s="55"/>
       <c r="L10" s="55"/>
     </row>
-    <row r="11" spans="1:12" ht="56" customHeight="1">
+    <row r="11" spans="1:12" ht="96" customHeight="1">
       <c r="A11" s="48" t="s">
         <v>175</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="55" t="str">
-        <f>"（雇入れ直後）"&amp;IF(入力!$C$29="","　　　　　　　　　　　",入力!$C$29)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(入力!$C$30="","　　　　　　　　　　　",入力!$C$30)&amp;CHAR(10)&amp;"【有期雇用特別措置法による特例の対象者（高度専門）の場合】"&amp;CHAR(10)&amp;"・特定有期業務（"&amp;IF(入力!$C$31="","　　　　　　　　　",入力!$C$31)&amp;"　開始日："&amp;IF(入力!$C$32="","　　　　",TEXT(入力!$C$32,"yyyy年m月d日"))&amp;"　完了日："&amp;IF(入力!$C$33="","　　　　",TEXT(入力!$C$33,"yyyy年m月d日"))&amp;"）"</f>
-        <v>（雇入れ直後）　　　　　　　　　　　
-（変更の範囲）　　　　　　　　　　　
-【有期雇用特別措置法による特例の対象者（高度専門）の場合】
-・特定有期業務（　　　　　　　　　　開始日：　　　　　完了日：　　　　）</v>
+      <c r="C11" s="55">
+        <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$29)=0,"　　　　　　　　　　　",'入力'!$C$29)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$30)=0,"　　　　　　　　　　　",'入力'!$C$30)&amp;CHAR(10)&amp;"【有期雇用特別措置法による特例の対象者（高度専門）の場合】"&amp;CHAR(10)&amp;"・特定有期業務（"&amp;IF(LEN('入力'!$C$31)=0,"　　　　　　　　　",'入力'!$C$31)&amp;"　開始日："&amp;IF(LEN('入力'!$C$32)=0,"　　　　",TEXT('入力'!$C$32,"yyyy年m月d日"))&amp;"　完了日："&amp;IF(LEN('入力'!$C$33)=0,"　　　　",TEXT('入力'!$C$33,"yyyy年m月d日"))&amp;"）"</f>
       </c>
       <c r="D11" s="55"/>
       <c r="E11" s="55"/>
@@ -5102,30 +5127,20 @@
       <c r="K11" s="55"/>
       <c r="L11" s="55"/>
     </row>
-    <row r="12" spans="1:12" ht="232" customHeight="1">
-      <c r="A12" s="48" t="s">
-        <v>176</v>
+    <row r="12" spans="1:12" ht="130" customHeight="1">
+      <c r="A12" s="48" t="inlineStr">
+        <is>
+          <t xml:space="preserve">始業・終業の時刻
+休憩時間
+勤務制度
+所定時間外労働</t>
+        </is>
       </c>
       <c r="B12" s="48" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="50" t="str">
-        <f>"１　始業・終業の時刻等"&amp;CHAR(10)&amp;"(1) 始業（"&amp;IF(入力!$C$35="","　時　分",入力!$C$35)&amp;"）　終業（"&amp;IF(入力!$C$36="","　時　分",入力!$C$36)&amp;"）"&amp;CHAR(10)&amp;"【以下のような制度が労働者に適用される場合】"&amp;CHAR(10)&amp;"(2) 変形労働時間制等；（"&amp;IF(入力!$C$37="","　",入力!$C$37)&amp;"）単位の変形労働時間制・交替制として、次の勤務時間の組み合わせによる。"&amp;CHAR(10)&amp;"　├ "&amp;IF(入力!$C$38="","始業（　時　分）終業（　時　分）（適用日　　　　）",入力!$C$38)&amp;CHAR(10)&amp;"　├ "&amp;IF(入力!$C$39="","始業（　時　分）終業（　時　分）（適用日　　　　）",入力!$C$39)&amp;CHAR(10)&amp;"　└ "&amp;IF(入力!$C$40="","始業（　時　分）終業（　時　分）（適用日　　　　）",入力!$C$40)&amp;CHAR(10)&amp;"(3) フレックスタイム制；始業及び終業の時刻は労働者の決定に委ねる。"&amp;CHAR(10)&amp;"　（ただし、フレキシブルタイム　"&amp;IF(入力!$C$41="","（始業）　時　分から　時　分、（終業）　時　分から　時　分",入力!$C$41)&amp;"、"&amp;CHAR(10)&amp;"　　　　　　　　コアタイム　"&amp;IF(入力!$C$42="","　時　分から　時　分",入力!$C$42)&amp;"）"&amp;CHAR(10)&amp;"(4) 事業場外みなし労働時間制；"&amp;IF(入力!$C$43="","始業（　時　分）終業（　時　分）",入力!$C$43)&amp;CHAR(10)&amp;"(5) 裁量労働制；"&amp;IF(入力!$C$44="","始業（　時　分）終業（　時　分）",入力!$C$44)&amp;"を基本とし、労働者の決定に委ねる。"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$45="","第　条～第　条、第　条～第　条、第　条～第　条",入力!$C$45)&amp;CHAR(10)&amp;"２　休憩時間（"&amp;IF(入力!$C$46="","　",TEXT(入力!$C$46,IF(入力!$C$46=INT(N(入力!$C$46)),"0","0.##")))&amp;"）分"&amp;CHAR(10)&amp;"３　所定時間外労働の有無（"&amp;IF(入力!$C$47="有","○有","有")&amp;"，"&amp;IF(入力!$C$47="無","○無","無")&amp;"）"</f>
-        <v>１　始業・終業の時刻等
-(1) 始業（　時　分）　終業（　時　分）
-【以下のような制度が労働者に適用される場合】
-(2) 変形労働時間制等；（　）単位の変形労働時間制・交替制として、次の勤務時間の組み合わせによる。
-　├ 始業（　時　分）終業（　時　分）（適用日　　　　）
-　├ 始業（　時　分）終業（　時　分）（適用日　　　　）
-　└ 始業（　時　分）終業（　時　分）（適用日　　　　）
-(3) フレックスタイム制；始業及び終業の時刻は労働者の決定に委ねる。
-　（ただし、フレキシブルタイム　（始業）　時　分から　時　分、（終業）　時　分から　時　分、
-　　　　　　　　コアタイム　　時　分から　時　分）
-(4) 事業場外みなし労働時間制；始業（　時　分）終業（　時　分）
-(5) 裁量労働制；始業（　時　分）終業（　時　分）を基本とし、労働者の決定に委ねる。
-○詳細は、就業規則　第　条～第　条、第　条～第　条、第　条～第　条
-２　休憩時間（　）分
-３　所定時間外労働の有無（有，無）</v>
+      <c r="C12" s="50">
+        <f>"１ 始業・終業の時刻等"&amp;CHAR(10)&amp;IF('入力'!$C$114="通常勤務","○(1) 始業（"&amp;IF(LEN('入力'!$C$35)=0,"　時　分",'入力'!$C$35)&amp;"） 終業（"&amp;IF(LEN('入力'!$C$36)=0,"　時　分",'入力'!$C$36)&amp;"）",IF('入力'!$C$114="変形労働時間制等","○(2) "&amp;IF(LEN('入力'!$C$37)=0,"適用する制度の名称を記入",'入力'!$C$37)&amp;CHAR(10)&amp;IF(LEN('入力'!$C$38)=0,"始業・終業・適用日を記入",'入力'!$C$38)&amp;CHAR(10)&amp;IF(LEN('入力'!$C$39)=0,"",'入力'!$C$39)&amp;CHAR(10)&amp;IF(LEN('入力'!$C$40)=0,"",'入力'!$C$40),IF('入力'!$C$114="フレックスタイム制","○(3) フレックスタイム制：始業・終業は労働者の決定に委ねる。"&amp;CHAR(10)&amp;"フレキシブルタイム："&amp;IF(LEN('入力'!$C$41)=0,"　",'入力'!$C$41)&amp;CHAR(10)&amp;"コアタイム："&amp;IF(LEN('入力'!$C$42)=0,"　",'入力'!$C$42),IF('入力'!$C$114="事業場外みなし労働時間制","○(4) 事業場外みなし労働時間制："&amp;IF(LEN('入力'!$C$43)=0,"始業・終業を記入",'入力'!$C$43),IF('入力'!$C$114="裁量労働制","○(5) 裁量労働制："&amp;IF(LEN('入力'!$C$44)=0,"始業・終業を記入",'入力'!$C$44)&amp;"を基本とし、労働者の決定に委ねる。","入力シート末尾の勤務制度を選択してください")))))&amp;CHAR(10)&amp;"○詳細は、就業規則 "&amp;IF(LEN('入力'!$C$45)=0,"　",'入力'!$C$45)&amp;CHAR(10)&amp;"２ 休憩時間（"&amp;IF(LEN('入力'!$C$46)=0,"　",TEXT('入力'!$C$46,IF('入力'!$C$46=INT(N('入力'!$C$46)),"0","0.##")))&amp;"）分"&amp;CHAR(10)&amp;"３ 所定時間外労働（"&amp;IF('入力'!$C$47="有","○有","有")&amp;"、"&amp;IF('入力'!$C$47="無","○無","無")&amp;"）"</f>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="50"/>
@@ -5144,12 +5159,8 @@
       <c r="B13" s="46" t="s">
         <v>177</v>
       </c>
-      <c r="C13" s="47" t="str">
-        <f>"・定例日；毎週　"&amp;IF(入力!$C$53="","　曜日",入力!$C$53)&amp;"、国民の祝日、その他（"&amp;IF(入力!$C$54="","　　　　　　　　　",入力!$C$54)&amp;"）"&amp;CHAR(10)&amp;"・非定例日；"&amp;IF(入力!$C$55="","週・月当たり　日、その他（　　　　　　）",入力!$C$55)&amp;CHAR(10)&amp;"・１年単位の変形労働時間制の場合－年間　"&amp;IF(入力!$C$56="","　",TEXT(入力!$C$56,IF(入力!$C$56=INT(N(入力!$C$56)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$59="","第　条～第　条、第　条～第　条",入力!$C$59)</f>
-        <v>・定例日；毎週　　曜日、国民の祝日、その他（　　　　　　　　　）
-・非定例日；週・月当たり　日、その他（　　　　　　）
-・１年単位の変形労働時間制の場合－年間　　日
-○詳細は、就業規則　第　条～第　条、第　条～第　条</v>
+      <c r="C13" s="47">
+        <f>"・定例休日："&amp;IF(LEN('入力'!$C$53)=0,"実際に休日とする日を記入",'入力'!$C$53)&amp;"、その他（"&amp;IF(LEN('入力'!$C$54)=0,"　",'入力'!$C$54)&amp;"）"&amp;CHAR(10)&amp;"・非定例休日："&amp;IF(LEN('入力'!$C$55)=0,"　",'入力'!$C$55)&amp;CHAR(10)&amp;"・1年単位の変形労働時間制の場合：年間 "&amp;IF(LEN('入力'!$C$56)=0,"　",TEXT('入力'!$C$56,IF('入力'!$C$56=INT(N('入力'!$C$56)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"○詳細は、就業規則 "&amp;IF(LEN('入力'!$C$59)=0,"　",'入力'!$C$59)</f>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -5161,23 +5172,15 @@
       <c r="K13" s="47"/>
       <c r="L13" s="47"/>
     </row>
-    <row r="14" spans="1:12" ht="100" customHeight="1">
+    <row r="14" spans="1:12" ht="124" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>178</v>
       </c>
       <c r="B14" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="47" t="str">
-        <f>"１　年次有給休暇　６か月継続勤務した場合→　"&amp;IF(入力!$C$60="","　",TEXT(入力!$C$60,IF(入力!$C$60=INT(N(入力!$C$60)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　　　　　　　　 継続勤務６か月以内の年次有給休暇　（"&amp;IF(入力!$C$61="有","○有","有")&amp;"・"&amp;IF(入力!$C$61="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"　　　　　　　　 →　"&amp;IF(入力!$C$62="","　",TEXT(入力!$C$62,IF(入力!$C$62=INT(N(入力!$C$62)),"0","0.##")))&amp;"か月経過で　"&amp;IF(入力!$C$63="","　",TEXT(入力!$C$63,IF(入力!$C$63=INT(N(入力!$C$63)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　　　　　　　　 時間単位年休（"&amp;IF(入力!$C$64="有","○有","有")&amp;"・"&amp;IF(入力!$C$64="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"２　代替休暇（"&amp;IF(入力!$C$65="有","○有","有")&amp;"・"&amp;IF(入力!$C$65="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"３　その他の休暇　有給（"&amp;IF(入力!$C$66="","　　　　　　　　　　　",入力!$C$66)&amp;"）"&amp;CHAR(10)&amp;"　　　　　　　　　無給（"&amp;IF(入力!$C$67="","　　　　　　　　　　　",入力!$C$67)&amp;"）"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$68="","第　条～第　条、第　条～第　条",入力!$C$68)</f>
-        <v>１　年次有給休暇　６か月継続勤務した場合→　　日
-　　　　　　　　 継続勤務６か月以内の年次有給休暇　（有・無）
-　　　　　　　　 →　　か月経過で　　日
-　　　　　　　　 時間単位年休（有・無）
-２　代替休暇（有・無）
-３　その他の休暇　有給（　　　　　　　　　　　）
-　　　　　　　　　無給（　　　　　　　　　　　）
-○詳細は、就業規則　第　条～第　条、第　条～第　条</v>
+      <c r="C14" s="47">
+        <f>"１　年次有給休暇　６か月継続勤務した場合→　"&amp;IF(LEN('入力'!$C$60)=0,"　",TEXT('入力'!$C$60,IF('入力'!$C$60=INT(N('入力'!$C$60)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　　　　　　　　 継続勤務６か月以内の年次有給休暇　（"&amp;IF('入力'!$C$61="有","○有","有")&amp;"・"&amp;IF('入力'!$C$61="無","○無","無")&amp;"）"&amp;IF('入力'!$C$61="有",CHAR(10)&amp;"→ "&amp;IF(LEN('入力'!$C$62)=0,"　",TEXT('入力'!$C$62,IF('入力'!$C$62=INT(N('入力'!$C$62)),"0","0.##")))&amp;"か月経過で "&amp;IF(LEN('入力'!$C$63)=0,"　",TEXT('入力'!$C$63,IF('入力'!$C$63=INT(N('入力'!$C$63)),"0","0.##")))&amp;"日","")&amp;CHAR(10)&amp;"　　　　　　　　 時間単位年休（"&amp;IF('入力'!$C$64="有","○有","有")&amp;"・"&amp;IF('入力'!$C$64="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"２　代替休暇（"&amp;IF('入力'!$C$65="有","○有","有")&amp;"・"&amp;IF('入力'!$C$65="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"３　その他の休暇　有給（"&amp;IF(LEN('入力'!$C$66)=0,"　　　　　　　　　　　",'入力'!$C$66)&amp;"）"&amp;CHAR(10)&amp;"　　　　　　　　　無給（"&amp;IF(LEN('入力'!$C$67)=0,"　　　　　　　　　　　",'入力'!$C$67)&amp;"）"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(LEN('入力'!$C$68)=0,"第　条～第　条、第　条～第　条",'入力'!$C$68)</f>
       </c>
       <c r="D14" s="47"/>
       <c r="E14" s="47"/>
@@ -5189,7 +5192,7 @@
       <c r="K14" s="47"/>
       <c r="L14" s="47"/>
     </row>
-    <row r="15" spans="1:12" ht="14" customHeight="1">
+    <row r="15" spans="1:12" ht="10" customHeight="1">
       <c r="A15" s="51" t="s">
         <v>179</v>
       </c>
@@ -5241,7 +5244,7 @@
       <c r="K16" s="28"/>
       <c r="L16" s="28"/>
     </row>
-    <row r="17" spans="1:12" ht="10" customHeight="1">
+    <row r="17" spans="1:12" ht="0" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -5255,34 +5258,15 @@
       <c r="K17" s="28"/>
       <c r="L17" s="28"/>
     </row>
-    <row r="18" spans="1:12" ht="310" customHeight="1">
+    <row r="18" spans="1:12" ht="370" customHeight="1">
       <c r="A18" s="46" t="s">
         <v>180</v>
       </c>
       <c r="B18" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C18" s="50" t="str">
-        <f>"１　基本賃金　イ　月給（"&amp;IF(入力!$C$70="","　　　　　",TEXT(入力!$C$70,"#,##0"))&amp;"円）、ロ　日給（"&amp;IF(入力!$C$71="","　　　　　",TEXT(入力!$C$71,"#,##0"))&amp;"円）"&amp;CHAR(10)&amp;"　　　　　　　ハ　時間給（"&amp;IF(入力!$C$72="","　　　　　",TEXT(入力!$C$72,"#,##0"))&amp;"円）、"&amp;CHAR(10)&amp;"　　　　　　　ニ　出来高給（基本単価　"&amp;IF(入力!$C$73="","　　　　　",TEXT(入力!$C$73,"#,##0"))&amp;"円、保障給　"&amp;IF(入力!$C$74="","　　　　　",TEXT(入力!$C$74,"#,##0"))&amp;"円）"&amp;CHAR(10)&amp;"　　　　　　　ホ　その他（"&amp;IF(入力!$C$75="","　　　　　",TEXT(入力!$C$75,"#,##0"))&amp;"円）"&amp;CHAR(10)&amp;"　　　　　　　ヘ　就業規則に規定されている賃金等級等　"&amp;IF(入力!$C$76="","　　　　　　　　　　　　　　",入力!$C$76)&amp;CHAR(10)&amp;""&amp;CHAR(10)&amp;"２　諸手当の額又は計算方法"&amp;CHAR(10)&amp;"　イ（"&amp;IF(入力!$C$77="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$77)&amp;"）"&amp;CHAR(10)&amp;"　ロ（"&amp;IF(入力!$C$78="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$78)&amp;"）"&amp;CHAR(10)&amp;"　ハ（"&amp;IF(入力!$C$79="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$79)&amp;"）"&amp;CHAR(10)&amp;"　ニ（"&amp;IF(入力!$C$80="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$80)&amp;"）"&amp;CHAR(10)&amp;"３　所定時間外、休日又は深夜労働に対して支払われる割増賃金率"&amp;CHAR(10)&amp;"　イ　所定時間外、法定超　月６０時間以内（"&amp;IF(入力!$C$81="","　",TEXT(入力!$C$81,IF(入力!$C$81=INT(N(入力!$C$81)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　　　　　月６０時間超　（"&amp;IF(入力!$C$82="","　",TEXT(入力!$C$82,IF(入力!$C$82=INT(N(入力!$C$82)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　所定超　（"&amp;IF(入力!$C$83="","　",TEXT(入力!$C$83,IF(入力!$C$83=INT(N(入力!$C$83)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ロ　休日　法定休日（"&amp;IF(入力!$C$84="","　",TEXT(入力!$C$84,IF(入力!$C$84=INT(N(入力!$C$84)),"0","0.##")))&amp;"）％、法定外休日（"&amp;IF(入力!$C$85="","　",TEXT(入力!$C$85,IF(入力!$C$85=INT(N(入力!$C$85)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ハ　深夜（"&amp;IF(入力!$C$86="","　",TEXT(入力!$C$86,IF(入力!$C$86=INT(N(入力!$C$86)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"４　賃金締切日（"&amp;IF(入力!$C$87="","　　　　　",入力!$C$87)&amp;"）"&amp;CHAR(10)&amp;"５　賃金支払日（"&amp;IF(入力!$C$88="","　　　　　",入力!$C$88)&amp;"）"&amp;CHAR(10)&amp;"６　賃金の支払方法（"&amp;IF(入力!$C$89="","　　　　　　　　　　　",入力!$C$89)&amp;"）"</f>
-        <v>１　基本賃金　イ　月給（　　　　　円）、ロ　日給（　　　　　円）
-　　　　　　　ハ　時間給（　　　　　円）、
-　　　　　　　ニ　出来高給（基本単価　　　　　　円、保障給　　　　　　円）
-　　　　　　　ホ　その他（　　　　　円）
-　　　　　　　ヘ　就業規則に規定されている賃金等級等　　　　　　　　　　　　　　　
-２　諸手当の額又は計算方法
-　イ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-　ロ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-　ハ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-　ニ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-３　所定時間外、休日又は深夜労働に対して支払われる割増賃金率
-　イ　所定時間外、法定超　月６０時間以内（　）％
-　　　　　　　　　　　　　月６０時間超　（　）％
-　　　　　　　　　所定超　（　）％
-　ロ　休日　法定休日（　）％、法定外休日（　）％
-　ハ　深夜（　）％
-４　賃金締切日（　　　　　）
-５　賃金支払日（　　　　　）
-６　賃金の支払方法（　　　　　　　　　　　）</v>
+      <c r="C18" s="50">
+        <f>"１ 基本賃金 "&amp;IF('入力'!$C$115="月給","○イ 月給（"&amp;IF(LEN('入力'!$C$70)=0,"　",TEXT('入力'!$C$70,"#,##0"))&amp;"円）",IF('入力'!$C$115="日給","○ロ 日給（"&amp;IF(LEN('入力'!$C$71)=0,"　",TEXT('入力'!$C$71,"#,##0"))&amp;"円）",IF('入力'!$C$115="時間給","○ハ 時間給（"&amp;IF(LEN('入力'!$C$72)=0,"　",TEXT('入力'!$C$72,"#,##0"))&amp;"円）",IF('入力'!$C$115="出来高給","○ニ 出来高給（基本単価 "&amp;IF(LEN('入力'!$C$73)=0,"　",TEXT('入力'!$C$73,"#,##0"))&amp;"円、保障給 "&amp;IF(LEN('入力'!$C$74)=0,"　",TEXT('入力'!$C$74,"#,##0"))&amp;"円）",IF('入力'!$C$115="その他","○ホ その他（"&amp;IF(LEN('入力'!$C$75)=0,"　",TEXT('入力'!$C$75,"#,##0"))&amp;"円）","入力シート末尾の基本賃金形態を選択してください")))))&amp;CHAR(10)&amp;"　　　　　　　ヘ　就業規則に規定されている賃金等級等　"&amp;IF(LEN('入力'!$C$76)=0,"　　　　　　　　　　　　　　",'入力'!$C$76)&amp;CHAR(10)&amp;""&amp;CHAR(10)&amp;"２　諸手当の額又は計算方法"&amp;CHAR(10)&amp;"　イ（"&amp;IF(LEN('入力'!$C$77)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$77)&amp;"）"&amp;CHAR(10)&amp;"　ロ（"&amp;IF(LEN('入力'!$C$78)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$78)&amp;"）"&amp;CHAR(10)&amp;"　ハ（"&amp;IF(LEN('入力'!$C$79)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$79)&amp;"）"&amp;CHAR(10)&amp;"　ニ（"&amp;IF(LEN('入力'!$C$80)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$80)&amp;"）"&amp;CHAR(10)&amp;"３　所定時間外、休日又は深夜労働に対して支払われる割増賃金率"&amp;CHAR(10)&amp;"　イ　所定時間外、法定超　月６０時間以内（"&amp;IF(LEN('入力'!$C$81)=0,"　",TEXT('入力'!$C$81,IF('入力'!$C$81=INT(N('入力'!$C$81)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　　　　　月６０時間超　（"&amp;IF(LEN('入力'!$C$82)=0,"　",TEXT('入力'!$C$82,IF('入力'!$C$82=INT(N('入力'!$C$82)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　所定超　（"&amp;IF(LEN('入力'!$C$83)=0,"　",TEXT('入力'!$C$83,IF('入力'!$C$83=INT(N('入力'!$C$83)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ロ　休日　法定休日（"&amp;IF(LEN('入力'!$C$84)=0,"　",TEXT('入力'!$C$84,IF('入力'!$C$84=INT(N('入力'!$C$84)),"0","0.##")))&amp;"）％、法定外休日（"&amp;IF(LEN('入力'!$C$85)=0,"　",TEXT('入力'!$C$85,IF('入力'!$C$85=INT(N('入力'!$C$85)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ハ　深夜（"&amp;IF(LEN('入力'!$C$86)=0,"　",TEXT('入力'!$C$86,IF('入力'!$C$86=INT(N('入力'!$C$86)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"４　賃金締切日（"&amp;IF(LEN('入力'!$C$87)=0,"　　　　　",'入力'!$C$87)&amp;"）"&amp;CHAR(10)&amp;"５　賃金支払日（"&amp;IF(LEN('入力'!$C$88)=0,"　　　　　",'入力'!$C$88)&amp;"）"&amp;CHAR(10)&amp;"６　賃金の支払方法（"&amp;IF(LEN('入力'!$C$89)=0,"　　　　　　　　　　　",'入力'!$C$89)&amp;"）"</f>
       </c>
       <c r="D18" s="50"/>
       <c r="E18" s="50"/>
@@ -5294,19 +5278,15 @@
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
     </row>
-    <row r="19" spans="1:12" ht="70" customHeight="1">
+    <row r="19" spans="1:12" ht="108" customHeight="1">
       <c r="A19" s="46" t="s">
         <v>180</v>
       </c>
       <c r="B19" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="52" t="str">
-        <f>"７　労使協定に基づく賃金支払時の控除（"&amp;IF(入力!$C$90="","無　，　有（　　　）",入力!$C$90)&amp;"）"&amp;CHAR(10)&amp;"８　昇給（"&amp;IF(入力!$C$91="","有（時期、金額等　　　　　），無",入力!$C$91)&amp;"）"&amp;CHAR(10)&amp;"９　賞与（"&amp;IF(入力!$C$92="","有（時期、金額等　　　　　），無",入力!$C$92)&amp;"）"&amp;CHAR(10)&amp;"10　退職金（"&amp;IF(入力!$C$93="","有（時期、金額等　　　　　），無",入力!$C$93)&amp;"）"</f>
-        <v>７　労使協定に基づく賃金支払時の控除（無　，　有（　　　））
-８　昇給（有（時期、金額等　　　　　），無）
-９　賞与（有（時期、金額等　　　　　），無）
-10　退職金（有（時期、金額等　　　　　），無）</v>
+      <c r="C19" s="52">
+        <f>"７　労使協定に基づく賃金支払時の控除（"&amp;IF(LEN('入力'!$C$90)=0,"無　，　有（　　　）",'入力'!$C$90)&amp;"）"&amp;CHAR(10)&amp;"８　昇給（"&amp;IF(LEN('入力'!$C$91)=0,"有（時期、金額等　　　　　），無",'入力'!$C$91)&amp;"）"&amp;CHAR(10)&amp;"９　賞与（"&amp;IF(LEN('入力'!$C$92)=0,"有（時期、金額等　　　　　），無",'入力'!$C$92)&amp;"）"&amp;CHAR(10)&amp;"10　退職金（"&amp;IF(LEN('入力'!$C$93)=0,"有（時期、金額等　　　　　），無",'入力'!$C$93)&amp;"）"</f>
       </c>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -5318,21 +5298,15 @@
       <c r="K19" s="52"/>
       <c r="L19" s="52"/>
     </row>
-    <row r="20" spans="1:12" ht="108" customHeight="1">
+    <row r="20" spans="1:12" ht="95" customHeight="1">
       <c r="A20" s="46" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C20" s="47" t="str">
-        <f>"１　定年制　（"&amp;IF(入力!$C$95="","有（　歳），無",入力!$C$95)&amp;"）"&amp;CHAR(10)&amp;"２　継続雇用制度（"&amp;IF(入力!$C$96="","有（　歳まで），無",入力!$C$96)&amp;"）"&amp;CHAR(10)&amp;"３　創業支援等措置（"&amp;IF(入力!$C$97="","有（　歳まで業務委託・社会貢献事業），無",入力!$C$97)&amp;"）"&amp;CHAR(10)&amp;"４　自己都合退職の手続（退職する　"&amp;IF(入力!$C$98="","　",TEXT(入力!$C$98,IF(入力!$C$98=INT(N(入力!$C$98)),"0","0.##")))&amp;"日以上前に届け出ること）"&amp;CHAR(10)&amp;"５　解雇の事由及び手続　"&amp;IF(入力!$C$99="","　　　　　　　　　　　　　　　　　　　　　",入力!$C$99)&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$100="","第　条～第　条、第　条～第　条",入力!$C$100)</f>
-        <v>１　定年制　（有（　歳），無）
-２　継続雇用制度（有（　歳まで），無）
-３　創業支援等措置（有（　歳まで業務委託・社会貢献事業），無）
-４　自己都合退職の手続（退職する　　日以上前に届け出ること）
-５　解雇の事由及び手続　　　　　　　　　　　　　　　　　　　　　　
-○詳細は、就業規則　第　条～第　条、第　条～第　条</v>
+      <c r="C20" s="47">
+        <f>"１　定年制　（"&amp;IF(LEN('入力'!$C$95)=0,"有（　歳），無",'入力'!$C$95)&amp;"）"&amp;CHAR(10)&amp;"２　継続雇用制度（"&amp;IF(LEN('入力'!$C$96)=0,"有（　歳まで），無",'入力'!$C$96)&amp;"）"&amp;CHAR(10)&amp;"３　創業支援等措置（"&amp;IF(LEN('入力'!$C$97)=0,"有（　歳まで業務委託・社会貢献事業），無",'入力'!$C$97)&amp;"）"&amp;CHAR(10)&amp;"４　自己都合退職の手続（退職する　"&amp;IF(LEN('入力'!$C$98)=0,"　",TEXT('入力'!$C$98,IF('入力'!$C$98=INT(N('入力'!$C$98)),"0","0.##")))&amp;"日以上前に届け出ること）"&amp;CHAR(10)&amp;"５　解雇の事由及び手続　"&amp;IF(LEN('入力'!$C$99)=0,"　　　　　　　　　　　　　　　　　　　　　",'入力'!$C$99)&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(LEN('入力'!$C$100)=0,"第　条～第　条、第　条～第　条",'入力'!$C$100)</f>
       </c>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
@@ -5344,24 +5318,15 @@
       <c r="K20" s="47"/>
       <c r="L20" s="47"/>
     </row>
-    <row r="21" spans="1:12" ht="143" customHeight="1">
+    <row r="21" spans="1:12" ht="148" customHeight="1">
       <c r="A21" s="46" t="s">
         <v>182</v>
       </c>
       <c r="B21" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="47" t="str">
-        <f>"・社会保険の加入状況（"&amp;IF(入力!$C$101="","厚生年金　健康保険　その他（　　　）",入力!$C$101)&amp;"）"&amp;CHAR(10)&amp;"・雇用保険の適用（"&amp;IF(入力!$C$102="有","○有","有")&amp;"，"&amp;IF(入力!$C$102="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"・中小企業退職金共済制度（"&amp;IF(入力!$C$103="","加入している，加入していない",入力!$C$103)&amp;"）（※中小企業の場合）"&amp;CHAR(10)&amp;"・企業年金制度（"&amp;IF(入力!$C$104="","有（制度名　　　　　　），無",入力!$C$104)&amp;"）"&amp;CHAR(10)&amp;"・次の窓口に対して通常の労働者との間の待遇の相違（内容・理由）等について説明を求めることができる。"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(入力!$C$105="","　　　　　　　　　　　　　　　　　　　",入力!$C$105)&amp;CHAR(10)&amp;"・雇用管理の改善等に関する事項に係る相談窓口"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(入力!$C$106="","　　　　　　　　　　　　　　　　　　　",入力!$C$106)&amp;CHAR(10)&amp;"・その他（"&amp;IF(入力!$C$107="","　　　　　　　　　　　　　　　　　　　　　　　　　",入力!$C$107)&amp;"）"</f>
-        <v>・社会保険の加入状況（厚生年金　健康保険　その他（　　　））
-・雇用保険の適用（有，無）
-・中小企業退職金共済制度（加入している，加入していない）（※中小企業の場合）
-・企業年金制度（有（制度名　　　　　　），無）
-・次の窓口に対して通常の労働者との間の待遇の相違（内容・理由）等について説明を求めることができる。
-　部署名・担当者職氏名・連絡先　　　　　　　　　　　　　　　　　　　　
-・雇用管理の改善等に関する事項に係る相談窓口
-　部署名・担当者職氏名・連絡先　　　　　　　　　　　　　　　　　　　　
-・その他（　　　　　　　　　　　　　　　　　　　　　　　　　）</v>
+      <c r="C21" s="47">
+        <f>"・社会保険の加入状況（"&amp;IF(LEN('入力'!$C$101)=0,"厚生年金　健康保険　その他（　　　）",'入力'!$C$101)&amp;"）"&amp;CHAR(10)&amp;"・雇用保険の適用（"&amp;IF('入力'!$C$102="有","○有","有")&amp;"，"&amp;IF('入力'!$C$102="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"・中小企業退職金共済制度（"&amp;IF(LEN('入力'!$C$103)=0,"加入している，加入していない",'入力'!$C$103)&amp;"）（※中小企業の場合）"&amp;CHAR(10)&amp;"・企業年金制度（"&amp;IF(LEN('入力'!$C$104)=0,"有（制度名　　　　　　），無",'入力'!$C$104)&amp;"）"&amp;CHAR(10)&amp;"・次の窓口に対して通常の労働者との間の待遇の相違（内容・理由）等について説明を求めることができる。"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(LEN('入力'!$C$105)=0,"　　　　　　　　　　　　　　　　　　　",'入力'!$C$105)&amp;CHAR(10)&amp;"・雇用管理の改善等に関する事項に係る相談窓口"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(LEN('入力'!$C$106)=0,"　　　　　　　　　　　　　　　　　　　",'入力'!$C$106)&amp;CHAR(10)&amp;"・その他（"&amp;IF(LEN('入力'!$C$107)=0,"　　　　　　　　　　　　　　　　　　　　　　　　　",'入力'!$C$107)&amp;"）"</f>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -5373,17 +5338,15 @@
       <c r="K21" s="47"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="1:12" ht="85" customHeight="1">
+    <row r="22" spans="1:12" ht="65" customHeight="1">
       <c r="A22" s="46" t="s">
         <v>182</v>
       </c>
       <c r="B22" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="53" t="str">
+      <c r="C22" s="53">
         <f>"※以下は、「契約期間」について「期間の定めあり」とした場合についての説明です。"&amp;CHAR(10)&amp;"　労働契約法第18条の規定により、有期労働契約（平成25年4月1日以降に開始するもの）の契約期間が通算5年を超える場合には、労働契約の期間の末日までに労働者から申込みをすることにより、当該労働契約の期間の末日の翌日から期間の定めのない労働契約に転換されます。ただし、有期雇用特別措置法による特例の対象となる場合は、無期転換申込権の発生については、特例的に本通知書の「契約期間」の「有期雇用特別措置法による特例の対象者の場合」欄に明示したとおりとなります。"</f>
-        <v>※以下は、「契約期間」について「期間の定めあり」とした場合についての説明です。
-　労働契約法第18条の規定により、有期労働契約（平成25年4月1日以降に開始するもの）の契約期間が通算5年を超える場合には、労働契約の期間の末日までに労働者から申込みをすることにより、当該労働契約の期間の末日の翌日から期間の定めのない労働契約に転換されます。ただし、有期雇用特別措置法による特例の対象となる場合は、無期転換申込権の発生については、特例的に本通知書の「契約期間」の「有期雇用特別措置法による特例の対象者の場合」欄に明示したとおりとなります。</v>
       </c>
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
@@ -5395,11 +5358,9 @@
       <c r="K22" s="53"/>
       <c r="L22" s="53"/>
     </row>
-    <row r="23" spans="1:12" ht="28" customHeight="1">
-      <c r="A23" s="49" t="str">
-        <f>"以上のほかは、当社就業規則による。"&amp;CHAR(10)&amp;"就業規則を確認できる場所や方法（"&amp;IF(入力!$C$109="","　　　　　　　　　　　　　　　　",入力!$C$109)&amp;"）"</f>
-        <v>以上のほかは、当社就業規則による。
-就業規則を確認できる場所や方法（　　　　　　　　　　　　　　　　）</v>
+    <row r="23" spans="1:12" ht="34" customHeight="1">
+      <c r="A23" s="49">
+        <f>"以上のほかは、当社就業規則による。"&amp;CHAR(10)&amp;"就業規則を確認できる場所や方法（"&amp;IF(LEN('入力'!$C$109)=0,"　　　　　　　　　　　　　　　　",'入力'!$C$109)&amp;"）"</f>
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
@@ -5451,7 +5412,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="20" customHeight="1">
+    <row r="25" spans="1:12" ht="10" customHeight="1">
       <c r="A25" s="54" t="s">
         <v>184</v>
       </c>
@@ -5490,6 +5451,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0"/>
   <mergeCells count="36">
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>
@@ -5550,7 +5512,7 @@
     <col min="3" max="12" width="7.83203125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" ht="16" customHeight="1">
+    <row r="1" spans="1:12" ht="12" customHeight="1">
       <c r="A1" s="26" t="s">
         <v>185</v>
       </c>
@@ -5648,27 +5610,23 @@
       <c r="E4" s="30"/>
       <c r="F4" s="30"/>
       <c r="G4" s="30"/>
-      <c r="H4" s="31" t="str">
-        <f>IF(入力!$C$6="","　　年　月　日",TEXT(入力!$C$6,"yyyy年m月d日"))</f>
-        <v>　　年　月　日</v>
+      <c r="H4" s="31">
+        <f>IF(LEN('入力'!$C$6)=0,"　　年　月　日",TEXT('入力'!$C$6,"yyyy年m月d日"))</f>
       </c>
       <c r="I4" s="32"/>
       <c r="J4" s="32"/>
       <c r="K4" s="32"/>
       <c r="L4" s="33"/>
     </row>
-    <row r="5" spans="1:12" ht="30" customHeight="1">
-      <c r="A5" s="34" t="str">
-        <f>IF(入力!$C$7="","　　　　　　　　　",入力!$C$7)&amp;"　殿"</f>
-        <v>　　　　　　　　　　殿</v>
+    <row r="5" spans="1:12" ht="60" customHeight="1">
+      <c r="A5" s="34">
+        <f>IF(LEN('入力'!$C$7)=0,"　　　　　　　　　",'入力'!$C$7)&amp;"　殿"</f>
       </c>
       <c r="B5" s="35"/>
       <c r="C5" s="35"/>
       <c r="D5" s="36"/>
-      <c r="E5" s="40" t="str">
-        <f>"事業場名称・所在地　"&amp;IF(入力!$C$8="","　　　　　　　　　",入力!$C$8)&amp;CHAR(10)&amp;"　　　　　　　　　"&amp;IF(入力!$C$9="","　　　　　　　　　",入力!$C$9)</f>
-        <v>事業場名称・所在地　　　　　　　　　　
-　　　　　　　　　　　　　　　　　　</v>
+      <c r="E5" s="40">
+        <f>"事業場名称・所在地　"&amp;IF(LEN('入力'!$C$8)=0,"　　　　　　　　　",'入力'!$C$8)&amp;CHAR(10)&amp;"　　　　　　　　　"&amp;IF(LEN('入力'!$C$9)=0,"　　　　　　　　　",'入力'!$C$9)</f>
       </c>
       <c r="F5" s="41"/>
       <c r="G5" s="41"/>
@@ -5678,14 +5636,13 @@
       <c r="K5" s="41"/>
       <c r="L5" s="42"/>
     </row>
-    <row r="6" spans="1:12" ht="24" customHeight="1">
+    <row r="6" spans="1:12" ht="36" customHeight="1">
       <c r="A6" s="37"/>
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="39"/>
-      <c r="E6" s="43" t="str">
-        <f>"使　用　者　職　氏　名　"&amp;IF(入力!$C$10="","　　　　　",入力!$C$10)&amp;"　"&amp;IF(入力!$C$11="","　　　　　",入力!$C$11)</f>
-        <v>使　用　者　職　氏　名　　　　　　　　　　　　</v>
+      <c r="E6" s="43">
+        <f>"使　用　者　職　氏　名　"&amp;IF(LEN('入力'!$C$10)=0,"　　　　　",'入力'!$C$10)&amp;"　"&amp;IF(LEN('入力'!$C$11)=0,"　　　　　",'入力'!$C$11)</f>
       </c>
       <c r="F6" s="44"/>
       <c r="G6" s="44"/>
@@ -5695,24 +5652,15 @@
       <c r="K6" s="44"/>
       <c r="L6" s="45"/>
     </row>
-    <row r="7" spans="1:12" ht="116" customHeight="1">
+    <row r="7" spans="1:12" ht="100" customHeight="1">
       <c r="A7" s="46" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="46" t="s">
         <v>16</v>
       </c>
-      <c r="C7" s="47" t="str">
-        <f>IF(入力!$C$13="期間の定めなし","○期間の定めなし","期間の定めなし")&amp;"、"&amp;IF(入力!$C$13="期間の定めあり","○期間の定めあり","期間の定めあり")&amp;"（"&amp;IF(入力!$C$14="","　年　月　日",TEXT(入力!$C$14,"yyyy年m月d日"))&amp;"～"&amp;IF(入力!$C$15="","　年　月　日",TEXT(入力!$C$15,"yyyy年m月d日"))&amp;"）"&amp;CHAR(10)&amp;"※以下は、「契約期間」について「期間の定めあり」とした場合に記入"&amp;CHAR(10)&amp;"１　契約の更新の有無"&amp;CHAR(10)&amp;"　［"&amp;IF(入力!$C$16="自動的に更新する","○自動的に更新する","自動的に更新する")&amp;"・"&amp;IF(入力!$C$16="更新する場合があり得る","○更新する場合があり得る","更新する場合があり得る")&amp;"・"&amp;IF(入力!$C$16="契約の更新はしない","○契約の更新はしない","契約の更新はしない")&amp;"・"&amp;IF(入力!$C$16="その他","○その他","その他")&amp;"（"&amp;IF(入力!$C$17="","　　　",入力!$C$17)&amp;"）］"&amp;CHAR(10)&amp;"２　契約の更新は次により判断する。"&amp;CHAR(10)&amp;"　・契約期間満了時の業務量　　・勤務成績、態度　　　　・能力"&amp;CHAR(10)&amp;"　・会社の経営状況　　・従事している業務の進捗状況"&amp;CHAR(10)&amp;"　・その他（"&amp;IF(入力!$C$18="","　　　　　　　　　　　　　",入力!$C$18)&amp;"）"&amp;CHAR(10)&amp;"３　更新上限の有無（"&amp;IF(入力!$C$19="無","○無","無")&amp;"・"&amp;IF(入力!$C$19="有","○有","有")&amp;"（更新　"&amp;IF(入力!$C$20="","　",TEXT(入力!$C$20,IF(入力!$C$20=INT(N(入力!$C$20)),"0","0.##")))&amp;"回まで／通算契約期間　"&amp;IF(入力!$C$21="","　",TEXT(入力!$C$21,IF(入力!$C$21=INT(N(入力!$C$21)),"0","0.##")))&amp;"年まで））"</f>
-        <v>期間の定めなし、期間の定めあり（　年　月　日～　年　月　日）
-※以下は、「契約期間」について「期間の定めあり」とした場合に記入
-１　契約の更新の有無
-　［自動的に更新する・更新する場合があり得る・契約の更新はしない・その他（　　　）］
-２　契約の更新は次により判断する。
-　・契約期間満了時の業務量　　・勤務成績、態度　　　　・能力
-　・会社の経営状況　　・従事している業務の進捗状況
-　・その他（　　　　　　　　　　　　　）
-３　更新上限の有無（無・有（更新　　回まで／通算契約期間　　年まで））</v>
+      <c r="C7" s="47">
+        <f>IF('入力'!$C$13="期間の定めなし","○期間の定めなし","期間の定めなし")&amp;"、"&amp;IF('入力'!$C$13="期間の定めあり","○期間の定めあり","期間の定めあり")&amp;IF('入力'!$C$13="期間の定めあり","（"&amp;IF(LEN('入力'!$C$14)=0,"　年　月　日",TEXT('入力'!$C$14,"yyyy年m月d日"))&amp;"～"&amp;IF(LEN('入力'!$C$15)=0,"　年　月　日",TEXT('入力'!$C$15,"yyyy年m月d日"))&amp;"）"&amp;CHAR(10)&amp;"１ 契約更新："&amp;IF('入力'!$C$16="自動的に更新する","○自動的に更新する","自動的に更新する")&amp;"・"&amp;IF('入力'!$C$16="更新する場合があり得る","○更新する場合があり得る","更新する場合があり得る")&amp;"・"&amp;IF('入力'!$C$16="契約の更新はしない","○契約の更新はしない","契約の更新はしない")&amp;"・"&amp;IF('入力'!$C$16="その他","○その他","その他")&amp;IF(LEN('入力'!$C$17)=0,"","（"&amp;'入力'!$C$17&amp;"）")&amp;CHAR(10)&amp;"２ 契約更新の判断基準："&amp;IF(LEN('入力'!$C$18)=0,"適用する判断基準を記入",'入力'!$C$18)&amp;CHAR(10)&amp;"３ 更新上限："&amp;IF('入力'!$C$19="無","○無","無")&amp;"・"&amp;IF('入力'!$C$19="有","○有","有")&amp;IF('入力'!$C$19="有","（更新 "&amp;IF(LEN('入力'!$C$20)=0,"　",TEXT('入力'!$C$20,IF('入力'!$C$20=INT(N('入力'!$C$20)),"0","0.##")))&amp;"回まで／通算契約期間 "&amp;IF(LEN('入力'!$C$21)=0,"　",TEXT('入力'!$C$21,IF('入力'!$C$21=INT(N('入力'!$C$21)),"0","0.##")))&amp;"年まで）",""),"")</f>
       </c>
       <c r="D7" s="47"/>
       <c r="E7" s="47"/>
@@ -5724,11 +5672,9 @@
       <c r="K7" s="47"/>
       <c r="L7" s="47"/>
     </row>
-    <row r="8" spans="1:12" ht="41" customHeight="1">
-      <c r="A8" s="47" t="str">
-        <f>"【労働契約法に定める同一の企業との間での通算契約期間が５年を超える有期労働契約の締結の場合】"&amp;CHAR(10)&amp;"　本契約期間中に会社に対して期間の定めのない労働契約（無期労働契約）の締結の申込みをすることにより、本契約期間の末日の翌日（"&amp;IF(入力!$C$22="","　年　月　日",TEXT(入力!$C$22,"yyyy年m月d日"))&amp;"）から、無期労働契約での雇用に転換することができる。この場合の本契約からの労働条件の変更の有無（"&amp;IF(入力!$C$23="無","○無","無")&amp;"・"&amp;IF(入力!$C$23="有（別紙のとおり）","○有（別紙のとおり）","有（別紙のとおり）")&amp;"）"</f>
-        <v>【労働契約法に定める同一の企業との間での通算契約期間が５年を超える有期労働契約の締結の場合】
-　本契約期間中に会社に対して期間の定めのない労働契約（無期労働契約）の締結の申込みをすることにより、本契約期間の末日の翌日（　年　月　日）から、無期労働契約での雇用に転換することができる。この場合の本契約からの労働条件の変更の有無（無・有（別紙のとおり））</v>
+    <row r="8" spans="1:12" ht="45" customHeight="1">
+      <c r="A8" s="47">
+        <f>"【労働契約法に定める同一の企業との間での通算契約期間が５年を超える有期労働契約の締結の場合】"&amp;CHAR(10)&amp;"　本契約期間中に会社に対して期間の定めのない労働契約（無期労働契約）の締結の申込みをすることにより、本契約期間の末日の翌日（"&amp;IF(LEN('入力'!$C$22)=0,"　年　月　日",TEXT('入力'!$C$22,"yyyy年m月d日"))&amp;"）から、無期労働契約での雇用に転換することができる。この場合の本契約からの労働条件の変更の有無（"&amp;IF('入力'!$C$23="無","○無","無")&amp;"・"&amp;IF('入力'!$C$23="有（別紙のとおり）","○有（別紙のとおり）","有（別紙のとおり）")&amp;"）"</f>
       </c>
       <c r="B8" s="47"/>
       <c r="C8" s="47"/>
@@ -5742,13 +5688,9 @@
       <c r="K8" s="47"/>
       <c r="L8" s="47"/>
     </row>
-    <row r="9" spans="1:12" ht="56" customHeight="1">
-      <c r="A9" s="47" t="str">
-        <f>"【有期雇用特別措置法による特例の対象者の場合】"&amp;CHAR(10)&amp;"　無期転換申込権が発生しない期間：　Ⅰ（高度専門）・Ⅱ（定年後の高齢者）　　対象："&amp;IF(入力!$C$24="","　　　　　　",入力!$C$24)&amp;CHAR(10)&amp;"　Ⅰ　特定有期業務の開始から完了までの期間（　"&amp;IF(入力!$C$25="","　",TEXT(入力!$C$25,IF(入力!$C$25=INT(N(入力!$C$25)),"0","0.##")))&amp;"か月（上限10年））"&amp;CHAR(10)&amp;"　Ⅱ　定年後引き続いて雇用されている期間"</f>
-        <v>【有期雇用特別措置法による特例の対象者の場合】
-　無期転換申込権が発生しない期間：　Ⅰ（高度専門）・Ⅱ（定年後の高齢者）　　対象：　　　　　　
-　Ⅰ　特定有期業務の開始から完了までの期間（　　か月（上限10年））
-　Ⅱ　定年後引き続いて雇用されている期間</v>
+    <row r="9" spans="1:12" ht="38" customHeight="1">
+      <c r="A9" s="47">
+        <f>"【有期雇用特別措置法による特例の対象者の場合】"&amp;CHAR(10)&amp;"無期転換申込権が発生しない期間／対象："&amp;IF(LEN('入力'!$C$24)=0,"　",'入力'!$C$24)&amp;IF('入力'!$C$24="高度専門",CHAR(10)&amp;"Ⅰ 特定有期業務の開始から完了まで（"&amp;IF(LEN('入力'!$C$25)=0,"　",TEXT('入力'!$C$25,IF('入力'!$C$25=INT(N('入力'!$C$25)),"0","0.##")))&amp;"か月、上限10年）",IF('入力'!$C$24="定年後の高齢者",CHAR(10)&amp;"Ⅱ 定年後引き続いて雇用されている期間",""))</f>
       </c>
       <c r="B9" s="47"/>
       <c r="C9" s="47"/>
@@ -5762,17 +5704,15 @@
       <c r="K9" s="47"/>
       <c r="L9" s="47"/>
     </row>
-    <row r="10" spans="1:12" ht="28" customHeight="1">
+    <row r="10" spans="1:12" ht="60" customHeight="1">
       <c r="A10" s="48" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="49" t="str">
-        <f>"（雇入れ直後）"&amp;IF(入力!$C$27="","　　　　　　　　　　　",入力!$C$27)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(入力!$C$28="","　　　　　　　　　　　",入力!$C$28)</f>
-        <v>（雇入れ直後）　　　　　　　　　　　
-（変更の範囲）　　　　　　　　　　　</v>
+      <c r="C10" s="49">
+        <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$27)=0,"　　　　　　　　　　　",'入力'!$C$27)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$28)=0,"　　　　　　　　　　　",'入力'!$C$28)</f>
       </c>
       <c r="D10" s="49"/>
       <c r="E10" s="49"/>
@@ -5784,19 +5724,15 @@
       <c r="K10" s="49"/>
       <c r="L10" s="49"/>
     </row>
-    <row r="11" spans="1:12" ht="54" customHeight="1">
+    <row r="11" spans="1:12" ht="96" customHeight="1">
       <c r="A11" s="48" t="s">
         <v>175</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="47" t="str">
-        <f>"（雇入れ直後）"&amp;IF(入力!$C$29="","　　　　　　　　　　　",入力!$C$29)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(入力!$C$30="","　　　　　　　　　　　",入力!$C$30)&amp;CHAR(10)&amp;"【有期雇用特別措置法による特例の対象者（高度専門）の場合】"&amp;CHAR(10)&amp;"・特定有期業務（"&amp;IF(入力!$C$31="","　　　　　　　　　",入力!$C$31)&amp;"　開始日："&amp;IF(入力!$C$32="","　　　　",TEXT(入力!$C$32,"yyyy年m月d日"))&amp;"　完了日："&amp;IF(入力!$C$33="","　　　　",TEXT(入力!$C$33,"yyyy年m月d日"))&amp;"）"</f>
-        <v>（雇入れ直後）　　　　　　　　　　　
-（変更の範囲）　　　　　　　　　　　
-【有期雇用特別措置法による特例の対象者（高度専門）の場合】
-・特定有期業務（　　　　　　　　　　開始日：　　　　　完了日：　　　　）</v>
+      <c r="C11" s="47">
+        <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$29)=0,"　　　　　　　　　　　",'入力'!$C$29)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$30)=0,"　　　　　　　　　　　",'入力'!$C$30)&amp;CHAR(10)&amp;"【有期雇用特別措置法による特例の対象者（高度専門）の場合】"&amp;CHAR(10)&amp;"・特定有期業務（"&amp;IF(LEN('入力'!$C$31)=0,"　　　　　　　　　",'入力'!$C$31)&amp;"　開始日："&amp;IF(LEN('入力'!$C$32)=0,"　　　　",TEXT('入力'!$C$32,"yyyy年m月d日"))&amp;"　完了日："&amp;IF(LEN('入力'!$C$33)=0,"　　　　",TEXT('入力'!$C$33,"yyyy年m月d日"))&amp;"）"</f>
       </c>
       <c r="D11" s="47"/>
       <c r="E11" s="47"/>
@@ -5808,31 +5744,21 @@
       <c r="K11" s="47"/>
       <c r="L11" s="47"/>
     </row>
-    <row r="12" spans="1:12" ht="276" customHeight="1">
-      <c r="A12" s="50" t="s">
-        <v>176</v>
+    <row r="12" spans="1:12" ht="130" customHeight="1">
+      <c r="A12" s="50" t="inlineStr">
+        <is>
+          <t xml:space="preserve">始業・終業の時刻
+休憩時間
+勤務制度
+所定時間外労働
+休日労働</t>
+        </is>
       </c>
       <c r="B12" s="50" t="s">
         <v>176</v>
       </c>
-      <c r="C12" s="50" t="str">
-        <f>"１　始業・終業の時刻等"&amp;CHAR(10)&amp;"(1) 始業（"&amp;IF(入力!$C$35="","　時　分",入力!$C$35)&amp;"）　終業（"&amp;IF(入力!$C$36="","　時　分",入力!$C$36)&amp;"）"&amp;CHAR(10)&amp;"【以下のような制度が労働者に適用される場合】"&amp;CHAR(10)&amp;"(2) 変形労働時間制等；（"&amp;IF(入力!$C$37="","　",入力!$C$37)&amp;"）単位の変形労働時間制・交替制として、次の勤務時間の組み合わせによる。"&amp;CHAR(10)&amp;"　├ "&amp;IF(入力!$C$38="","始業（　時　分）終業（　時　分）（適用日　　　　）",入力!$C$38)&amp;CHAR(10)&amp;"　├ "&amp;IF(入力!$C$39="","始業（　時　分）終業（　時　分）（適用日　　　　）",入力!$C$39)&amp;CHAR(10)&amp;"　└ "&amp;IF(入力!$C$40="","始業（　時　分）終業（　時　分）（適用日　　　　）",入力!$C$40)&amp;CHAR(10)&amp;"(3) フレックスタイム制；始業及び終業の時刻は労働者の決定に委ねる。"&amp;CHAR(10)&amp;"　（ただし、フレキシブルタイム　"&amp;IF(入力!$C$41="","（始業）　時　分から　時　分、（終業）　時　分から　時　分",入力!$C$41)&amp;"、"&amp;CHAR(10)&amp;"　　　　　　　　コアタイム　"&amp;IF(入力!$C$42="","　時　分から　時　分",入力!$C$42)&amp;"）"&amp;CHAR(10)&amp;"(4) 事業場外みなし労働時間制；"&amp;IF(入力!$C$43="","始業（　時　分）終業（　時　分）",入力!$C$43)&amp;CHAR(10)&amp;"(5) 裁量労働制；"&amp;IF(入力!$C$44="","始業（　時　分）終業（　時　分）",入力!$C$44)&amp;"を基本とし、労働者の決定に委ねる。"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$45="","第　条～第　条、第　条～第　条、第　条～第　条",入力!$C$45)&amp;CHAR(10)&amp;"２　休憩時間（"&amp;IF(入力!$C$46="","　",TEXT(入力!$C$46,IF(入力!$C$46=INT(N(入力!$C$46)),"0","0.##")))&amp;"）分"&amp;CHAR(10)&amp;"３　所定時間外労働の有無（"&amp;IF(入力!$C$47="有","○有","有")&amp;"，"&amp;IF(入力!$C$47="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"４　休日労働（"&amp;IF(入力!$C$48="有","○有","有")&amp;"（１週　"&amp;IF(入力!$C$49="","　",入力!$C$49)&amp;"時間、１か月　"&amp;IF(入力!$C$50="","　日・　時間",入力!$C$50)&amp;"、１年　"&amp;IF(入力!$C$51="","　日",入力!$C$51)&amp;"），"&amp;IF(入力!$C$48="無","○無","無")&amp;"）"</f>
-        <v>１　始業・終業の時刻等
-(1) 始業（　時　分）　終業（　時　分）
-【以下のような制度が労働者に適用される場合】
-(2) 変形労働時間制等；（　）単位の変形労働時間制・交替制として、次の勤務時間の組み合わせによる。
-　├ 始業（　時　分）終業（　時　分）（適用日　　　　）
-　├ 始業（　時　分）終業（　時　分）（適用日　　　　）
-　└ 始業（　時　分）終業（　時　分）（適用日　　　　）
-(3) フレックスタイム制；始業及び終業の時刻は労働者の決定に委ねる。
-　（ただし、フレキシブルタイム　（始業）　時　分から　時　分、（終業）　時　分から　時　分、
-　　　　　　　　コアタイム　　時　分から　時　分）
-(4) 事業場外みなし労働時間制；始業（　時　分）終業（　時　分）
-(5) 裁量労働制；始業（　時　分）終業（　時　分）を基本とし、労働者の決定に委ねる。
-○詳細は、就業規則　第　条～第　条、第　条～第　条、第　条～第　条
-２　休憩時間（　）分
-３　所定時間外労働の有無（有，無）
-４　休日労働（有（１週　　時間、１か月　　日・　時間、１年　　日），無）</v>
+      <c r="C12" s="50">
+        <f>"１ 始業・終業の時刻等"&amp;CHAR(10)&amp;IF('入力'!$C$114="通常勤務","○(1) 始業（"&amp;IF(LEN('入力'!$C$35)=0,"　時　分",'入力'!$C$35)&amp;"） 終業（"&amp;IF(LEN('入力'!$C$36)=0,"　時　分",'入力'!$C$36)&amp;"）",IF('入力'!$C$114="変形労働時間制等","○(2) "&amp;IF(LEN('入力'!$C$37)=0,"適用する制度の名称を記入",'入力'!$C$37)&amp;CHAR(10)&amp;IF(LEN('入力'!$C$38)=0,"始業・終業・適用日を記入",'入力'!$C$38)&amp;CHAR(10)&amp;IF(LEN('入力'!$C$39)=0,"",'入力'!$C$39)&amp;CHAR(10)&amp;IF(LEN('入力'!$C$40)=0,"",'入力'!$C$40),IF('入力'!$C$114="フレックスタイム制","○(3) フレックスタイム制：始業・終業は労働者の決定に委ねる。"&amp;CHAR(10)&amp;"フレキシブルタイム："&amp;IF(LEN('入力'!$C$41)=0,"　",'入力'!$C$41)&amp;CHAR(10)&amp;"コアタイム："&amp;IF(LEN('入力'!$C$42)=0,"　",'入力'!$C$42),IF('入力'!$C$114="事業場外みなし労働時間制","○(4) 事業場外みなし労働時間制："&amp;IF(LEN('入力'!$C$43)=0,"始業・終業を記入",'入力'!$C$43),IF('入力'!$C$114="裁量労働制","○(5) 裁量労働制："&amp;IF(LEN('入力'!$C$44)=0,"始業・終業を記入",'入力'!$C$44)&amp;"を基本とし、労働者の決定に委ねる。","入力シート末尾の勤務制度を選択してください")))))&amp;CHAR(10)&amp;"○詳細は、就業規則 "&amp;IF(LEN('入力'!$C$45)=0,"　",'入力'!$C$45)&amp;CHAR(10)&amp;"２ 休憩時間（"&amp;IF(LEN('入力'!$C$46)=0,"　",TEXT('入力'!$C$46,IF('入力'!$C$46=INT(N('入力'!$C$46)),"0","0.##")))&amp;"）分"&amp;CHAR(10)&amp;"３ 所定時間外労働（"&amp;IF('入力'!$C$47="有","○有","有")&amp;IF('入力'!$C$47="有","（1週 "&amp;IF(LEN('入力'!$C$49)=0,"　",TEXT('入力'!$C$49,IF('入力'!$C$49=INT(N('入力'!$C$49)),"0","0.##")))&amp;"時間、1か月 "&amp;IF(LEN('入力'!$C$50)=0,"　",TEXT('入力'!$C$50,IF('入力'!$C$50=INT(N('入力'!$C$50)),"0","0.##")))&amp;"時間、1年 "&amp;IF(LEN('入力'!$C$51)=0,"　",TEXT('入力'!$C$51,IF('入力'!$C$51=INT(N('入力'!$C$51)),"0","0.##")))&amp;"時間）","")&amp;"、"&amp;IF('入力'!$C$47="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"４ 休日労働（"&amp;IF('入力'!$C$48="有","○有","有")&amp;IF('入力'!$C$48="有","（1か月 "&amp;IF(LEN('入力'!$C$116)=0,"　",TEXT('入力'!$C$116,IF('入力'!$C$116=INT(N('入力'!$C$116)),"0","0.##")))&amp;"日、1年 "&amp;IF(LEN('入力'!$C$117)=0,"　",TEXT('入力'!$C$117,IF('入力'!$C$117=INT(N('入力'!$C$117)),"0","0.##")))&amp;"日）","")&amp;"、"&amp;IF('入力'!$C$48="無","○無","無")&amp;"）"</f>
       </c>
       <c r="D12" s="50"/>
       <c r="E12" s="50"/>
@@ -5851,13 +5777,8 @@
       <c r="B13" s="46" t="s">
         <v>186</v>
       </c>
-      <c r="C13" s="47" t="str">
-        <f>"・定例日；毎週　"&amp;IF(入力!$C$53="","　曜日",入力!$C$53)&amp;"、国民の祝日、その他（"&amp;IF(入力!$C$54="","　　　　　　　　　",入力!$C$54)&amp;"）"&amp;CHAR(10)&amp;"・非定例日；"&amp;IF(入力!$C$55="","週・月当たり　日、その他（　　　　　　）",入力!$C$55)&amp;CHAR(10)&amp;"・１年単位の変形労働時間制の場合－年間　"&amp;IF(入力!$C$56="","　",TEXT(入力!$C$56,IF(入力!$C$56=INT(N(入力!$C$56)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　（勤務日）毎週（"&amp;IF(入力!$C$57="","　　　　　　　",入力!$C$57)&amp;"）、その他（"&amp;IF(入力!$C$58="","　　　　　　　",入力!$C$58)&amp;"）"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$59="","第　条～第　条、第　条～第　条",入力!$C$59)</f>
-        <v>・定例日；毎週　　曜日、国民の祝日、その他（　　　　　　　　　）
-・非定例日；週・月当たり　日、その他（　　　　　　）
-・１年単位の変形労働時間制の場合－年間　　日
-　（勤務日）毎週（　　　　　　　）、その他（　　　　　　　）
-○詳細は、就業規則　第　条～第　条、第　条～第　条</v>
+      <c r="C13" s="47">
+        <f>"・定例休日："&amp;IF(LEN('入力'!$C$53)=0,"実際に休日とする日を記入",'入力'!$C$53)&amp;"、その他（"&amp;IF(LEN('入力'!$C$54)=0,"　",'入力'!$C$54)&amp;"）"&amp;CHAR(10)&amp;"・非定例休日："&amp;IF(LEN('入力'!$C$55)=0,"　",'入力'!$C$55)&amp;CHAR(10)&amp;"・1年単位の変形労働時間制の場合：年間 "&amp;IF(LEN('入力'!$C$56)=0,"　",TEXT('入力'!$C$56,IF('入力'!$C$56=INT(N('入力'!$C$56)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"（勤務日）毎週（"&amp;IF(LEN('入力'!$C$57)=0,"　",'入力'!$C$57)&amp;"）、その他（"&amp;IF(LEN('入力'!$C$58)=0,"　",'入力'!$C$58)&amp;"）"&amp;CHAR(10)&amp;"○詳細は、就業規則 "&amp;IF(LEN('入力'!$C$59)=0,"　",'入力'!$C$59)</f>
       </c>
       <c r="D13" s="47"/>
       <c r="E13" s="47"/>
@@ -5869,23 +5790,15 @@
       <c r="K13" s="47"/>
       <c r="L13" s="47"/>
     </row>
-    <row r="14" spans="1:12" ht="100" customHeight="1">
+    <row r="14" spans="1:12" ht="124" customHeight="1">
       <c r="A14" s="46" t="s">
         <v>178</v>
       </c>
       <c r="B14" s="46" t="s">
         <v>178</v>
       </c>
-      <c r="C14" s="47" t="str">
-        <f>"１　年次有給休暇　６か月継続勤務した場合→　"&amp;IF(入力!$C$60="","　",TEXT(入力!$C$60,IF(入力!$C$60=INT(N(入力!$C$60)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　　　　　　　　 継続勤務６か月以内の年次有給休暇　（"&amp;IF(入力!$C$61="有","○有","有")&amp;"・"&amp;IF(入力!$C$61="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"　　　　　　　　 →　"&amp;IF(入力!$C$62="","　",TEXT(入力!$C$62,IF(入力!$C$62=INT(N(入力!$C$62)),"0","0.##")))&amp;"か月経過で　"&amp;IF(入力!$C$63="","　",TEXT(入力!$C$63,IF(入力!$C$63=INT(N(入力!$C$63)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　　　　　　　　 時間単位年休（"&amp;IF(入力!$C$64="有","○有","有")&amp;"・"&amp;IF(入力!$C$64="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"２　代替休暇（"&amp;IF(入力!$C$65="有","○有","有")&amp;"・"&amp;IF(入力!$C$65="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"３　その他の休暇　有給（"&amp;IF(入力!$C$66="","　　　　　　　　　　　",入力!$C$66)&amp;"）"&amp;CHAR(10)&amp;"　　　　　　　　　無給（"&amp;IF(入力!$C$67="","　　　　　　　　　　　",入力!$C$67)&amp;"）"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$68="","第　条～第　条、第　条～第　条",入力!$C$68)</f>
-        <v>１　年次有給休暇　６か月継続勤務した場合→　　日
-　　　　　　　　 継続勤務６か月以内の年次有給休暇　（有・無）
-　　　　　　　　 →　　か月経過で　　日
-　　　　　　　　 時間単位年休（有・無）
-２　代替休暇（有・無）
-３　その他の休暇　有給（　　　　　　　　　　　）
-　　　　　　　　　無給（　　　　　　　　　　　）
-○詳細は、就業規則　第　条～第　条、第　条～第　条</v>
+      <c r="C14" s="47">
+        <f>"１　年次有給休暇　６か月継続勤務した場合→　"&amp;IF(LEN('入力'!$C$60)=0,"　",TEXT('入力'!$C$60,IF('入力'!$C$60=INT(N('入力'!$C$60)),"0","0.##")))&amp;"日"&amp;CHAR(10)&amp;"　　　　　　　　 継続勤務６か月以内の年次有給休暇　（"&amp;IF('入力'!$C$61="有","○有","有")&amp;"・"&amp;IF('入力'!$C$61="無","○無","無")&amp;"）"&amp;IF('入力'!$C$61="有",CHAR(10)&amp;"→ "&amp;IF(LEN('入力'!$C$62)=0,"　",TEXT('入力'!$C$62,IF('入力'!$C$62=INT(N('入力'!$C$62)),"0","0.##")))&amp;"か月経過で "&amp;IF(LEN('入力'!$C$63)=0,"　",TEXT('入力'!$C$63,IF('入力'!$C$63=INT(N('入力'!$C$63)),"0","0.##")))&amp;"日","")&amp;CHAR(10)&amp;"　　　　　　　　 時間単位年休（"&amp;IF('入力'!$C$64="有","○有","有")&amp;"・"&amp;IF('入力'!$C$64="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"２　代替休暇（"&amp;IF('入力'!$C$65="有","○有","有")&amp;"・"&amp;IF('入力'!$C$65="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"３　その他の休暇　有給（"&amp;IF(LEN('入力'!$C$66)=0,"　　　　　　　　　　　",'入力'!$C$66)&amp;"）"&amp;CHAR(10)&amp;"　　　　　　　　　無給（"&amp;IF(LEN('入力'!$C$67)=0,"　　　　　　　　　　　",'入力'!$C$67)&amp;"）"&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(LEN('入力'!$C$68)=0,"第　条～第　条、第　条～第　条",'入力'!$C$68)</f>
       </c>
       <c r="D14" s="47"/>
       <c r="E14" s="47"/>
@@ -5897,7 +5810,7 @@
       <c r="K14" s="47"/>
       <c r="L14" s="47"/>
     </row>
-    <row r="15" spans="1:12" ht="14" customHeight="1">
+    <row r="15" spans="1:12" ht="10" customHeight="1">
       <c r="A15" s="51" t="s">
         <v>179</v>
       </c>
@@ -5949,7 +5862,7 @@
       <c r="K16" s="28"/>
       <c r="L16" s="28"/>
     </row>
-    <row r="17" spans="1:12" ht="10" customHeight="1">
+    <row r="17" spans="1:12" ht="0" customHeight="1">
       <c r="A17" s="28"/>
       <c r="B17" s="28"/>
       <c r="C17" s="28"/>
@@ -5963,34 +5876,15 @@
       <c r="K17" s="28"/>
       <c r="L17" s="28"/>
     </row>
-    <row r="18" spans="1:12" ht="310" customHeight="1">
+    <row r="18" spans="1:12" ht="370" customHeight="1">
       <c r="A18" s="46" t="s">
         <v>180</v>
       </c>
       <c r="B18" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C18" s="50" t="str">
-        <f>"１　基本賃金　イ　月給（"&amp;IF(入力!$C$70="","　　　　　",TEXT(入力!$C$70,"#,##0"))&amp;"円）、ロ　日給（"&amp;IF(入力!$C$71="","　　　　　",TEXT(入力!$C$71,"#,##0"))&amp;"円）"&amp;CHAR(10)&amp;"　　　　　　　ハ　時間給（"&amp;IF(入力!$C$72="","　　　　　",TEXT(入力!$C$72,"#,##0"))&amp;"円）、"&amp;CHAR(10)&amp;"　　　　　　　ニ　出来高給（基本単価　"&amp;IF(入力!$C$73="","　　　　　",TEXT(入力!$C$73,"#,##0"))&amp;"円、保障給　"&amp;IF(入力!$C$74="","　　　　　",TEXT(入力!$C$74,"#,##0"))&amp;"円）"&amp;CHAR(10)&amp;"　　　　　　　ホ　その他（"&amp;IF(入力!$C$75="","　　　　　",TEXT(入力!$C$75,"#,##0"))&amp;"円）"&amp;CHAR(10)&amp;"　　　　　　　ヘ　就業規則に規定されている賃金等級等　"&amp;IF(入力!$C$76="","　　　　　　　　　　　　　　",入力!$C$76)&amp;CHAR(10)&amp;""&amp;CHAR(10)&amp;"２　諸手当の額又は計算方法"&amp;CHAR(10)&amp;"　イ（"&amp;IF(入力!$C$77="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$77)&amp;"）"&amp;CHAR(10)&amp;"　ロ（"&amp;IF(入力!$C$78="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$78)&amp;"）"&amp;CHAR(10)&amp;"　ハ（"&amp;IF(入力!$C$79="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$79)&amp;"）"&amp;CHAR(10)&amp;"　ニ（"&amp;IF(入力!$C$80="","　　　手当　　　円 ／計算方法：　　　　　　　　　",入力!$C$80)&amp;"）"&amp;CHAR(10)&amp;"３　所定時間外、休日又は深夜労働に対して支払われる割増賃金率"&amp;CHAR(10)&amp;"　イ　所定時間外、法定超　月６０時間以内（"&amp;IF(入力!$C$81="","　",TEXT(入力!$C$81,IF(入力!$C$81=INT(N(入力!$C$81)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　　　　　月６０時間超　（"&amp;IF(入力!$C$82="","　",TEXT(入力!$C$82,IF(入力!$C$82=INT(N(入力!$C$82)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　所定超　（"&amp;IF(入力!$C$83="","　",TEXT(入力!$C$83,IF(入力!$C$83=INT(N(入力!$C$83)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ロ　休日　法定休日（"&amp;IF(入力!$C$84="","　",TEXT(入力!$C$84,IF(入力!$C$84=INT(N(入力!$C$84)),"0","0.##")))&amp;"）％、法定外休日（"&amp;IF(入力!$C$85="","　",TEXT(入力!$C$85,IF(入力!$C$85=INT(N(入力!$C$85)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ハ　深夜（"&amp;IF(入力!$C$86="","　",TEXT(入力!$C$86,IF(入力!$C$86=INT(N(入力!$C$86)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"４　賃金締切日（"&amp;IF(入力!$C$87="","　　　　　",入力!$C$87)&amp;"）"&amp;CHAR(10)&amp;"５　賃金支払日（"&amp;IF(入力!$C$88="","　　　　　",入力!$C$88)&amp;"）"&amp;CHAR(10)&amp;"６　賃金の支払方法（"&amp;IF(入力!$C$89="","　　　　　　　　　　　",入力!$C$89)&amp;"）"</f>
-        <v>１　基本賃金　イ　月給（　　　　　円）、ロ　日給（　　　　　円）
-　　　　　　　ハ　時間給（　　　　　円）、
-　　　　　　　ニ　出来高給（基本単価　　　　　　円、保障給　　　　　　円）
-　　　　　　　ホ　その他（　　　　　円）
-　　　　　　　ヘ　就業規則に規定されている賃金等級等　　　　　　　　　　　　　　　
-２　諸手当の額又は計算方法
-　イ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-　ロ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-　ハ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-　ニ（　　　手当　　　円 ／計算方法：　　　　　　　　　）
-３　所定時間外、休日又は深夜労働に対して支払われる割増賃金率
-　イ　所定時間外、法定超　月６０時間以内（　）％
-　　　　　　　　　　　　　月６０時間超　（　）％
-　　　　　　　　　所定超　（　）％
-　ロ　休日　法定休日（　）％、法定外休日（　）％
-　ハ　深夜（　）％
-４　賃金締切日（　　　　　）
-５　賃金支払日（　　　　　）
-６　賃金の支払方法（　　　　　　　　　　　）</v>
+      <c r="C18" s="50">
+        <f>"１ 基本賃金 "&amp;IF('入力'!$C$115="月給","○イ 月給（"&amp;IF(LEN('入力'!$C$70)=0,"　",TEXT('入力'!$C$70,"#,##0"))&amp;"円）",IF('入力'!$C$115="日給","○ロ 日給（"&amp;IF(LEN('入力'!$C$71)=0,"　",TEXT('入力'!$C$71,"#,##0"))&amp;"円）",IF('入力'!$C$115="時間給","○ハ 時間給（"&amp;IF(LEN('入力'!$C$72)=0,"　",TEXT('入力'!$C$72,"#,##0"))&amp;"円）",IF('入力'!$C$115="出来高給","○ニ 出来高給（基本単価 "&amp;IF(LEN('入力'!$C$73)=0,"　",TEXT('入力'!$C$73,"#,##0"))&amp;"円、保障給 "&amp;IF(LEN('入力'!$C$74)=0,"　",TEXT('入力'!$C$74,"#,##0"))&amp;"円）",IF('入力'!$C$115="その他","○ホ その他（"&amp;IF(LEN('入力'!$C$75)=0,"　",TEXT('入力'!$C$75,"#,##0"))&amp;"円）","入力シート末尾の基本賃金形態を選択してください")))))&amp;CHAR(10)&amp;"　　　　　　　ヘ　就業規則に規定されている賃金等級等　"&amp;IF(LEN('入力'!$C$76)=0,"　　　　　　　　　　　　　　",'入力'!$C$76)&amp;CHAR(10)&amp;""&amp;CHAR(10)&amp;"２　諸手当の額又は計算方法"&amp;CHAR(10)&amp;"　イ（"&amp;IF(LEN('入力'!$C$77)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$77)&amp;"）"&amp;CHAR(10)&amp;"　ロ（"&amp;IF(LEN('入力'!$C$78)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$78)&amp;"）"&amp;CHAR(10)&amp;"　ハ（"&amp;IF(LEN('入力'!$C$79)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$79)&amp;"）"&amp;CHAR(10)&amp;"　ニ（"&amp;IF(LEN('入力'!$C$80)=0,"　　　手当　　　円 ／計算方法：　　　　　　　　　",'入力'!$C$80)&amp;"）"&amp;CHAR(10)&amp;"３　所定時間外、休日又は深夜労働に対して支払われる割増賃金率"&amp;CHAR(10)&amp;"　イ　所定時間外、法定超　月６０時間以内（"&amp;IF(LEN('入力'!$C$81)=0,"　",TEXT('入力'!$C$81,IF('入力'!$C$81=INT(N('入力'!$C$81)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　　　　　月６０時間超　（"&amp;IF(LEN('入力'!$C$82)=0,"　",TEXT('入力'!$C$82,IF('入力'!$C$82=INT(N('入力'!$C$82)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　　　　　　　　　所定超　（"&amp;IF(LEN('入力'!$C$83)=0,"　",TEXT('入力'!$C$83,IF('入力'!$C$83=INT(N('入力'!$C$83)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ロ　休日　法定休日（"&amp;IF(LEN('入力'!$C$84)=0,"　",TEXT('入力'!$C$84,IF('入力'!$C$84=INT(N('入力'!$C$84)),"0","0.##")))&amp;"）％、法定外休日（"&amp;IF(LEN('入力'!$C$85)=0,"　",TEXT('入力'!$C$85,IF('入力'!$C$85=INT(N('入力'!$C$85)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"　ハ　深夜（"&amp;IF(LEN('入力'!$C$86)=0,"　",TEXT('入力'!$C$86,IF('入力'!$C$86=INT(N('入力'!$C$86)),"0","0.##")))&amp;"）％"&amp;CHAR(10)&amp;"４　賃金締切日（"&amp;IF(LEN('入力'!$C$87)=0,"　　　　　",'入力'!$C$87)&amp;"）"&amp;CHAR(10)&amp;"５　賃金支払日（"&amp;IF(LEN('入力'!$C$88)=0,"　　　　　",'入力'!$C$88)&amp;"）"&amp;CHAR(10)&amp;"６　賃金の支払方法（"&amp;IF(LEN('入力'!$C$89)=0,"　　　　　　　　　　　",'入力'!$C$89)&amp;"）"</f>
       </c>
       <c r="D18" s="50"/>
       <c r="E18" s="50"/>
@@ -6002,19 +5896,15 @@
       <c r="K18" s="50"/>
       <c r="L18" s="50"/>
     </row>
-    <row r="19" spans="1:12" ht="70" customHeight="1">
+    <row r="19" spans="1:12" ht="108" customHeight="1">
       <c r="A19" s="46" t="s">
         <v>180</v>
       </c>
       <c r="B19" s="46" t="s">
         <v>180</v>
       </c>
-      <c r="C19" s="52" t="str">
-        <f>"７　労使協定に基づく賃金支払時の控除（"&amp;IF(入力!$C$90="","無　，　有（　　　）",入力!$C$90)&amp;"）"&amp;CHAR(10)&amp;"８　昇給（"&amp;IF(入力!$C$91="","有（時期、金額等　　　　　），無",入力!$C$91)&amp;"）"&amp;CHAR(10)&amp;"９　賞与（"&amp;IF(入力!$C$92="","有（時期、金額等　　　　　），無",入力!$C$92)&amp;"）"&amp;CHAR(10)&amp;"10　退職金（"&amp;IF(入力!$C$93="","有（時期、金額等　　　　　），無",入力!$C$93)&amp;"）"</f>
-        <v>７　労使協定に基づく賃金支払時の控除（無　，　有（　　　））
-８　昇給（有（時期、金額等　　　　　），無）
-９　賞与（有（時期、金額等　　　　　），無）
-10　退職金（有（時期、金額等　　　　　），無）</v>
+      <c r="C19" s="52">
+        <f>"７　労使協定に基づく賃金支払時の控除（"&amp;IF(LEN('入力'!$C$90)=0,"無　，　有（　　　）",'入力'!$C$90)&amp;"）"&amp;CHAR(10)&amp;"８　昇給（"&amp;IF(LEN('入力'!$C$91)=0,"有（時期、金額等　　　　　），無",'入力'!$C$91)&amp;"）"&amp;CHAR(10)&amp;"９　賞与（"&amp;IF(LEN('入力'!$C$92)=0,"有（時期、金額等　　　　　），無",'入力'!$C$92)&amp;"）"&amp;CHAR(10)&amp;"10　退職金（"&amp;IF(LEN('入力'!$C$93)=0,"有（時期、金額等　　　　　），無",'入力'!$C$93)&amp;"）"</f>
       </c>
       <c r="D19" s="52"/>
       <c r="E19" s="52"/>
@@ -6026,21 +5916,15 @@
       <c r="K19" s="52"/>
       <c r="L19" s="52"/>
     </row>
-    <row r="20" spans="1:12" ht="84" customHeight="1">
+    <row r="20" spans="1:12" ht="95" customHeight="1">
       <c r="A20" s="46" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="46" t="s">
         <v>181</v>
       </c>
-      <c r="C20" s="47" t="str">
-        <f>"１　定年制　（"&amp;IF(入力!$C$95="","有（　歳），無",入力!$C$95)&amp;"）"&amp;CHAR(10)&amp;"２　継続雇用制度（"&amp;IF(入力!$C$96="","有（　歳まで），無",入力!$C$96)&amp;"）"&amp;CHAR(10)&amp;"３　創業支援等措置（"&amp;IF(入力!$C$97="","有（　歳まで業務委託・社会貢献事業），無",入力!$C$97)&amp;"）"&amp;CHAR(10)&amp;"４　自己都合退職の手続（退職する　"&amp;IF(入力!$C$98="","　",TEXT(入力!$C$98,IF(入力!$C$98=INT(N(入力!$C$98)),"0","0.##")))&amp;"日以上前に届け出ること）"&amp;CHAR(10)&amp;"５　解雇の事由及び手続　"&amp;IF(入力!$C$99="","　　　　　　　　　　　　　　　　　　　　　",入力!$C$99)&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(入力!$C$100="","第　条～第　条、第　条～第　条",入力!$C$100)</f>
-        <v>１　定年制　（有（　歳），無）
-２　継続雇用制度（有（　歳まで），無）
-３　創業支援等措置（有（　歳まで業務委託・社会貢献事業），無）
-４　自己都合退職の手続（退職する　　日以上前に届け出ること）
-５　解雇の事由及び手続　　　　　　　　　　　　　　　　　　　　　　
-○詳細は、就業規則　第　条～第　条、第　条～第　条</v>
+      <c r="C20" s="47">
+        <f>"１　定年制　（"&amp;IF(LEN('入力'!$C$95)=0,"有（　歳），無",'入力'!$C$95)&amp;"）"&amp;CHAR(10)&amp;"２　継続雇用制度（"&amp;IF(LEN('入力'!$C$96)=0,"有（　歳まで），無",'入力'!$C$96)&amp;"）"&amp;CHAR(10)&amp;"３　創業支援等措置（"&amp;IF(LEN('入力'!$C$97)=0,"有（　歳まで業務委託・社会貢献事業），無",'入力'!$C$97)&amp;"）"&amp;CHAR(10)&amp;"４　自己都合退職の手続（退職する　"&amp;IF(LEN('入力'!$C$98)=0,"　",TEXT('入力'!$C$98,IF('入力'!$C$98=INT(N('入力'!$C$98)),"0","0.##")))&amp;"日以上前に届け出ること）"&amp;CHAR(10)&amp;"５　解雇の事由及び手続　"&amp;IF(LEN('入力'!$C$99)=0,"　　　　　　　　　　　　　　　　　　　　　",'入力'!$C$99)&amp;CHAR(10)&amp;"○詳細は、就業規則　"&amp;IF(LEN('入力'!$C$100)=0,"第　条～第　条、第　条～第　条",'入力'!$C$100)</f>
       </c>
       <c r="D20" s="47"/>
       <c r="E20" s="47"/>
@@ -6052,25 +5936,15 @@
       <c r="K20" s="47"/>
       <c r="L20" s="47"/>
     </row>
-    <row r="21" spans="1:12" ht="148" customHeight="1">
+    <row r="21" spans="1:12" ht="180" customHeight="1">
       <c r="A21" s="46" t="s">
         <v>182</v>
       </c>
       <c r="B21" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="C21" s="47" t="str">
-        <f>"・社会保険の加入状況（"&amp;IF(入力!$C$101="","厚生年金　健康保険　その他（　　　）",入力!$C$101)&amp;"）"&amp;CHAR(10)&amp;"・雇用保険の適用（"&amp;IF(入力!$C$102="有","○有","有")&amp;"，"&amp;IF(入力!$C$102="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"・中小企業退職金共済制度（"&amp;IF(入力!$C$103="","加入している，加入していない",入力!$C$103)&amp;"）（※中小企業の場合）"&amp;CHAR(10)&amp;"・企業年金制度（"&amp;IF(入力!$C$104="","有（制度名　　　　　　），無",入力!$C$104)&amp;"）"&amp;CHAR(10)&amp;"・次の窓口に対して通常の労働者との間の待遇の相違（内容・理由）等について説明を求めることができる。"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(入力!$C$105="","　　　　　　　　　　　　　　　　　　　",入力!$C$105)&amp;CHAR(10)&amp;"・雇用管理の改善等に関する事項に係る相談窓口"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(入力!$C$106="","　　　　　　　　　　　　　　　　　　　",入力!$C$106)&amp;CHAR(10)&amp;"・その他（"&amp;IF(入力!$C$107="","　　　　　　　　　　　　　　　　　　　　　　　　　",入力!$C$107)&amp;"）"&amp;CHAR(10)&amp;"・具体的に適用される就業規則名（"&amp;IF(入力!$C$108="","　　　　　　　　　　　　　　",入力!$C$108)&amp;"）"</f>
-        <v>・社会保険の加入状況（厚生年金　健康保険　その他（　　　））
-・雇用保険の適用（有，無）
-・中小企業退職金共済制度（加入している，加入していない）（※中小企業の場合）
-・企業年金制度（有（制度名　　　　　　），無）
-・次の窓口に対して通常の労働者との間の待遇の相違（内容・理由）等について説明を求めることができる。
-　部署名・担当者職氏名・連絡先　　　　　　　　　　　　　　　　　　　　
-・雇用管理の改善等に関する事項に係る相談窓口
-　部署名・担当者職氏名・連絡先　　　　　　　　　　　　　　　　　　　　
-・その他（　　　　　　　　　　　　　　　　　　　　　　　　　）
-・具体的に適用される就業規則名（　　　　　　　　　　　　　　）</v>
+      <c r="C21" s="47">
+        <f>"・社会保険の加入状況（"&amp;IF(LEN('入力'!$C$101)=0,"厚生年金　健康保険　その他（　　　）",'入力'!$C$101)&amp;"）"&amp;CHAR(10)&amp;"・雇用保険の適用（"&amp;IF('入力'!$C$102="有","○有","有")&amp;"，"&amp;IF('入力'!$C$102="無","○無","無")&amp;"）"&amp;CHAR(10)&amp;"・中小企業退職金共済制度（"&amp;IF(LEN('入力'!$C$103)=0,"加入している，加入していない",'入力'!$C$103)&amp;"）（※中小企業の場合）"&amp;CHAR(10)&amp;"・企業年金制度（"&amp;IF(LEN('入力'!$C$104)=0,"有（制度名　　　　　　），無",'入力'!$C$104)&amp;"）"&amp;CHAR(10)&amp;"・次の窓口に対して通常の労働者との間の待遇の相違（内容・理由）等について説明を求めることができる。"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(LEN('入力'!$C$105)=0,"　　　　　　　　　　　　　　　　　　　",'入力'!$C$105)&amp;CHAR(10)&amp;"・雇用管理の改善等に関する事項に係る相談窓口"&amp;CHAR(10)&amp;"　部署名・担当者職氏名・連絡先　"&amp;IF(LEN('入力'!$C$106)=0,"　　　　　　　　　　　　　　　　　　　",'入力'!$C$106)&amp;CHAR(10)&amp;"・その他（"&amp;IF(LEN('入力'!$C$107)=0,"　　　　　　　　　　　　　　　　　　　　　　　　　",'入力'!$C$107)&amp;"）"&amp;CHAR(10)&amp;"・具体的に適用される就業規則名（"&amp;IF(LEN('入力'!$C$108)=0,"　　　　　　　　　　　　　　",'入力'!$C$108)&amp;"）"</f>
       </c>
       <c r="D21" s="47"/>
       <c r="E21" s="47"/>
@@ -6082,17 +5956,15 @@
       <c r="K21" s="47"/>
       <c r="L21" s="47"/>
     </row>
-    <row r="22" spans="1:12" ht="85" customHeight="1">
+    <row r="22" spans="1:12" ht="65" customHeight="1">
       <c r="A22" s="46" t="s">
         <v>182</v>
       </c>
       <c r="B22" s="46" t="s">
         <v>182</v>
       </c>
-      <c r="C22" s="53" t="str">
+      <c r="C22" s="53">
         <f>"※以下は、「契約期間」について「期間の定めあり」とした場合についての説明です。"&amp;CHAR(10)&amp;"　労働契約法第18条の規定により、有期労働契約（平成25年4月1日以降に開始するもの）の契約期間が通算5年を超える場合には、労働契約の期間の末日までに労働者から申込みをすることにより、当該労働契約の期間の末日の翌日から期間の定めのない労働契約に転換されます。ただし、有期雇用特別措置法による特例の対象となる場合は、無期転換申込権の発生については、特例的に本通知書の「契約期間」の「有期雇用特別措置法による特例の対象者の場合」欄に明示したとおりとなります。"</f>
-        <v>※以下は、「契約期間」について「期間の定めあり」とした場合についての説明です。
-　労働契約法第18条の規定により、有期労働契約（平成25年4月1日以降に開始するもの）の契約期間が通算5年を超える場合には、労働契約の期間の末日までに労働者から申込みをすることにより、当該労働契約の期間の末日の翌日から期間の定めのない労働契約に転換されます。ただし、有期雇用特別措置法による特例の対象となる場合は、無期転換申込権の発生については、特例的に本通知書の「契約期間」の「有期雇用特別措置法による特例の対象者の場合」欄に明示したとおりとなります。</v>
       </c>
       <c r="D22" s="53"/>
       <c r="E22" s="53"/>
@@ -6104,11 +5976,9 @@
       <c r="K22" s="53"/>
       <c r="L22" s="53"/>
     </row>
-    <row r="23" spans="1:12" ht="35" customHeight="1">
-      <c r="A23" s="49" t="str">
-        <f>"以上のほかは、当社就業規則による。"&amp;CHAR(10)&amp;"就業規則を確認できる場所や方法（"&amp;IF(入力!$C$109="","　　　　　　　　　　　　　　　　",入力!$C$109)&amp;"）"</f>
-        <v>以上のほかは、当社就業規則による。
-就業規則を確認できる場所や方法（　　　　　　　　　　　　　　　　）</v>
+    <row r="23" spans="1:12" ht="34" customHeight="1">
+      <c r="A23" s="49">
+        <f>"以上のほかは、当社就業規則による。"&amp;CHAR(10)&amp;"就業規則を確認できる場所や方法（"&amp;IF(LEN('入力'!$C$109)=0,"　　　　　　　　　　　　　　　　",'入力'!$C$109)&amp;"）"</f>
       </c>
       <c r="B23" s="49"/>
       <c r="C23" s="49"/>
@@ -6160,7 +6030,7 @@
         <v>183</v>
       </c>
     </row>
-    <row r="25" spans="1:12" ht="20" customHeight="1">
+    <row r="25" spans="1:12" ht="10" customHeight="1">
       <c r="A25" s="54" t="s">
         <v>184</v>
       </c>
@@ -6199,6 +6069,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0"/>
   <mergeCells count="36">
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>

--- a/assets/download/onboarding-kit/labor-notice.xlsx
+++ b/assets/download/onboarding-kit/labor-notice.xlsx
@@ -1184,175 +1184,236 @@
     </border>
   </borders>
   <cellStyleXfs count="2">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="16" fillId="0" borderId="0"/>
+    <xf applyProtection="1" numFmtId="0" fontId="0" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="16" fillId="0" borderId="0">
+      <protection locked="0"/>
+    </xf>
   </cellStyleXfs>
-  <cellXfs count="65">
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
+  <cellXfs count="72">
+    <xf applyProtection="1" numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="1" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="2" fillId="2" borderId="1" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="3" fillId="3" borderId="2" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="3" fillId="3" borderId="3" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="3" fillId="3" borderId="4" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="4" fillId="4" borderId="5" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="4" fillId="4" borderId="6" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="4" fillId="4" borderId="7" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="5" fillId="3" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="31" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="31" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="7" fillId="2" borderId="9" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="6" fillId="5" borderId="8" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="1" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="1" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="176" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="176" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="177" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="177" fontId="6" fillId="5" borderId="8" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="10" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="11" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="12" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="13" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="14" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="15" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="16" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="8" fillId="3" borderId="17" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="13" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
+      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="178" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1388,6 +1449,34 @@
     </xf>
     <xf applyProtection="1" numFmtId="1" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="center" vertical="center"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="top"/>
+      <protection locked="0"/>
+    </xf>
+    <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment wrapText="1" horizontal="left" vertical="top"/>
       <protection locked="0"/>
     </xf>
   </cellXfs>
@@ -5024,7 +5113,7 @@
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="39"/>
-      <c r="E6" s="43">
+      <c r="E6" s="68">
         <f>"使　用　者　職　氏　名　"&amp;IF(LEN('入力'!$C$10)=0,"　　　　　",'入力'!$C$10)&amp;"　"&amp;IF(LEN('入力'!$C$11)=0,"　　　　　",'入力'!$C$11)</f>
       </c>
       <c r="F6" s="44"/>
@@ -5036,7 +5125,7 @@
       <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="100" customHeight="1">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="65" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="46" t="s">
@@ -5088,13 +5177,13 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:12" ht="60" customHeight="1">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="66" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="55">
+      <c r="C10" s="67">
         <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$27)=0,"　　　　　　　　　　　",'入力'!$C$27)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$28)=0,"　　　　　　　　　　　",'入力'!$C$28)</f>
       </c>
       <c r="D10" s="55"/>
@@ -5108,13 +5197,13 @@
       <c r="L10" s="55"/>
     </row>
     <row r="11" spans="1:12" ht="96" customHeight="1">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="66" t="s">
         <v>175</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="55">
+      <c r="C11" s="67">
         <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$29)=0,"　　　　　　　　　　　",'入力'!$C$29)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$30)=0,"　　　　　　　　　　　",'入力'!$C$30)&amp;CHAR(10)&amp;"【有期雇用特別措置法による特例の対象者（高度専門）の場合】"&amp;CHAR(10)&amp;"・特定有期業務（"&amp;IF(LEN('入力'!$C$31)=0,"　　　　　　　　　",'入力'!$C$31)&amp;"　開始日："&amp;IF(LEN('入力'!$C$32)=0,"　　　　",TEXT('入力'!$C$32,"yyyy年m月d日"))&amp;"　完了日："&amp;IF(LEN('入力'!$C$33)=0,"　　　　",TEXT('入力'!$C$33,"yyyy年m月d日"))&amp;"）"</f>
       </c>
       <c r="D11" s="55"/>
@@ -5128,7 +5217,7 @@
       <c r="L11" s="55"/>
     </row>
     <row r="12" spans="1:12" ht="130" customHeight="1">
-      <c r="A12" s="48" t="inlineStr">
+      <c r="A12" s="66" t="inlineStr">
         <is>
           <t xml:space="preserve">始業・終業の時刻
 休憩時間
@@ -5153,7 +5242,7 @@
       <c r="L12" s="50"/>
     </row>
     <row r="13" spans="1:12" ht="55" customHeight="1">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="65" t="s">
         <v>177</v>
       </c>
       <c r="B13" s="46" t="s">
@@ -5173,7 +5262,7 @@
       <c r="L13" s="47"/>
     </row>
     <row r="14" spans="1:12" ht="124" customHeight="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="65" t="s">
         <v>178</v>
       </c>
       <c r="B14" s="46" t="s">
@@ -5259,7 +5348,7 @@
       <c r="L17" s="28"/>
     </row>
     <row r="18" spans="1:12" ht="370" customHeight="1">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="65" t="s">
         <v>180</v>
       </c>
       <c r="B18" s="46" t="s">
@@ -5299,7 +5388,7 @@
       <c r="L19" s="52"/>
     </row>
     <row r="20" spans="1:12" ht="95" customHeight="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="65" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="46" t="s">
@@ -5319,7 +5408,7 @@
       <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:12" ht="148" customHeight="1">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="65" t="s">
         <v>182</v>
       </c>
       <c r="B21" s="46" t="s">
@@ -5451,7 +5540,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0"/>
   <mergeCells count="36">
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>
@@ -5641,7 +5729,7 @@
       <c r="B6" s="38"/>
       <c r="C6" s="38"/>
       <c r="D6" s="39"/>
-      <c r="E6" s="43">
+      <c r="E6" s="68">
         <f>"使　用　者　職　氏　名　"&amp;IF(LEN('入力'!$C$10)=0,"　　　　　",'入力'!$C$10)&amp;"　"&amp;IF(LEN('入力'!$C$11)=0,"　　　　　",'入力'!$C$11)</f>
       </c>
       <c r="F6" s="44"/>
@@ -5653,7 +5741,7 @@
       <c r="L6" s="45"/>
     </row>
     <row r="7" spans="1:12" ht="100" customHeight="1">
-      <c r="A7" s="46" t="s">
+      <c r="A7" s="65" t="s">
         <v>16</v>
       </c>
       <c r="B7" s="46" t="s">
@@ -5705,13 +5793,13 @@
       <c r="L9" s="47"/>
     </row>
     <row r="10" spans="1:12" ht="60" customHeight="1">
-      <c r="A10" s="48" t="s">
+      <c r="A10" s="66" t="s">
         <v>174</v>
       </c>
       <c r="B10" s="48" t="s">
         <v>174</v>
       </c>
-      <c r="C10" s="49">
+      <c r="C10" s="70">
         <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$27)=0,"　　　　　　　　　　　",'入力'!$C$27)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$28)=0,"　　　　　　　　　　　",'入力'!$C$28)</f>
       </c>
       <c r="D10" s="49"/>
@@ -5725,13 +5813,13 @@
       <c r="L10" s="49"/>
     </row>
     <row r="11" spans="1:12" ht="96" customHeight="1">
-      <c r="A11" s="48" t="s">
+      <c r="A11" s="66" t="s">
         <v>175</v>
       </c>
       <c r="B11" s="48" t="s">
         <v>175</v>
       </c>
-      <c r="C11" s="47">
+      <c r="C11" s="71">
         <f>"（雇入れ直後）"&amp;IF(LEN('入力'!$C$29)=0,"　　　　　　　　　　　",'入力'!$C$29)&amp;CHAR(10)&amp;"（変更の範囲）"&amp;IF(LEN('入力'!$C$30)=0,"　　　　　　　　　　　",'入力'!$C$30)&amp;CHAR(10)&amp;"【有期雇用特別措置法による特例の対象者（高度専門）の場合】"&amp;CHAR(10)&amp;"・特定有期業務（"&amp;IF(LEN('入力'!$C$31)=0,"　　　　　　　　　",'入力'!$C$31)&amp;"　開始日："&amp;IF(LEN('入力'!$C$32)=0,"　　　　",TEXT('入力'!$C$32,"yyyy年m月d日"))&amp;"　完了日："&amp;IF(LEN('入力'!$C$33)=0,"　　　　",TEXT('入力'!$C$33,"yyyy年m月d日"))&amp;"）"</f>
       </c>
       <c r="D11" s="47"/>
@@ -5745,7 +5833,7 @@
       <c r="L11" s="47"/>
     </row>
     <row r="12" spans="1:12" ht="130" customHeight="1">
-      <c r="A12" s="50" t="inlineStr">
+      <c r="A12" s="69" t="inlineStr">
         <is>
           <t xml:space="preserve">始業・終業の時刻
 休憩時間
@@ -5771,7 +5859,7 @@
       <c r="L12" s="50"/>
     </row>
     <row r="13" spans="1:12" ht="66" customHeight="1">
-      <c r="A13" s="46" t="s">
+      <c r="A13" s="65" t="s">
         <v>186</v>
       </c>
       <c r="B13" s="46" t="s">
@@ -5791,7 +5879,7 @@
       <c r="L13" s="47"/>
     </row>
     <row r="14" spans="1:12" ht="124" customHeight="1">
-      <c r="A14" s="46" t="s">
+      <c r="A14" s="65" t="s">
         <v>178</v>
       </c>
       <c r="B14" s="46" t="s">
@@ -5877,7 +5965,7 @@
       <c r="L17" s="28"/>
     </row>
     <row r="18" spans="1:12" ht="370" customHeight="1">
-      <c r="A18" s="46" t="s">
+      <c r="A18" s="65" t="s">
         <v>180</v>
       </c>
       <c r="B18" s="46" t="s">
@@ -5917,7 +6005,7 @@
       <c r="L19" s="52"/>
     </row>
     <row r="20" spans="1:12" ht="95" customHeight="1">
-      <c r="A20" s="46" t="s">
+      <c r="A20" s="65" t="s">
         <v>181</v>
       </c>
       <c r="B20" s="46" t="s">
@@ -5937,7 +6025,7 @@
       <c r="L20" s="47"/>
     </row>
     <row r="21" spans="1:12" ht="180" customHeight="1">
-      <c r="A21" s="46" t="s">
+      <c r="A21" s="65" t="s">
         <v>182</v>
       </c>
       <c r="B21" s="46" t="s">
@@ -6069,7 +6157,6 @@
       </c>
     </row>
   </sheetData>
-  <sheetProtection sheet="1" objects="1" scenarios="1" selectLockedCells="0" selectUnlockedCells="0"/>
   <mergeCells count="36">
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>

--- a/assets/download/onboarding-kit/labor-notice.xlsx
+++ b/assets/download/onboarding-kit/labor-notice.xlsx
@@ -192,7 +192,7 @@
     <t>特定有期業務の完了日</t>
   </si>
   <si>
-    <t>始業・終業・休憩・時間外労働</t>
+    <t>始業・終業・休憩・時間外労働（勤務制度は114行で選択）</t>
   </si>
   <si>
     <t>始業時刻</t>
@@ -369,7 +369,7 @@
     <t>休暇の就業規則条文</t>
   </si>
   <si>
-    <t>賃金</t>
+    <t>賃金（基本賃金の形態は115行で選択）</t>
   </si>
   <si>
     <t>月給</t>
@@ -764,7 +764,7 @@
     </fill>
     <fill>
       <patternFill patternType="solid">
-        <fgColor rgb="FFFFFBEA"/>
+        <fgColor rgb="FFFFF2CC"/>
       </patternFill>
     </fill>
   </fills>

--- a/assets/download/onboarding-kit/labor-notice.xlsx
+++ b/assets/download/onboarding-kit/labor-notice.xlsx
@@ -13,6 +13,7 @@
     <sheet name="短時間労働者用" sheetId="3" r:id="rId3"/>
   </sheets>
   <definedNames>
+    <definedName name="_xlnm.Print_Area" localSheetId="0">入力!$A$1:$J$117</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="1">一般労働者用!$A$1:$L$25</definedName>
     <definedName name="_xlnm.Print_Area" localSheetId="2">短時間労働者用!$A$1:$L$25</definedName>
   </definedNames>
@@ -1297,71 +1298,54 @@
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="10" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="11" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="18" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="19" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="20" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="21" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="22" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="right" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="23" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="24" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="25" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="29" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="30" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="13" fillId="2" borderId="31" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="26" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="27" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="28" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1369,51 +1353,39 @@
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="33" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="34" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="9" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="36" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="37" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="15" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="178" fontId="6" fillId="5" borderId="38" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
@@ -1453,31 +1425,24 @@
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="32" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="12" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="center" vertical="center"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
     <xf applyProtection="1" numFmtId="0" fontId="14" fillId="2" borderId="35" xfId="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment wrapText="1" horizontal="left" vertical="top"/>
-      <protection locked="0"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -1692,6 +1657,9 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+  <sheetPr>
+    <pageSetUpPr fitToPage="1"/>
+  </sheetPr>
   <dimension ref="A1:J125"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.83203125" defaultRowHeight="14"/>
   <cols>
@@ -4969,6 +4937,7 @@
     </dataValidation>
   </dataValidations>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" fitToWidth="1" fitToHeight="0" orientation="portrait"/>
 </worksheet>
 </file>
 
@@ -5540,6 +5509,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="36">
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>
@@ -6157,6 +6127,7 @@
       </c>
     </row>
   </sheetData>
+  <sheetProtection sheet="1" objects="1" scenarios="1"/>
   <mergeCells count="36">
     <mergeCell ref="A23:L23"/>
     <mergeCell ref="A24:L24"/>
